--- a/docs/Homes List.xlsx
+++ b/docs/Homes List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9df306d6984b8b22/Documents/GitHub/Wix-Products/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80D36A84-4750-49D3-A74F-D751E3159B6F}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77D415F4-09C2-4EF8-939C-A0EF6A103F06}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="171">
   <si>
     <t xml:space="preserve">Golden West </t>
   </si>
@@ -741,6 +741,12 @@
   </si>
   <si>
     <t>27' x 56'</t>
+  </si>
+  <si>
+    <t>PDF Link</t>
+  </si>
+  <si>
+    <t>Virtual 360  Rendering link</t>
   </si>
 </sst>
 </file>
@@ -860,7 +866,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -929,16 +935,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -946,9 +961,6 @@
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -964,15 +976,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
@@ -991,6 +994,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1352,2183 +1370,2233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69257E43-B717-415B-87B6-EDDB262DB689}">
   <dimension ref="A1:F172"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="19" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.453125" customWidth="1"/>
     <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" customWidth="1"/>
+    <col min="6" max="6" width="28.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+    </row>
+    <row r="2" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="E2" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>409</v>
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>540</v>
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>648</v>
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>702</v>
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>756</v>
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>810</v>
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <v>891</v>
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>840</v>
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <v>900</v>
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <v>990</v>
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <v>547</v>
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <v>800</v>
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="8">
         <v>944</v>
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="8">
         <v>1101</v>
       </c>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="8">
         <v>864</v>
       </c>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="8">
         <v>900</v>
       </c>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="8">
         <v>900</v>
       </c>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="8">
         <v>1152</v>
       </c>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="8">
         <v>1176</v>
       </c>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="8">
         <v>1188</v>
       </c>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="8">
         <v>1188</v>
       </c>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A24" s="7" t="s">
+    <row r="24" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="8">
         <v>1296</v>
       </c>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="8">
         <v>1296</v>
       </c>
       <c r="D25" s="1"/>
     </row>
-    <row r="26" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="8">
         <v>1296</v>
       </c>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="8">
         <v>1296</v>
       </c>
       <c r="D27" s="1"/>
     </row>
-    <row r="28" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="8">
         <v>1296</v>
       </c>
       <c r="D28" s="1"/>
     </row>
-    <row r="29" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="8">
         <v>1404</v>
       </c>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="8">
         <v>1512</v>
       </c>
       <c r="D30" s="1"/>
     </row>
-    <row r="31" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="8">
         <v>1512</v>
       </c>
       <c r="D31" s="1"/>
     </row>
-    <row r="32" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="8">
         <v>1512</v>
       </c>
       <c r="D32" s="1"/>
     </row>
-    <row r="33" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="8">
         <v>1512</v>
       </c>
       <c r="D33" s="1"/>
     </row>
-    <row r="34" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A34" s="7" t="s">
+    <row r="34" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="8">
         <v>1620</v>
       </c>
       <c r="D34" s="1"/>
     </row>
-    <row r="35" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C35" s="8">
         <v>1836</v>
       </c>
       <c r="D35" s="1"/>
     </row>
-    <row r="36" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A36" s="7" t="s">
+    <row r="36" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="8">
         <v>1836</v>
       </c>
       <c r="D36" s="1"/>
     </row>
-    <row r="37" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="8">
         <v>1917</v>
       </c>
       <c r="D37" s="1"/>
     </row>
-    <row r="38" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="6" t="s">
+    <row r="38" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="10" t="s">
+      <c r="E38" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C39" s="8">
         <v>852</v>
       </c>
       <c r="D39" s="1"/>
     </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="10" t="s">
+    <row r="40" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="8">
         <v>958</v>
       </c>
       <c r="D40" s="1"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="10" t="s">
+    <row r="41" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="8">
         <v>1026</v>
       </c>
       <c r="D41" s="1"/>
     </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="10" t="s">
+    <row r="42" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="8">
         <v>1296</v>
       </c>
       <c r="D42" s="1"/>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="10" t="s">
+    <row r="43" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C43" s="8">
         <v>1296</v>
       </c>
       <c r="D43" s="1"/>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="10" t="s">
+    <row r="44" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="8">
         <v>1404</v>
       </c>
       <c r="D44" s="1"/>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="10" t="s">
+    <row r="45" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="8">
         <v>1404</v>
       </c>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="10" t="s">
+    <row r="46" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="8">
         <v>1512</v>
       </c>
       <c r="D46" s="1"/>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="10" t="s">
+    <row r="47" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47" s="8">
         <v>1512</v>
       </c>
       <c r="D47" s="1"/>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="10" t="s">
+    <row r="48" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="8">
         <v>1512</v>
       </c>
       <c r="D48" s="1"/>
     </row>
-    <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="10" t="s">
+    <row r="49" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="8">
         <v>1512</v>
       </c>
       <c r="D49" s="1"/>
     </row>
-    <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="10" t="s">
+    <row r="50" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="8">
         <v>1620</v>
       </c>
       <c r="D50" s="1"/>
     </row>
-    <row r="51" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="10" t="s">
+    <row r="51" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="8">
         <v>1782</v>
       </c>
       <c r="D51" s="1"/>
     </row>
-    <row r="52" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="10" t="s">
+    <row r="52" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="8">
         <v>1836</v>
       </c>
       <c r="D52" s="1"/>
     </row>
-    <row r="53" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="10" t="s">
+    <row r="53" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C53" s="9">
+      <c r="C53" s="8">
         <v>1836</v>
       </c>
       <c r="D53" s="1"/>
     </row>
-    <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="10" t="s">
+    <row r="54" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54" s="8">
         <v>2280</v>
       </c>
       <c r="D54" s="1"/>
     </row>
-    <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="10" t="s">
+    <row r="55" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C55" s="9">
+      <c r="C55" s="8">
         <v>2280</v>
       </c>
       <c r="D55" s="1"/>
     </row>
-    <row r="56" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="10" t="s">
+    <row r="56" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C56" s="9">
+      <c r="C56" s="8">
         <v>2347</v>
       </c>
       <c r="D56" s="1"/>
     </row>
-    <row r="57" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="10" t="s">
+    <row r="57" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C57" s="9">
+      <c r="C57" s="8">
         <v>2347</v>
       </c>
       <c r="D57" s="1"/>
     </row>
-    <row r="58" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="10" t="s">
+    <row r="58" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C58" s="9">
+      <c r="C58" s="8">
         <v>2038</v>
       </c>
       <c r="D58" s="1"/>
     </row>
-    <row r="59" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="10" t="s">
+    <row r="59" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C59" s="9">
+      <c r="C59" s="8">
         <v>2654</v>
       </c>
       <c r="D59" s="1"/>
     </row>
-    <row r="60" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="11" t="s">
+    <row r="60" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="18"/>
       <c r="D60" s="2"/>
     </row>
-    <row r="61" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="6" t="s">
+    <row r="61" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A62" s="14">
+      <c r="E61" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="10">
         <v>1001</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C62" s="9">
+      <c r="C62" s="8">
         <v>480</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
     </row>
-    <row r="63" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A63" s="14">
+    <row r="63" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="10">
         <v>1002</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C63" s="9">
+      <c r="C63" s="8">
         <v>533</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
     </row>
-    <row r="64" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A64" s="14">
+    <row r="64" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="10">
         <v>1003</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C64" s="9">
+      <c r="C64" s="8">
         <v>640</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
     </row>
-    <row r="65" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A65" s="14">
+    <row r="65" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="10">
         <v>1004</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C65" s="9">
+      <c r="C65" s="8">
         <v>746</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
     </row>
-    <row r="66" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A66" s="14">
+    <row r="66" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="10">
         <v>1005</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C66" s="9">
+      <c r="C66" s="8">
         <v>800</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
     </row>
-    <row r="67" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="14">
+    <row r="67" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="10">
         <v>1006</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C67" s="9">
+      <c r="C67" s="8">
         <v>720</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
     </row>
-    <row r="68" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A68" s="14">
+    <row r="68" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="10">
         <v>1007</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C68" s="9">
+      <c r="C68" s="8">
         <v>840</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
     </row>
-    <row r="69" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A69" s="14">
+    <row r="69" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="10">
         <v>1008</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C69" s="9">
+      <c r="C69" s="8">
         <v>900</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
     </row>
-    <row r="70" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A70" s="14">
+    <row r="70" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="10">
         <v>1009</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C70" s="9">
+      <c r="C70" s="8">
         <v>990</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
     </row>
-    <row r="71" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A71" s="14">
+    <row r="71" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="10">
         <v>1010</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C71" s="15">
+      <c r="C71" s="11">
         <v>1080</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A72" s="14">
+    <row r="72" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="10">
         <v>2015</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C72" s="15">
+      <c r="C72" s="11">
         <v>1173</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
     </row>
-    <row r="73" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A73" s="14">
+    <row r="73" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="10">
         <v>2017</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C73" s="15">
+      <c r="C73" s="11">
         <v>1280</v>
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A74" s="14">
+    <row r="74" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="10">
         <v>2019</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C74" s="15">
+      <c r="C74" s="11">
         <v>1280</v>
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A75" s="14">
+    <row r="75" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="10">
         <v>2021</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C75" s="15">
+      <c r="C75" s="11">
         <v>1493</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A76" s="14">
+    <row r="76" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="10">
         <v>2022</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C76" s="15">
+      <c r="C76" s="11">
         <v>1493</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
     </row>
-    <row r="77" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A77" s="14">
+    <row r="77" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="10">
         <v>2023</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C77" s="15">
+      <c r="C77" s="11">
         <v>1493</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
     </row>
-    <row r="78" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A78" s="14">
+    <row r="78" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="10">
         <v>2024</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C78" s="15">
+      <c r="C78" s="11">
         <v>1600</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
     </row>
-    <row r="79" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A79" s="14">
+    <row r="79" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="10">
         <v>2025</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C79" s="15">
+      <c r="C79" s="11">
         <v>1814</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A80" s="14">
+    <row r="80" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="10">
         <v>2028</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C80" s="15">
+      <c r="C80" s="11">
         <v>2100</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
     </row>
-    <row r="81" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A81" s="14">
+    <row r="81" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="10">
         <v>2029</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C81" s="9">
+      <c r="C81" s="8">
         <v>864</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
     </row>
-    <row r="82" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A82" s="14">
+    <row r="82" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="10">
         <v>2030</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C82" s="15">
+      <c r="C82" s="11">
         <v>1280</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
     </row>
-    <row r="83" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A83" s="14">
+    <row r="83" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="10">
         <v>2031</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C83" s="15">
+      <c r="C83" s="11">
         <v>1280</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
     </row>
-    <row r="84" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A84" s="14">
+    <row r="84" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="10">
         <v>2032</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C84" s="15">
+      <c r="C84" s="11">
         <v>1493</v>
       </c>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
     </row>
-    <row r="85" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A85" s="14">
+    <row r="85" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="10">
         <v>2033</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C85" s="15">
+      <c r="C85" s="11">
         <v>1493</v>
       </c>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
     </row>
-    <row r="86" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A86" s="14">
+    <row r="86" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="10">
         <v>2034</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C86" s="15">
+      <c r="C86" s="11">
         <v>1600</v>
       </c>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
     </row>
-    <row r="87" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A87" s="14">
+    <row r="87" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="10">
         <v>2035</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C87" s="15">
+      <c r="C87" s="11">
         <v>1920</v>
       </c>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A88" s="14">
+    <row r="88" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="10">
         <v>2036</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C88" s="15">
+      <c r="C88" s="11">
         <v>1056</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
     </row>
-    <row r="89" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A89" s="14">
+    <row r="89" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="10">
         <v>2037</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B89" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C89" s="15">
+      <c r="C89" s="11">
         <v>1344</v>
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="14">
+    <row r="90" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="10">
         <v>2038</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C90" s="9">
+      <c r="C90" s="8">
         <v>839</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
     </row>
-    <row r="91" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A91" s="6" t="s">
+    <row r="91" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A92" s="14">
+      <c r="E91" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F91" s="20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="10">
         <v>2017</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C92" s="15">
+      <c r="C92" s="11">
         <v>1440</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
     </row>
-    <row r="93" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A93" s="14">
+    <row r="93" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="10">
         <v>2019</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C93" s="15">
+      <c r="C93" s="11">
         <v>1440</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
     </row>
-    <row r="94" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A94" s="14">
+    <row r="94" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="10">
         <v>2021</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="B94" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C94" s="15">
+      <c r="C94" s="11">
         <v>1680</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
     </row>
-    <row r="95" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A95" s="14">
+    <row r="95" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="10">
         <v>2022</v>
       </c>
-      <c r="B95" s="8" t="s">
+      <c r="B95" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C95" s="15">
+      <c r="C95" s="11">
         <v>1680</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A96" s="14">
+    <row r="96" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="10">
         <v>2023</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="B96" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C96" s="15">
+      <c r="C96" s="11">
         <v>1680</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
     </row>
-    <row r="97" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A97" s="14">
+    <row r="97" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="10">
         <v>2024</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C97" s="15">
+      <c r="C97" s="11">
         <v>1800</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A98" s="14">
+    <row r="98" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="10">
         <v>2025</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C98" s="15">
+      <c r="C98" s="11">
         <v>2040</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A99" s="14">
+    <row r="99" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="10">
         <v>2029</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C99" s="9">
+      <c r="C99" s="8">
         <v>960</v>
       </c>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
     </row>
-    <row r="100" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A100" s="14">
+    <row r="100" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="10">
         <v>2031</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B100" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C100" s="15">
+      <c r="C100" s="11">
         <v>1440</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
     </row>
-    <row r="101" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A101" s="14">
+    <row r="101" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="10">
         <v>2034</v>
       </c>
-      <c r="B101" s="8" t="s">
+      <c r="B101" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C101" s="15">
+      <c r="C101" s="11">
         <v>1800</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
     </row>
-    <row r="102" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A102" s="14">
+    <row r="102" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="10">
         <v>2035</v>
       </c>
-      <c r="B102" s="8" t="s">
+      <c r="B102" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C102" s="15">
+      <c r="C102" s="11">
         <v>2160</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A103" s="14">
+    <row r="103" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="10">
         <v>2037</v>
       </c>
-      <c r="B103" s="8" t="s">
+      <c r="B103" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C103" s="15">
+      <c r="C103" s="11">
         <v>1413</v>
       </c>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
     </row>
-    <row r="104" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="14">
+    <row r="104" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="10">
         <v>2038</v>
       </c>
-      <c r="B104" s="8" t="s">
+      <c r="B104" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C104" s="15">
+      <c r="C104" s="11">
         <v>1024</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
     </row>
-    <row r="105" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A105" s="6" t="s">
+    <row r="105" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B105" s="6" t="s">
+      <c r="B105" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C105" s="6" t="s">
+      <c r="C105" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A106" s="16">
+      <c r="E105" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F105" s="20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="12">
         <v>5015</v>
       </c>
-      <c r="B106" s="8" t="s">
+      <c r="B106" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C106" s="15">
+      <c r="C106" s="11">
         <v>1173</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
     </row>
-    <row r="107" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A107" s="16">
+    <row r="107" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="12">
         <v>5017</v>
       </c>
-      <c r="B107" s="8" t="s">
+      <c r="B107" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C107" s="15">
+      <c r="C107" s="11">
         <v>1280</v>
       </c>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
     </row>
-    <row r="108" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A108" s="16">
+    <row r="108" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="12">
         <v>5019</v>
       </c>
-      <c r="B108" s="8" t="s">
+      <c r="B108" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C108" s="15">
+      <c r="C108" s="11">
         <v>1280</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
     </row>
-    <row r="109" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A109" s="16">
+    <row r="109" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="12">
         <v>5021</v>
       </c>
-      <c r="B109" s="8" t="s">
+      <c r="B109" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C109" s="15">
+      <c r="C109" s="11">
         <v>1493</v>
       </c>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
     </row>
-    <row r="110" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A110" s="16">
+    <row r="110" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="12">
         <v>5022</v>
       </c>
-      <c r="B110" s="8" t="s">
+      <c r="B110" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C110" s="15">
+      <c r="C110" s="11">
         <v>1493</v>
       </c>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
     </row>
-    <row r="111" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A111" s="16">
+    <row r="111" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="12">
         <v>5023</v>
       </c>
-      <c r="B111" s="8" t="s">
+      <c r="B111" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C111" s="15">
+      <c r="C111" s="11">
         <v>1493</v>
       </c>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
     </row>
-    <row r="112" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A112" s="16">
+    <row r="112" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="12">
         <v>5024</v>
       </c>
-      <c r="B112" s="8" t="s">
+      <c r="B112" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C112" s="15">
+      <c r="C112" s="11">
         <v>1600</v>
       </c>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
     </row>
-    <row r="113" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A113" s="16">
+    <row r="113" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="12">
         <v>5025</v>
       </c>
-      <c r="B113" s="8" t="s">
+      <c r="B113" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C113" s="15">
+      <c r="C113" s="11">
         <v>1814</v>
       </c>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
     </row>
-    <row r="114" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A114" s="16">
+    <row r="114" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="12">
         <v>5028</v>
       </c>
-      <c r="B114" s="8" t="s">
+      <c r="B114" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C114" s="15">
+      <c r="C114" s="11">
         <v>2100</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
     </row>
-    <row r="115" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A115" s="16">
+    <row r="115" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="12">
         <v>5029</v>
       </c>
-      <c r="B115" s="8" t="s">
+      <c r="B115" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C115" s="9">
+      <c r="C115" s="8">
         <v>864</v>
       </c>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
     </row>
-    <row r="116" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A116" s="16">
+    <row r="116" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="12">
         <v>5030</v>
       </c>
-      <c r="B116" s="8" t="s">
+      <c r="B116" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C116" s="15">
+      <c r="C116" s="11">
         <v>1280</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
     </row>
-    <row r="117" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A117" s="16">
+    <row r="117" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="12">
         <v>5031</v>
       </c>
-      <c r="B117" s="8" t="s">
+      <c r="B117" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C117" s="15">
+      <c r="C117" s="11">
         <v>1280</v>
       </c>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
     </row>
-    <row r="118" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A118" s="16">
+    <row r="118" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="12">
         <v>5032</v>
       </c>
-      <c r="B118" s="8" t="s">
+      <c r="B118" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C118" s="15">
+      <c r="C118" s="11">
         <v>1493</v>
       </c>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
     </row>
-    <row r="119" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A119" s="16">
+    <row r="119" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="12">
         <v>5033</v>
       </c>
-      <c r="B119" s="8" t="s">
+      <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C119" s="15">
+      <c r="C119" s="11">
         <v>1493</v>
       </c>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
     </row>
-    <row r="120" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A120" s="16">
+    <row r="120" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="12">
         <v>5034</v>
       </c>
-      <c r="B120" s="8" t="s">
+      <c r="B120" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C120" s="15">
+      <c r="C120" s="11">
         <v>1600</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
     </row>
-    <row r="121" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A121" s="16">
+    <row r="121" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="12">
         <v>5035</v>
       </c>
-      <c r="B121" s="8" t="s">
+      <c r="B121" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C121" s="15">
+      <c r="C121" s="11">
         <v>1920</v>
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
     </row>
-    <row r="122" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A122" s="16">
+    <row r="122" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="12">
         <v>5036</v>
       </c>
-      <c r="B122" s="8" t="s">
+      <c r="B122" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C122" s="15">
+      <c r="C122" s="11">
         <v>1056</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
     </row>
-    <row r="123" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A123" s="16">
+    <row r="123" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="12">
         <v>5037</v>
       </c>
-      <c r="B123" s="8" t="s">
+      <c r="B123" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C123" s="15">
+      <c r="C123" s="11">
         <v>1344</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
     </row>
-    <row r="124" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="16">
+    <row r="124" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="12">
         <v>5038</v>
       </c>
-      <c r="B124" s="8" t="s">
+      <c r="B124" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C124" s="9">
+      <c r="C124" s="8">
         <v>839</v>
       </c>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
     </row>
-    <row r="125" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A125" s="6" t="s">
+    <row r="125" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B125" s="6" t="s">
+      <c r="B125" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C125" s="6" t="s">
+      <c r="C125" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A126" s="17" t="s">
+      <c r="E125" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F125" s="20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B126" s="8" t="s">
+      <c r="B126" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C126" s="15">
+      <c r="C126" s="11">
         <v>2293</v>
       </c>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
     </row>
-    <row r="127" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A127" s="17" t="s">
+    <row r="127" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B127" s="8" t="s">
+      <c r="B127" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C127" s="15">
+      <c r="C127" s="11">
         <v>2800</v>
       </c>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
     </row>
-    <row r="128" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A128" s="17" t="s">
+    <row r="128" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B128" s="8" t="s">
+      <c r="B128" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C128" s="15">
+      <c r="C128" s="11">
         <v>2240</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
     </row>
-    <row r="129" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A129" s="17" t="s">
+    <row r="129" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B129" s="8" t="s">
+      <c r="B129" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C129" s="15">
+      <c r="C129" s="11">
         <v>1387</v>
       </c>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
     </row>
-    <row r="130" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A130" s="17" t="s">
+    <row r="130" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B130" s="8" t="s">
+      <c r="B130" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C130" s="15">
+      <c r="C130" s="11">
         <v>2560</v>
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
     </row>
-    <row r="131" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A131" s="17" t="s">
+    <row r="131" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B131" s="8" t="s">
+      <c r="B131" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C131" s="15">
+      <c r="C131" s="11">
         <v>1867</v>
       </c>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
     </row>
-    <row r="132" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A132" s="17" t="s">
+    <row r="132" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B132" s="8" t="s">
+      <c r="B132" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C132" s="15">
+      <c r="C132" s="11">
         <v>1280</v>
       </c>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
     </row>
-    <row r="133" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A133" s="17" t="s">
+    <row r="133" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B133" s="8" t="s">
+      <c r="B133" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C133" s="15">
+      <c r="C133" s="11">
         <v>1599</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
     </row>
-    <row r="134" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A134" s="17" t="s">
+    <row r="134" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B134" s="8" t="s">
+      <c r="B134" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C134" s="15">
+      <c r="C134" s="11">
         <v>1792</v>
       </c>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
     </row>
-    <row r="135" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A135" s="17" t="s">
+    <row r="135" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B135" s="8" t="s">
+      <c r="B135" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C135" s="15">
+      <c r="C135" s="11">
         <v>1980</v>
       </c>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
     </row>
-    <row r="136" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A136" s="17" t="s">
+    <row r="136" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B136" s="8" t="s">
+      <c r="B136" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C136" s="15">
+      <c r="C136" s="11">
         <v>1944</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
     </row>
-    <row r="137" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A137" s="6" t="s">
+    <row r="137" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A137" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B137" s="6" t="s">
+      <c r="B137" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C137" s="6" t="s">
+      <c r="C137" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A138" s="17" t="s">
+      <c r="E137" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F137" s="20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B138" s="18" t="s">
+      <c r="B138" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C138" s="15">
+      <c r="C138" s="11">
         <v>2100</v>
       </c>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
     </row>
-    <row r="139" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A139" s="17" t="s">
+    <row r="139" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B139" s="18" t="s">
+      <c r="B139" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C139" s="15">
+      <c r="C139" s="11">
         <v>1560</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
     </row>
-    <row r="140" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A140" s="17" t="s">
+    <row r="140" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B140" s="18" t="s">
+      <c r="B140" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="C140" s="15">
+      <c r="C140" s="11">
         <v>1800</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
     </row>
-    <row r="141" spans="1:6" ht="16" x14ac:dyDescent="0.4">
-      <c r="A141" s="19" t="s">
+    <row r="141" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A141" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="B141" s="19"/>
-      <c r="C141" s="19"/>
-    </row>
-    <row r="142" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A142" s="6" t="s">
+      <c r="B141" s="15"/>
+      <c r="C141" s="15"/>
+    </row>
+    <row r="142" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B142" s="6" t="s">
+      <c r="B142" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C142" s="6" t="s">
+      <c r="C142" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="8" t="s">
+      <c r="E142" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F142" s="20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A143" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B143" s="8" t="s">
+      <c r="B143" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C143" s="9">
+      <c r="C143" s="8">
         <v>533</v>
       </c>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
     </row>
-    <row r="144" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="8" t="s">
+    <row r="144" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B144" s="8" t="s">
+      <c r="B144" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C144" s="9">
+      <c r="C144" s="8">
         <v>640</v>
       </c>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
     </row>
-    <row r="145" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="8" t="s">
+    <row r="145" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B145" s="8" t="s">
+      <c r="B145" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C145" s="9">
+      <c r="C145" s="8">
         <v>800</v>
       </c>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
     </row>
-    <row r="146" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="8" t="s">
+    <row r="146" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B146" s="8" t="s">
+      <c r="B146" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C146" s="9">
+      <c r="C146" s="8">
         <v>880</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
     </row>
-    <row r="147" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A147" s="8" t="s">
+    <row r="147" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B147" s="8" t="s">
+      <c r="B147" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C147" s="9">
+      <c r="C147" s="8">
         <v>660</v>
       </c>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
     </row>
-    <row r="148" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A148" s="8" t="s">
+    <row r="148" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B148" s="8" t="s">
+      <c r="B148" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C148" s="9">
+      <c r="C148" s="8">
         <v>780</v>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
     </row>
-    <row r="149" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A149" s="8" t="s">
+    <row r="149" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B149" s="8" t="s">
+      <c r="B149" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C149" s="9">
+      <c r="C149" s="8">
         <v>840</v>
       </c>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
     </row>
-    <row r="150" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A150" s="8" t="s">
+    <row r="150" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="B150" s="8" t="s">
+      <c r="B150" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C150" s="9">
+      <c r="C150" s="8">
         <v>900</v>
       </c>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
     </row>
-    <row r="151" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A151" s="8" t="s">
+    <row r="151" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B151" s="8" t="s">
+      <c r="B151" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C151" s="9">
+      <c r="C151" s="8">
         <v>990</v>
       </c>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
     </row>
-    <row r="152" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A152" s="8" t="s">
+    <row r="152" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B152" s="8" t="s">
+      <c r="B152" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C152" s="9">
+      <c r="C152" s="8">
         <v>1080</v>
       </c>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
     </row>
-    <row r="153" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A153" s="8" t="s">
+    <row r="153" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B153" s="8" t="s">
+      <c r="B153" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C153" s="9">
+      <c r="C153" s="8">
         <v>1140</v>
       </c>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
     </row>
-    <row r="154" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A154" s="8" t="s">
+    <row r="154" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="B154" s="8" t="s">
+      <c r="B154" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C154" s="9">
+      <c r="C154" s="8">
         <v>1056</v>
       </c>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
     </row>
-    <row r="155" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A155" s="8" t="s">
+    <row r="155" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A155" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B155" s="8" t="s">
+      <c r="B155" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C155" s="9">
+      <c r="C155" s="8">
         <v>1152</v>
       </c>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
     </row>
-    <row r="156" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A156" s="8" t="s">
+    <row r="156" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B156" s="8" t="s">
+      <c r="B156" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C156" s="9">
+      <c r="C156" s="8">
         <v>1248</v>
       </c>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
     </row>
-    <row r="157" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="8" t="s">
+    <row r="157" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B157" s="8" t="s">
+      <c r="B157" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C157" s="9">
+      <c r="C157" s="8">
         <v>1176</v>
       </c>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
     </row>
-    <row r="158" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A158" s="8" t="s">
+    <row r="158" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="B158" s="8" t="s">
+      <c r="B158" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C158" s="9">
+      <c r="C158" s="8">
         <v>1344</v>
       </c>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
     </row>
-    <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="8" t="s">
+    <row r="159" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A159" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B159" s="8" t="s">
+      <c r="B159" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C159" s="9">
+      <c r="C159" s="8">
         <v>1272</v>
       </c>
       <c r="D159" s="1"/>
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
     </row>
-    <row r="160" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="8" t="s">
+    <row r="160" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="B160" s="8" t="s">
+      <c r="B160" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C160" s="9">
+      <c r="C160" s="8">
         <v>1067</v>
       </c>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
     </row>
-    <row r="161" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="8" t="s">
+    <row r="161" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A161" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="B161" s="8" t="s">
+      <c r="B161" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C161" s="9">
+      <c r="C161" s="8">
         <v>1173</v>
       </c>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
     </row>
-    <row r="162" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="8" t="s">
+    <row r="162" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A162" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="B162" s="8" t="s">
+      <c r="B162" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C162" s="9">
+      <c r="C162" s="8">
         <v>1280</v>
       </c>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
     </row>
-    <row r="163" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="8" t="s">
+    <row r="163" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B163" s="8" t="s">
+      <c r="B163" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C163" s="9">
+      <c r="C163" s="8">
         <v>1306</v>
       </c>
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
     </row>
-    <row r="164" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="8" t="s">
+    <row r="164" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B164" s="8" t="s">
+      <c r="B164" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C164" s="9">
+      <c r="C164" s="8">
         <v>1387</v>
       </c>
       <c r="D164" s="1"/>
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
     </row>
-    <row r="165" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="8" t="s">
+    <row r="165" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B165" s="8" t="s">
+      <c r="B165" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C165" s="9">
+      <c r="C165" s="8">
         <v>1493</v>
       </c>
       <c r="D165" s="1"/>
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
     </row>
-    <row r="166" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="8" t="s">
+    <row r="166" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B166" s="8" t="s">
+      <c r="B166" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C166" s="9">
+      <c r="C166" s="8">
         <v>1414</v>
       </c>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
     </row>
-    <row r="167" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="8" t="s">
+    <row r="167" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="B167" s="8" t="s">
+      <c r="B167" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C167" s="9">
+      <c r="C167" s="8">
         <v>1600</v>
       </c>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
     </row>
-    <row r="168" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="8" t="s">
+    <row r="168" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="B168" s="8" t="s">
+      <c r="B168" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C168" s="9">
+      <c r="C168" s="8">
         <v>1760</v>
       </c>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
     </row>
-    <row r="169" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="8" t="s">
+    <row r="169" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B169" s="8" t="s">
+      <c r="B169" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C169" s="9">
+      <c r="C169" s="8">
         <v>1920</v>
       </c>
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
     </row>
-    <row r="170" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A170" s="8" t="s">
+    <row r="170" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B170" s="8" t="s">
+      <c r="B170" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C170" s="9">
+      <c r="C170" s="8">
         <v>2052</v>
       </c>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
     </row>
-    <row r="171" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A171" s="8" t="s">
+    <row r="171" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B171" s="8" t="s">
+      <c r="B171" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C171" s="9">
+      <c r="C171" s="8">
         <v>1680</v>
       </c>
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
     </row>
-    <row r="172" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A172" s="8" t="s">
+    <row r="172" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B172" s="8" t="s">
+      <c r="B172" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C172" s="9">
+      <c r="C172" s="8">
         <v>1493</v>
       </c>
       <c r="D172" s="1"/>

--- a/docs/Homes List.xlsx
+++ b/docs/Homes List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9df306d6984b8b22/Documents/GitHub/Wix-Products/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="428" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C96B60A7-FCA9-4A52-9D89-565B36001513}"/>
+  <xr:revisionPtr revIDLastSave="435" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92435532-986C-472E-95B4-DB15893A9E29}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
+    <workbookView xWindow="5390" yWindow="2510" windowWidth="28800" windowHeight="15380" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1438,7 +1438,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1478,10 +1478,9 @@
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1494,9 +1493,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
@@ -1526,18 +1522,11 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
@@ -1550,11 +1539,7 @@
     <xf numFmtId="1" fontId="14" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1562,24 +1547,31 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1948,50 +1940,50 @@
   <dimension ref="A1:G174"/>
   <sheetFormatPr defaultRowHeight="19" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.90625" customWidth="1"/>
+    <col min="1" max="1" width="32.26953125" customWidth="1"/>
     <col min="2" max="2" width="4.26953125" customWidth="1"/>
-    <col min="3" max="3" width="2.54296875" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" customWidth="1"/>
     <col min="4" max="4" width="2.1796875" customWidth="1"/>
-    <col min="5" max="5" width="87.7265625" style="60" customWidth="1"/>
+    <col min="5" max="5" width="87.7265625" customWidth="1"/>
     <col min="6" max="6" width="70.453125" customWidth="1"/>
     <col min="7" max="7" width="11.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32"/>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="45" t="s">
+      <c r="A1" s="30"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="30" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="46" t="s">
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="30" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-    </row>
-    <row r="4" spans="1:7" s="16" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+    </row>
+    <row r="4" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>72</v>
       </c>
@@ -2001,14 +1993,14 @@
       <c r="C4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="47" t="s">
+      <c r="D4" s="30"/>
+      <c r="E4" s="15" t="s">
         <v>168</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2023,7 +2015,7 @@
         <v>409</v>
       </c>
       <c r="D5" s="13"/>
-      <c r="E5" s="48" t="s">
+      <c r="E5" s="41" t="s">
         <v>170</v>
       </c>
       <c r="F5" s="14" t="s">
@@ -2041,7 +2033,7 @@
         <v>540</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="49"/>
+      <c r="E6" s="42"/>
       <c r="F6" s="10" t="s">
         <v>214</v>
       </c>
@@ -2060,7 +2052,7 @@
         <v>648</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="49" t="s">
+      <c r="E7" s="42" t="s">
         <v>171</v>
       </c>
       <c r="F7" s="10" t="s">
@@ -2081,10 +2073,10 @@
         <v>702</v>
       </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="F8" s="38"/>
+      <c r="F8" s="34"/>
     </row>
     <row r="9" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
@@ -2097,10 +2089,10 @@
         <v>756</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="50" t="s">
+      <c r="E9" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="32" t="s">
         <v>217</v>
       </c>
     </row>
@@ -2115,10 +2107,10 @@
         <v>810</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="50" t="s">
+      <c r="E10" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="33" t="s">
         <v>209</v>
       </c>
     </row>
@@ -2133,10 +2125,10 @@
         <v>891</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="F11" s="36"/>
+      <c r="F11" s="32"/>
     </row>
     <row r="12" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
@@ -2149,10 +2141,10 @@
         <v>840</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="50" t="s">
+      <c r="E12" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="F12" s="36"/>
+      <c r="F12" s="32"/>
     </row>
     <row r="13" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
@@ -2165,10 +2157,10 @@
         <v>900</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="50" t="s">
+      <c r="E13" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="32" t="s">
         <v>218</v>
       </c>
     </row>
@@ -2183,10 +2175,10 @@
         <v>990</v>
       </c>
       <c r="D14" s="3"/>
-      <c r="E14" s="50" t="s">
+      <c r="E14" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="F14" s="36"/>
+      <c r="F14" s="32"/>
     </row>
     <row r="15" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
@@ -2199,10 +2191,10 @@
         <v>547</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="50" t="s">
+      <c r="E15" s="43" t="s">
         <v>169</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="32" t="s">
         <v>223</v>
       </c>
     </row>
@@ -2217,10 +2209,10 @@
         <v>800</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="50" t="s">
+      <c r="E16" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="F16" s="36"/>
+      <c r="F16" s="32"/>
     </row>
     <row r="17" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
@@ -2233,10 +2225,10 @@
         <v>944</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="50" t="s">
+      <c r="E17" s="43" t="s">
         <v>183</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="32" t="s">
         <v>219</v>
       </c>
     </row>
@@ -2251,10 +2243,10 @@
         <v>1101</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="50" t="s">
+      <c r="E18" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="F18" s="36"/>
+      <c r="F18" s="32"/>
     </row>
     <row r="19" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
@@ -2267,10 +2259,10 @@
         <v>864</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="50" t="s">
+      <c r="E19" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="F19" s="36"/>
+      <c r="F19" s="32"/>
     </row>
     <row r="20" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
@@ -2283,10 +2275,10 @@
         <v>900</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="50" t="s">
+      <c r="E20" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="F20" s="36" t="s">
+      <c r="F20" s="32" t="s">
         <v>220</v>
       </c>
     </row>
@@ -2301,10 +2293,10 @@
         <v>900</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="50" t="s">
+      <c r="E21" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="F21" s="36" t="s">
+      <c r="F21" s="32" t="s">
         <v>221</v>
       </c>
     </row>
@@ -2319,10 +2311,10 @@
         <v>1152</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="50" t="s">
+      <c r="E22" s="43" t="s">
         <v>188</v>
       </c>
-      <c r="F22" s="36"/>
+      <c r="F22" s="32"/>
     </row>
     <row r="23" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
@@ -2335,10 +2327,10 @@
         <v>1176</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="50" t="s">
+      <c r="E23" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="F23" s="36"/>
+      <c r="F23" s="32"/>
     </row>
     <row r="24" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
@@ -2351,10 +2343,10 @@
         <v>1188</v>
       </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="50" t="s">
+      <c r="E24" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="F24" s="37" t="s">
+      <c r="F24" s="33" t="s">
         <v>226</v>
       </c>
     </row>
@@ -2369,10 +2361,10 @@
         <v>1188</v>
       </c>
       <c r="D25" s="3"/>
-      <c r="E25" s="50" t="s">
+      <c r="E25" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="32" t="s">
         <v>225</v>
       </c>
     </row>
@@ -2387,10 +2379,10 @@
         <v>1296</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="50" t="s">
+      <c r="E26" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="F26" s="36" t="s">
+      <c r="F26" s="32" t="s">
         <v>215</v>
       </c>
     </row>
@@ -2405,10 +2397,10 @@
         <v>1296</v>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="50" t="s">
+      <c r="E27" s="43" t="s">
         <v>193</v>
       </c>
-      <c r="F27" s="37" t="s">
+      <c r="F27" s="33" t="s">
         <v>227</v>
       </c>
     </row>
@@ -2423,10 +2415,10 @@
         <v>1296</v>
       </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="50" t="s">
+      <c r="E28" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="32" t="s">
         <v>228</v>
       </c>
     </row>
@@ -2441,10 +2433,10 @@
         <v>1296</v>
       </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="50" t="s">
+      <c r="E29" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="F29" s="36" t="s">
+      <c r="F29" s="32" t="s">
         <v>229</v>
       </c>
     </row>
@@ -2459,10 +2451,10 @@
         <v>1296</v>
       </c>
       <c r="D30" s="3"/>
-      <c r="E30" s="50" t="s">
+      <c r="E30" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="F30" s="37" t="s">
+      <c r="F30" s="33" t="s">
         <v>230</v>
       </c>
     </row>
@@ -2477,10 +2469,10 @@
         <v>1404</v>
       </c>
       <c r="D31" s="3"/>
-      <c r="E31" s="50" t="s">
+      <c r="E31" s="43" t="s">
         <v>197</v>
       </c>
-      <c r="F31" s="36"/>
+      <c r="F31" s="32"/>
     </row>
     <row r="32" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
@@ -2493,10 +2485,10 @@
         <v>1512</v>
       </c>
       <c r="D32" s="3"/>
-      <c r="E32" s="50" t="s">
+      <c r="E32" s="43" t="s">
         <v>198</v>
       </c>
-      <c r="F32" s="36"/>
+      <c r="F32" s="32"/>
     </row>
     <row r="33" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
@@ -2509,10 +2501,10 @@
         <v>1512</v>
       </c>
       <c r="D33" s="3"/>
-      <c r="E33" s="50" t="s">
+      <c r="E33" s="43" t="s">
         <v>199</v>
       </c>
-      <c r="F33" s="36" t="s">
+      <c r="F33" s="32" t="s">
         <v>216</v>
       </c>
     </row>
@@ -2527,10 +2519,10 @@
         <v>1512</v>
       </c>
       <c r="D34" s="3"/>
-      <c r="E34" s="50" t="s">
+      <c r="E34" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="F34" s="36" t="s">
+      <c r="F34" s="32" t="s">
         <v>231</v>
       </c>
     </row>
@@ -2545,10 +2537,10 @@
         <v>1512</v>
       </c>
       <c r="D35" s="3"/>
-      <c r="E35" s="50" t="s">
+      <c r="E35" s="43" t="s">
         <v>201</v>
       </c>
-      <c r="F35" s="36"/>
+      <c r="F35" s="32"/>
     </row>
     <row r="36" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
@@ -2561,10 +2553,10 @@
         <v>1620</v>
       </c>
       <c r="D36" s="3"/>
-      <c r="E36" s="50" t="s">
+      <c r="E36" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="F36" s="37" t="s">
+      <c r="F36" s="33" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2579,10 +2571,10 @@
         <v>1836</v>
       </c>
       <c r="D37" s="3"/>
-      <c r="E37" s="50" t="s">
+      <c r="E37" s="43" t="s">
         <v>203</v>
       </c>
-      <c r="F37" s="36"/>
+      <c r="F37" s="32"/>
     </row>
     <row r="38" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
@@ -2595,32 +2587,32 @@
         <v>1836</v>
       </c>
       <c r="D38" s="3"/>
-      <c r="E38" s="50" t="s">
+      <c r="E38" s="43" t="s">
         <v>204</v>
       </c>
-      <c r="F38" s="36" t="s">
+      <c r="F38" s="32" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="19">
+      <c r="C39" s="18">
         <v>1917</v>
       </c>
-      <c r="D39" s="19"/>
-      <c r="E39" s="51" t="s">
+      <c r="D39" s="18"/>
+      <c r="E39" s="44" t="s">
         <v>205</v>
       </c>
-      <c r="F39" s="39" t="s">
+      <c r="F39" s="35" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:6" s="16" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="15" t="s">
         <v>72</v>
       </c>
@@ -2630,8 +2622,8 @@
       <c r="C40" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="34"/>
-      <c r="E40" s="47" t="s">
+      <c r="D40" s="30"/>
+      <c r="E40" s="15" t="s">
         <v>168</v>
       </c>
       <c r="F40" s="15" t="s">
@@ -2639,7 +2631,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="20" t="s">
         <v>38</v>
       </c>
       <c r="B41" s="12" t="s">
@@ -2649,10 +2641,10 @@
         <v>852</v>
       </c>
       <c r="D41" s="13"/>
-      <c r="E41" s="52" t="s">
+      <c r="E41" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="F41" s="35"/>
+      <c r="F41" s="31"/>
     </row>
     <row r="42" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
@@ -2665,8 +2657,8 @@
         <v>958</v>
       </c>
       <c r="D42" s="3"/>
-      <c r="E42" s="53"/>
-      <c r="F42" s="36"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
     </row>
     <row r="43" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
@@ -2679,8 +2671,8 @@
         <v>1026</v>
       </c>
       <c r="D43" s="3"/>
-      <c r="E43" s="53"/>
-      <c r="F43" s="37" t="s">
+      <c r="E43" s="32"/>
+      <c r="F43" s="33" t="s">
         <v>235</v>
       </c>
     </row>
@@ -2695,8 +2687,8 @@
         <v>1296</v>
       </c>
       <c r="D44" s="3"/>
-      <c r="E44" s="53"/>
-      <c r="F44" s="36"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
     </row>
     <row r="45" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
@@ -2709,8 +2701,8 @@
         <v>1296</v>
       </c>
       <c r="D45" s="3"/>
-      <c r="E45" s="53"/>
-      <c r="F45" s="36"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
     </row>
     <row r="46" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
@@ -2723,8 +2715,8 @@
         <v>1404</v>
       </c>
       <c r="D46" s="3"/>
-      <c r="E46" s="53"/>
-      <c r="F46" s="36" t="s">
+      <c r="E46" s="32"/>
+      <c r="F46" s="32" t="s">
         <v>236</v>
       </c>
     </row>
@@ -2739,8 +2731,8 @@
         <v>1404</v>
       </c>
       <c r="D47" s="3"/>
-      <c r="E47" s="53"/>
-      <c r="F47" s="36"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
     </row>
     <row r="48" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
@@ -2753,8 +2745,8 @@
         <v>1512</v>
       </c>
       <c r="D48" s="3"/>
-      <c r="E48" s="53"/>
-      <c r="F48" s="36" t="s">
+      <c r="E48" s="32"/>
+      <c r="F48" s="32" t="s">
         <v>237</v>
       </c>
     </row>
@@ -2769,8 +2761,8 @@
         <v>1512</v>
       </c>
       <c r="D49" s="3"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="36"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
     </row>
     <row r="50" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
@@ -2783,8 +2775,8 @@
         <v>1512</v>
       </c>
       <c r="D50" s="3"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="37" t="s">
+      <c r="E50" s="32"/>
+      <c r="F50" s="33" t="s">
         <v>238</v>
       </c>
     </row>
@@ -2799,8 +2791,8 @@
         <v>1512</v>
       </c>
       <c r="D51" s="3"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="36"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
     </row>
     <row r="52" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
@@ -2813,8 +2805,8 @@
         <v>1620</v>
       </c>
       <c r="D52" s="3"/>
-      <c r="E52" s="53"/>
-      <c r="F52" s="36"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
     </row>
     <row r="53" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
@@ -2827,8 +2819,8 @@
         <v>1782</v>
       </c>
       <c r="D53" s="3"/>
-      <c r="E53" s="53"/>
-      <c r="F53" s="36"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
     </row>
     <row r="54" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
@@ -2841,8 +2833,8 @@
         <v>1836</v>
       </c>
       <c r="D54" s="3"/>
-      <c r="E54" s="53"/>
-      <c r="F54" s="36" t="s">
+      <c r="E54" s="32"/>
+      <c r="F54" s="32" t="s">
         <v>239</v>
       </c>
     </row>
@@ -2857,8 +2849,8 @@
         <v>1836</v>
       </c>
       <c r="D55" s="3"/>
-      <c r="E55" s="53"/>
-      <c r="F55" s="36"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
     </row>
     <row r="56" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
@@ -2871,8 +2863,8 @@
         <v>2280</v>
       </c>
       <c r="D56" s="3"/>
-      <c r="E56" s="53"/>
-      <c r="F56" s="36"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
     </row>
     <row r="57" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
@@ -2885,8 +2877,8 @@
         <v>2280</v>
       </c>
       <c r="D57" s="3"/>
-      <c r="E57" s="53"/>
-      <c r="F57" s="36"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
     </row>
     <row r="58" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
@@ -2899,8 +2891,8 @@
         <v>2347</v>
       </c>
       <c r="D58" s="3"/>
-      <c r="E58" s="53"/>
-      <c r="F58" s="36"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
     </row>
     <row r="59" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
@@ -2913,8 +2905,8 @@
         <v>2347</v>
       </c>
       <c r="D59" s="3"/>
-      <c r="E59" s="53"/>
-      <c r="F59" s="36"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
     </row>
     <row r="60" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
@@ -2927,8 +2919,8 @@
         <v>2038</v>
       </c>
       <c r="D60" s="3"/>
-      <c r="E60" s="53"/>
-      <c r="F60" s="36" t="s">
+      <c r="E60" s="32"/>
+      <c r="F60" s="32" t="s">
         <v>240</v>
       </c>
     </row>
@@ -2943,20 +2935,20 @@
         <v>2654</v>
       </c>
       <c r="D61" s="3"/>
-      <c r="E61" s="53"/>
-      <c r="F61" s="36"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
     </row>
     <row r="62" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="22" t="s">
+      <c r="A62" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="B62" s="22"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-    </row>
-    <row r="63" spans="1:6" s="16" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="53"/>
+      <c r="C62" s="53"/>
+      <c r="D62" s="53"/>
+      <c r="E62" s="53"/>
+      <c r="F62" s="53"/>
+    </row>
+    <row r="63" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="15" t="s">
         <v>72</v>
       </c>
@@ -2966,8 +2958,8 @@
       <c r="C63" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D63" s="34"/>
-      <c r="E63" s="47" t="s">
+      <c r="D63" s="30"/>
+      <c r="E63" s="15" t="s">
         <v>168</v>
       </c>
       <c r="F63" s="15" t="s">
@@ -2975,7 +2967,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="23">
+      <c r="A64" s="21">
         <v>1001</v>
       </c>
       <c r="B64" s="12" t="s">
@@ -2985,10 +2977,10 @@
         <v>480</v>
       </c>
       <c r="D64" s="13"/>
-      <c r="E64" s="48" t="s">
+      <c r="E64" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="F64" s="35"/>
+      <c r="F64" s="31"/>
     </row>
     <row r="65" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
@@ -3001,10 +2993,10 @@
         <v>533</v>
       </c>
       <c r="D65" s="3"/>
-      <c r="E65" s="48" t="s">
+      <c r="E65" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="F65" s="36"/>
+      <c r="F65" s="32"/>
     </row>
     <row r="66" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
@@ -3017,10 +3009,10 @@
         <v>640</v>
       </c>
       <c r="D66" s="3"/>
-      <c r="E66" s="48" t="s">
+      <c r="E66" s="41" t="s">
         <v>242</v>
       </c>
-      <c r="F66" s="36"/>
+      <c r="F66" s="32"/>
     </row>
     <row r="67" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
@@ -3033,10 +3025,10 @@
         <v>746</v>
       </c>
       <c r="D67" s="3"/>
-      <c r="E67" s="48" t="s">
+      <c r="E67" s="41" t="s">
         <v>243</v>
       </c>
-      <c r="F67" s="36"/>
+      <c r="F67" s="32"/>
     </row>
     <row r="68" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
@@ -3049,10 +3041,10 @@
         <v>800</v>
       </c>
       <c r="D68" s="3"/>
-      <c r="E68" s="48" t="s">
+      <c r="E68" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="F68" s="36"/>
+      <c r="F68" s="32"/>
     </row>
     <row r="69" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
@@ -3065,10 +3057,10 @@
         <v>720</v>
       </c>
       <c r="D69" s="3"/>
-      <c r="E69" s="48" t="s">
+      <c r="E69" s="41" t="s">
         <v>245</v>
       </c>
-      <c r="F69" s="36"/>
+      <c r="F69" s="32"/>
     </row>
     <row r="70" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
@@ -3081,10 +3073,10 @@
         <v>840</v>
       </c>
       <c r="D70" s="3"/>
-      <c r="E70" s="48" t="s">
+      <c r="E70" s="41" t="s">
         <v>246</v>
       </c>
-      <c r="F70" s="36"/>
+      <c r="F70" s="32"/>
     </row>
     <row r="71" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
@@ -3097,10 +3089,10 @@
         <v>900</v>
       </c>
       <c r="D71" s="3"/>
-      <c r="E71" s="48" t="s">
+      <c r="E71" s="41" t="s">
         <v>247</v>
       </c>
-      <c r="F71" s="36"/>
+      <c r="F71" s="32"/>
     </row>
     <row r="72" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
@@ -3113,10 +3105,10 @@
         <v>990</v>
       </c>
       <c r="D72" s="3"/>
-      <c r="E72" s="48" t="s">
+      <c r="E72" s="41" t="s">
         <v>248</v>
       </c>
-      <c r="F72" s="36"/>
+      <c r="F72" s="32"/>
     </row>
     <row r="73" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
@@ -3129,10 +3121,10 @@
         <v>1080</v>
       </c>
       <c r="D73" s="6"/>
-      <c r="E73" s="48" t="s">
+      <c r="E73" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="F73" s="36"/>
+      <c r="F73" s="32"/>
     </row>
     <row r="74" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5">
@@ -3145,10 +3137,10 @@
         <v>1173</v>
       </c>
       <c r="D74" s="6"/>
-      <c r="E74" s="48" t="s">
+      <c r="E74" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="F74" s="36"/>
+      <c r="F74" s="32"/>
     </row>
     <row r="75" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5">
@@ -3161,10 +3153,10 @@
         <v>1280</v>
       </c>
       <c r="D75" s="6"/>
-      <c r="E75" s="48" t="s">
+      <c r="E75" s="41" t="s">
         <v>251</v>
       </c>
-      <c r="F75" s="36"/>
+      <c r="F75" s="32"/>
     </row>
     <row r="76" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
@@ -3177,10 +3169,10 @@
         <v>1280</v>
       </c>
       <c r="D76" s="6"/>
-      <c r="E76" s="48" t="s">
+      <c r="E76" s="41" t="s">
         <v>252</v>
       </c>
-      <c r="F76" s="36"/>
+      <c r="F76" s="32"/>
     </row>
     <row r="77" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
@@ -3193,10 +3185,10 @@
         <v>1493</v>
       </c>
       <c r="D77" s="6"/>
-      <c r="E77" s="48" t="s">
+      <c r="E77" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="F77" s="36"/>
+      <c r="F77" s="32"/>
     </row>
     <row r="78" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
@@ -3209,10 +3201,10 @@
         <v>1493</v>
       </c>
       <c r="D78" s="6"/>
-      <c r="E78" s="48" t="s">
+      <c r="E78" s="41" t="s">
         <v>254</v>
       </c>
-      <c r="F78" s="36"/>
+      <c r="F78" s="32"/>
     </row>
     <row r="79" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
@@ -3225,10 +3217,10 @@
         <v>1493</v>
       </c>
       <c r="D79" s="6"/>
-      <c r="E79" s="48" t="s">
+      <c r="E79" s="41" t="s">
         <v>255</v>
       </c>
-      <c r="F79" s="36"/>
+      <c r="F79" s="32"/>
     </row>
     <row r="80" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
@@ -3241,10 +3233,10 @@
         <v>1600</v>
       </c>
       <c r="D80" s="6"/>
-      <c r="E80" s="48" t="s">
+      <c r="E80" s="41" t="s">
         <v>256</v>
       </c>
-      <c r="F80" s="36"/>
+      <c r="F80" s="32"/>
     </row>
     <row r="81" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
@@ -3257,10 +3249,10 @@
         <v>1814</v>
       </c>
       <c r="D81" s="6"/>
-      <c r="E81" s="48" t="s">
+      <c r="E81" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="F81" s="36"/>
+      <c r="F81" s="32"/>
     </row>
     <row r="82" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
@@ -3273,10 +3265,10 @@
         <v>2100</v>
       </c>
       <c r="D82" s="6"/>
-      <c r="E82" s="48" t="s">
+      <c r="E82" s="41" t="s">
         <v>258</v>
       </c>
-      <c r="F82" s="36"/>
+      <c r="F82" s="32"/>
     </row>
     <row r="83" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
@@ -3289,10 +3281,10 @@
         <v>864</v>
       </c>
       <c r="D83" s="3"/>
-      <c r="E83" s="48" t="s">
+      <c r="E83" s="41" t="s">
         <v>259</v>
       </c>
-      <c r="F83" s="36"/>
+      <c r="F83" s="32"/>
     </row>
     <row r="84" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="5">
@@ -3305,10 +3297,10 @@
         <v>1280</v>
       </c>
       <c r="D84" s="6"/>
-      <c r="E84" s="48" t="s">
+      <c r="E84" s="41" t="s">
         <v>260</v>
       </c>
-      <c r="F84" s="36"/>
+      <c r="F84" s="32"/>
     </row>
     <row r="85" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
@@ -3321,10 +3313,10 @@
         <v>1280</v>
       </c>
       <c r="D85" s="6"/>
-      <c r="E85" s="48" t="s">
+      <c r="E85" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="F85" s="36"/>
+      <c r="F85" s="32"/>
     </row>
     <row r="86" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="5">
@@ -3337,10 +3329,10 @@
         <v>1493</v>
       </c>
       <c r="D86" s="6"/>
-      <c r="E86" s="48" t="s">
+      <c r="E86" s="41" t="s">
         <v>262</v>
       </c>
-      <c r="F86" s="36"/>
+      <c r="F86" s="32"/>
     </row>
     <row r="87" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
@@ -3353,10 +3345,10 @@
         <v>1493</v>
       </c>
       <c r="D87" s="6"/>
-      <c r="E87" s="48" t="s">
+      <c r="E87" s="41" t="s">
         <v>263</v>
       </c>
-      <c r="F87" s="36"/>
+      <c r="F87" s="32"/>
     </row>
     <row r="88" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="5">
@@ -3369,10 +3361,10 @@
         <v>1600</v>
       </c>
       <c r="D88" s="6"/>
-      <c r="E88" s="48" t="s">
+      <c r="E88" s="41" t="s">
         <v>264</v>
       </c>
-      <c r="F88" s="36"/>
+      <c r="F88" s="32"/>
     </row>
     <row r="89" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
@@ -3385,10 +3377,10 @@
         <v>1920</v>
       </c>
       <c r="D89" s="6"/>
-      <c r="E89" s="48" t="s">
+      <c r="E89" s="41" t="s">
         <v>265</v>
       </c>
-      <c r="F89" s="36"/>
+      <c r="F89" s="32"/>
     </row>
     <row r="90" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="5">
@@ -3401,10 +3393,10 @@
         <v>1056</v>
       </c>
       <c r="D90" s="6"/>
-      <c r="E90" s="48" t="s">
+      <c r="E90" s="41" t="s">
         <v>266</v>
       </c>
-      <c r="F90" s="36"/>
+      <c r="F90" s="32"/>
     </row>
     <row r="91" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
@@ -3417,28 +3409,28 @@
         <v>1344</v>
       </c>
       <c r="D91" s="6"/>
-      <c r="E91" s="48" t="s">
+      <c r="E91" s="41" t="s">
         <v>267</v>
       </c>
-      <c r="F91" s="36"/>
+      <c r="F91" s="32"/>
     </row>
     <row r="92" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="24">
+      <c r="A92" s="22">
         <v>2038</v>
       </c>
-      <c r="B92" s="18" t="s">
+      <c r="B92" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C92" s="19">
+      <c r="C92" s="18">
         <v>839</v>
       </c>
-      <c r="D92" s="19"/>
-      <c r="E92" s="48" t="s">
+      <c r="D92" s="18"/>
+      <c r="E92" s="41" t="s">
         <v>268</v>
       </c>
-      <c r="F92" s="39"/>
-    </row>
-    <row r="93" spans="1:6" s="16" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F92" s="35"/>
+    </row>
+    <row r="93" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="15" t="s">
         <v>72</v>
       </c>
@@ -3448,8 +3440,8 @@
       <c r="C93" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D93" s="34"/>
-      <c r="E93" s="47" t="s">
+      <c r="D93" s="30"/>
+      <c r="E93" s="15" t="s">
         <v>168</v>
       </c>
       <c r="F93" s="15" t="s">
@@ -3457,18 +3449,18 @@
       </c>
     </row>
     <row r="94" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="23">
+      <c r="A94" s="21">
         <v>2017</v>
       </c>
       <c r="B94" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C94" s="25">
+      <c r="C94" s="23">
         <v>1440</v>
       </c>
-      <c r="D94" s="25"/>
-      <c r="E94" s="54"/>
-      <c r="F94" s="35"/>
+      <c r="D94" s="23"/>
+      <c r="E94" s="46"/>
+      <c r="F94" s="31"/>
     </row>
     <row r="95" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
@@ -3481,8 +3473,8 @@
         <v>1440</v>
       </c>
       <c r="D95" s="6"/>
-      <c r="E95" s="55"/>
-      <c r="F95" s="36"/>
+      <c r="E95" s="47"/>
+      <c r="F95" s="32"/>
     </row>
     <row r="96" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="5">
@@ -3495,8 +3487,8 @@
         <v>1680</v>
       </c>
       <c r="D96" s="6"/>
-      <c r="E96" s="55"/>
-      <c r="F96" s="36"/>
+      <c r="E96" s="47"/>
+      <c r="F96" s="32"/>
     </row>
     <row r="97" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
@@ -3509,8 +3501,8 @@
         <v>1680</v>
       </c>
       <c r="D97" s="6"/>
-      <c r="E97" s="55"/>
-      <c r="F97" s="36"/>
+      <c r="E97" s="47"/>
+      <c r="F97" s="32"/>
     </row>
     <row r="98" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="5">
@@ -3523,8 +3515,8 @@
         <v>1680</v>
       </c>
       <c r="D98" s="6"/>
-      <c r="E98" s="55"/>
-      <c r="F98" s="36"/>
+      <c r="E98" s="47"/>
+      <c r="F98" s="32"/>
     </row>
     <row r="99" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
@@ -3537,8 +3529,8 @@
         <v>1800</v>
       </c>
       <c r="D99" s="6"/>
-      <c r="E99" s="55"/>
-      <c r="F99" s="36"/>
+      <c r="E99" s="47"/>
+      <c r="F99" s="32"/>
     </row>
     <row r="100" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
@@ -3551,8 +3543,8 @@
         <v>2040</v>
       </c>
       <c r="D100" s="6"/>
-      <c r="E100" s="55"/>
-      <c r="F100" s="36"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="32"/>
     </row>
     <row r="101" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
@@ -3565,8 +3557,8 @@
         <v>960</v>
       </c>
       <c r="D101" s="3"/>
-      <c r="E101" s="55"/>
-      <c r="F101" s="36"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="32"/>
     </row>
     <row r="102" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
@@ -3579,8 +3571,8 @@
         <v>1440</v>
       </c>
       <c r="D102" s="6"/>
-      <c r="E102" s="55"/>
-      <c r="F102" s="36"/>
+      <c r="E102" s="47"/>
+      <c r="F102" s="32"/>
     </row>
     <row r="103" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
@@ -3593,8 +3585,8 @@
         <v>1800</v>
       </c>
       <c r="D103" s="6"/>
-      <c r="E103" s="55"/>
-      <c r="F103" s="36"/>
+      <c r="E103" s="47"/>
+      <c r="F103" s="32"/>
     </row>
     <row r="104" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
@@ -3607,8 +3599,8 @@
         <v>2160</v>
       </c>
       <c r="D104" s="6"/>
-      <c r="E104" s="55"/>
-      <c r="F104" s="36"/>
+      <c r="E104" s="47"/>
+      <c r="F104" s="32"/>
     </row>
     <row r="105" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
@@ -3621,24 +3613,24 @@
         <v>1413</v>
       </c>
       <c r="D105" s="6"/>
-      <c r="E105" s="55"/>
-      <c r="F105" s="36"/>
+      <c r="E105" s="47"/>
+      <c r="F105" s="32"/>
     </row>
     <row r="106" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="24">
+      <c r="A106" s="22">
         <v>2038</v>
       </c>
-      <c r="B106" s="18" t="s">
+      <c r="B106" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C106" s="26">
+      <c r="C106" s="24">
         <v>1024</v>
       </c>
-      <c r="D106" s="26"/>
-      <c r="E106" s="56"/>
-      <c r="F106" s="39"/>
-    </row>
-    <row r="107" spans="1:6" s="16" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D106" s="24"/>
+      <c r="E106" s="48"/>
+      <c r="F106" s="35"/>
+    </row>
+    <row r="107" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="15" t="s">
         <v>72</v>
       </c>
@@ -3648,8 +3640,8 @@
       <c r="C107" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D107" s="34"/>
-      <c r="E107" s="47" t="s">
+      <c r="D107" s="30"/>
+      <c r="E107" s="15" t="s">
         <v>168</v>
       </c>
       <c r="F107" s="15" t="s">
@@ -3657,20 +3649,20 @@
       </c>
     </row>
     <row r="108" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="29">
+      <c r="A108" s="27">
         <v>5015</v>
       </c>
       <c r="B108" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C108" s="25">
+      <c r="C108" s="23">
         <v>1173</v>
       </c>
-      <c r="D108" s="25"/>
-      <c r="E108" s="57" t="s">
+      <c r="D108" s="23"/>
+      <c r="E108" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="F108" s="35"/>
+      <c r="F108" s="31"/>
     </row>
     <row r="109" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="7">
@@ -3683,10 +3675,10 @@
         <v>1280</v>
       </c>
       <c r="D109" s="6"/>
-      <c r="E109" s="41" t="s">
+      <c r="E109" s="36" t="s">
         <v>269</v>
       </c>
-      <c r="F109" s="36"/>
+      <c r="F109" s="32"/>
     </row>
     <row r="110" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="7">
@@ -3699,10 +3691,10 @@
         <v>1280</v>
       </c>
       <c r="D110" s="6"/>
-      <c r="E110" s="41" t="s">
+      <c r="E110" s="36" t="s">
         <v>270</v>
       </c>
-      <c r="F110" s="36"/>
+      <c r="F110" s="32"/>
     </row>
     <row r="111" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="7">
@@ -3715,10 +3707,10 @@
         <v>1493</v>
       </c>
       <c r="D111" s="6"/>
-      <c r="E111" s="41" t="s">
+      <c r="E111" s="36" t="s">
         <v>271</v>
       </c>
-      <c r="F111" s="36"/>
+      <c r="F111" s="32"/>
     </row>
     <row r="112" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="7">
@@ -3731,10 +3723,10 @@
         <v>1493</v>
       </c>
       <c r="D112" s="6"/>
-      <c r="E112" s="41" t="s">
+      <c r="E112" s="36" t="s">
         <v>272</v>
       </c>
-      <c r="F112" s="36"/>
+      <c r="F112" s="32"/>
     </row>
     <row r="113" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="7">
@@ -3747,10 +3739,10 @@
         <v>1493</v>
       </c>
       <c r="D113" s="6"/>
-      <c r="E113" s="41" t="s">
+      <c r="E113" s="36" t="s">
         <v>273</v>
       </c>
-      <c r="F113" s="36"/>
+      <c r="F113" s="32"/>
     </row>
     <row r="114" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="7">
@@ -3763,10 +3755,10 @@
         <v>1600</v>
       </c>
       <c r="D114" s="6"/>
-      <c r="E114" s="41" t="s">
+      <c r="E114" s="36" t="s">
         <v>274</v>
       </c>
-      <c r="F114" s="36"/>
+      <c r="F114" s="32"/>
     </row>
     <row r="115" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="7">
@@ -3779,10 +3771,10 @@
         <v>1814</v>
       </c>
       <c r="D115" s="6"/>
-      <c r="E115" s="41" t="s">
+      <c r="E115" s="36" t="s">
         <v>275</v>
       </c>
-      <c r="F115" s="36"/>
+      <c r="F115" s="32"/>
     </row>
     <row r="116" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="7">
@@ -3795,10 +3787,10 @@
         <v>2100</v>
       </c>
       <c r="D116" s="6"/>
-      <c r="E116" s="41" t="s">
+      <c r="E116" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="F116" s="36"/>
+      <c r="F116" s="32"/>
     </row>
     <row r="117" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="7">
@@ -3811,10 +3803,10 @@
         <v>864</v>
       </c>
       <c r="D117" s="3"/>
-      <c r="E117" s="41" t="s">
+      <c r="E117" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="F117" s="36"/>
+      <c r="F117" s="32"/>
     </row>
     <row r="118" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="7">
@@ -3827,10 +3819,10 @@
         <v>1280</v>
       </c>
       <c r="D118" s="6"/>
-      <c r="E118" s="41" t="s">
+      <c r="E118" s="36" t="s">
         <v>278</v>
       </c>
-      <c r="F118" s="36"/>
+      <c r="F118" s="32"/>
     </row>
     <row r="119" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="7">
@@ -3843,10 +3835,10 @@
         <v>1280</v>
       </c>
       <c r="D119" s="6"/>
-      <c r="E119" s="41" t="s">
+      <c r="E119" s="36" t="s">
         <v>279</v>
       </c>
-      <c r="F119" s="36"/>
+      <c r="F119" s="32"/>
     </row>
     <row r="120" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="7">
@@ -3859,10 +3851,10 @@
         <v>1493</v>
       </c>
       <c r="D120" s="6"/>
-      <c r="E120" s="41" t="s">
+      <c r="E120" s="36" t="s">
         <v>280</v>
       </c>
-      <c r="F120" s="36"/>
+      <c r="F120" s="32"/>
     </row>
     <row r="121" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="7">
@@ -3875,10 +3867,10 @@
         <v>1493</v>
       </c>
       <c r="D121" s="6"/>
-      <c r="E121" s="41" t="s">
+      <c r="E121" s="36" t="s">
         <v>281</v>
       </c>
-      <c r="F121" s="36"/>
+      <c r="F121" s="32"/>
     </row>
     <row r="122" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="7">
@@ -3891,10 +3883,10 @@
         <v>1600</v>
       </c>
       <c r="D122" s="6"/>
-      <c r="E122" s="41" t="s">
+      <c r="E122" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="F122" s="36"/>
+      <c r="F122" s="32"/>
     </row>
     <row r="123" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="7">
@@ -3907,10 +3899,10 @@
         <v>1920</v>
       </c>
       <c r="D123" s="6"/>
-      <c r="E123" s="41" t="s">
+      <c r="E123" s="36" t="s">
         <v>283</v>
       </c>
-      <c r="F123" s="36"/>
+      <c r="F123" s="32"/>
     </row>
     <row r="124" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="7">
@@ -3923,10 +3915,10 @@
         <v>1056</v>
       </c>
       <c r="D124" s="6"/>
-      <c r="E124" s="41" t="s">
+      <c r="E124" s="36" t="s">
         <v>284</v>
       </c>
-      <c r="F124" s="36"/>
+      <c r="F124" s="32"/>
     </row>
     <row r="125" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="7">
@@ -3939,30 +3931,30 @@
         <v>1344</v>
       </c>
       <c r="D125" s="6"/>
-      <c r="E125" s="41" t="s">
+      <c r="E125" s="36" t="s">
         <v>285</v>
       </c>
-      <c r="F125" s="36"/>
+      <c r="F125" s="32"/>
     </row>
     <row r="126" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="27">
+      <c r="A126" s="25">
         <v>5038</v>
       </c>
-      <c r="B126" s="18" t="s">
+      <c r="B126" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C126" s="19">
+      <c r="C126" s="18">
         <v>839</v>
       </c>
-      <c r="D126" s="19"/>
-      <c r="E126" s="58" t="s">
+      <c r="D126" s="18"/>
+      <c r="E126" s="50" t="s">
         <v>286</v>
       </c>
-      <c r="F126" s="20" t="s">
+      <c r="F126" s="19" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="127" spans="1:6" s="16" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="15" t="s">
         <v>72</v>
       </c>
@@ -3972,8 +3964,8 @@
       <c r="C127" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D127" s="34"/>
-      <c r="E127" s="47" t="s">
+      <c r="D127" s="30"/>
+      <c r="E127" s="15" t="s">
         <v>168</v>
       </c>
       <c r="F127" s="15" t="s">
@@ -3981,20 +3973,20 @@
       </c>
     </row>
     <row r="128" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="30" t="s">
+      <c r="A128" s="28" t="s">
         <v>60</v>
       </c>
       <c r="B128" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="C128" s="25">
+      <c r="C128" s="23">
         <v>2293</v>
       </c>
-      <c r="D128" s="25"/>
-      <c r="E128" s="54" t="s">
+      <c r="D128" s="23"/>
+      <c r="E128" s="46" t="s">
         <v>287</v>
       </c>
-      <c r="F128" s="35"/>
+      <c r="F128" s="31"/>
     </row>
     <row r="129" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="8" t="s">
@@ -4007,10 +3999,10 @@
         <v>2800</v>
       </c>
       <c r="D129" s="6"/>
-      <c r="E129" s="58" t="s">
+      <c r="E129" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="F129" s="36"/>
+      <c r="F129" s="32"/>
     </row>
     <row r="130" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="8" t="s">
@@ -4023,10 +4015,10 @@
         <v>2240</v>
       </c>
       <c r="D130" s="6"/>
-      <c r="E130" s="41" t="s">
+      <c r="E130" s="36" t="s">
         <v>289</v>
       </c>
-      <c r="F130" s="36"/>
+      <c r="F130" s="32"/>
     </row>
     <row r="131" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="8" t="s">
@@ -4039,10 +4031,10 @@
         <v>1387</v>
       </c>
       <c r="D131" s="6"/>
-      <c r="E131" s="41" t="s">
+      <c r="E131" s="36" t="s">
         <v>290</v>
       </c>
-      <c r="F131" s="36"/>
+      <c r="F131" s="32"/>
     </row>
     <row r="132" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="8" t="s">
@@ -4055,10 +4047,10 @@
         <v>2560</v>
       </c>
       <c r="D132" s="6"/>
-      <c r="E132" s="41" t="s">
+      <c r="E132" s="36" t="s">
         <v>291</v>
       </c>
-      <c r="F132" s="36"/>
+      <c r="F132" s="32"/>
     </row>
     <row r="133" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="8" t="s">
@@ -4071,10 +4063,10 @@
         <v>1867</v>
       </c>
       <c r="D133" s="6"/>
-      <c r="E133" s="41" t="s">
+      <c r="E133" s="36" t="s">
         <v>292</v>
       </c>
-      <c r="F133" s="36"/>
+      <c r="F133" s="32"/>
     </row>
     <row r="134" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="8" t="s">
@@ -4087,10 +4079,10 @@
         <v>1280</v>
       </c>
       <c r="D134" s="6"/>
-      <c r="E134" s="41" t="s">
+      <c r="E134" s="36" t="s">
         <v>293</v>
       </c>
-      <c r="F134" s="36"/>
+      <c r="F134" s="32"/>
     </row>
     <row r="135" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="8" t="s">
@@ -4103,10 +4095,10 @@
         <v>1599</v>
       </c>
       <c r="D135" s="6"/>
-      <c r="E135" s="41" t="s">
+      <c r="E135" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="F135" s="36"/>
+      <c r="F135" s="32"/>
     </row>
     <row r="136" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="8" t="s">
@@ -4119,10 +4111,10 @@
         <v>1792</v>
       </c>
       <c r="D136" s="6"/>
-      <c r="E136" s="41" t="s">
+      <c r="E136" s="36" t="s">
         <v>295</v>
       </c>
-      <c r="F136" s="36"/>
+      <c r="F136" s="32"/>
     </row>
     <row r="137" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="8" t="s">
@@ -4135,28 +4127,28 @@
         <v>1980</v>
       </c>
       <c r="D137" s="6"/>
-      <c r="E137" s="41" t="s">
+      <c r="E137" s="36" t="s">
         <v>296</v>
       </c>
-      <c r="F137" s="36"/>
+      <c r="F137" s="32"/>
     </row>
     <row r="138" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="28" t="s">
+      <c r="A138" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B138" s="18" t="s">
+      <c r="B138" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C138" s="26">
+      <c r="C138" s="24">
         <v>1944</v>
       </c>
-      <c r="D138" s="26"/>
-      <c r="E138" s="58" t="s">
+      <c r="D138" s="24"/>
+      <c r="E138" s="50" t="s">
         <v>297</v>
       </c>
-      <c r="F138" s="39"/>
-    </row>
-    <row r="139" spans="1:6" s="16" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F138" s="35"/>
+    </row>
+    <row r="139" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="15" t="s">
         <v>72</v>
       </c>
@@ -4166,8 +4158,8 @@
       <c r="C139" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D139" s="34"/>
-      <c r="E139" s="47" t="s">
+      <c r="D139" s="30"/>
+      <c r="E139" s="15" t="s">
         <v>168</v>
       </c>
       <c r="F139" s="15" t="s">
@@ -4175,18 +4167,18 @@
       </c>
     </row>
     <row r="140" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="30" t="s">
+      <c r="A140" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="B140" s="31" t="s">
+      <c r="B140" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="C140" s="25">
+      <c r="C140" s="23">
         <v>2100</v>
       </c>
-      <c r="D140" s="25"/>
-      <c r="E140" s="59"/>
-      <c r="F140" s="35"/>
+      <c r="D140" s="23"/>
+      <c r="E140" s="51"/>
+      <c r="F140" s="31"/>
     </row>
     <row r="141" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="8" t="s">
@@ -4199,8 +4191,8 @@
         <v>1560</v>
       </c>
       <c r="D141" s="6"/>
-      <c r="E141" s="55"/>
-      <c r="F141" s="36"/>
+      <c r="E141" s="47"/>
+      <c r="F141" s="32"/>
     </row>
     <row r="142" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="8" t="s">
@@ -4213,20 +4205,20 @@
         <v>1800</v>
       </c>
       <c r="D142" s="6"/>
-      <c r="E142" s="55"/>
-      <c r="F142" s="36"/>
+      <c r="E142" s="47"/>
+      <c r="F142" s="32"/>
     </row>
     <row r="143" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="40" t="s">
+      <c r="A143" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="B143" s="40"/>
-      <c r="C143" s="40"/>
-      <c r="D143" s="40"/>
-      <c r="E143" s="40"/>
-      <c r="F143" s="40"/>
-    </row>
-    <row r="144" spans="1:6" s="16" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B143" s="54"/>
+      <c r="C143" s="54"/>
+      <c r="D143" s="54"/>
+      <c r="E143" s="54"/>
+      <c r="F143" s="54"/>
+    </row>
+    <row r="144" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="15" t="s">
         <v>72</v>
       </c>
@@ -4236,8 +4228,8 @@
       <c r="C144" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D144" s="34"/>
-      <c r="E144" s="47" t="s">
+      <c r="D144" s="30"/>
+      <c r="E144" s="15" t="s">
         <v>168</v>
       </c>
       <c r="F144" s="15" t="s">
@@ -4255,8 +4247,8 @@
         <v>533</v>
       </c>
       <c r="D145" s="13"/>
-      <c r="E145" s="59"/>
-      <c r="F145" s="42" t="s">
+      <c r="E145" s="51"/>
+      <c r="F145" s="37" t="s">
         <v>298</v>
       </c>
     </row>
@@ -4271,8 +4263,8 @@
         <v>640</v>
       </c>
       <c r="D146" s="3"/>
-      <c r="E146" s="55"/>
-      <c r="F146" s="43"/>
+      <c r="E146" s="47"/>
+      <c r="F146" s="38"/>
     </row>
     <row r="147" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
@@ -4285,8 +4277,8 @@
         <v>800</v>
       </c>
       <c r="D147" s="3"/>
-      <c r="E147" s="55"/>
-      <c r="F147" s="43" t="s">
+      <c r="E147" s="47"/>
+      <c r="F147" s="38" t="s">
         <v>306</v>
       </c>
     </row>
@@ -4301,8 +4293,8 @@
         <v>880</v>
       </c>
       <c r="D148" s="3"/>
-      <c r="E148" s="55"/>
-      <c r="F148" s="43" t="s">
+      <c r="E148" s="47"/>
+      <c r="F148" s="38" t="s">
         <v>301</v>
       </c>
     </row>
@@ -4317,8 +4309,8 @@
         <v>660</v>
       </c>
       <c r="D149" s="3"/>
-      <c r="E149" s="55"/>
-      <c r="F149" s="43" t="s">
+      <c r="E149" s="47"/>
+      <c r="F149" s="38" t="s">
         <v>320</v>
       </c>
     </row>
@@ -4333,8 +4325,8 @@
         <v>780</v>
       </c>
       <c r="D150" s="3"/>
-      <c r="E150" s="55"/>
-      <c r="F150" s="43"/>
+      <c r="E150" s="47"/>
+      <c r="F150" s="38"/>
     </row>
     <row r="151" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
@@ -4347,8 +4339,8 @@
         <v>840</v>
       </c>
       <c r="D151" s="3"/>
-      <c r="E151" s="55"/>
-      <c r="F151" s="43" t="s">
+      <c r="E151" s="47"/>
+      <c r="F151" s="38" t="s">
         <v>318</v>
       </c>
     </row>
@@ -4363,8 +4355,8 @@
         <v>900</v>
       </c>
       <c r="D152" s="3"/>
-      <c r="E152" s="55"/>
-      <c r="F152" s="43" t="s">
+      <c r="E152" s="47"/>
+      <c r="F152" s="38" t="s">
         <v>313</v>
       </c>
     </row>
@@ -4379,8 +4371,8 @@
         <v>990</v>
       </c>
       <c r="D153" s="3"/>
-      <c r="E153" s="55"/>
-      <c r="F153" s="43" t="s">
+      <c r="E153" s="47"/>
+      <c r="F153" s="38" t="s">
         <v>307</v>
       </c>
     </row>
@@ -4395,8 +4387,8 @@
         <v>1080</v>
       </c>
       <c r="D154" s="3"/>
-      <c r="E154" s="55"/>
-      <c r="F154" s="44" t="s">
+      <c r="E154" s="47"/>
+      <c r="F154" s="39" t="s">
         <v>321</v>
       </c>
     </row>
@@ -4411,8 +4403,8 @@
         <v>1140</v>
       </c>
       <c r="D155" s="3"/>
-      <c r="E155" s="55"/>
-      <c r="F155" s="43" t="s">
+      <c r="E155" s="47"/>
+      <c r="F155" s="38" t="s">
         <v>308</v>
       </c>
     </row>
@@ -4427,8 +4419,8 @@
         <v>1056</v>
       </c>
       <c r="D156" s="3"/>
-      <c r="E156" s="55"/>
-      <c r="F156" s="43" t="s">
+      <c r="E156" s="47"/>
+      <c r="F156" s="38" t="s">
         <v>309</v>
       </c>
     </row>
@@ -4443,8 +4435,8 @@
         <v>1152</v>
       </c>
       <c r="D157" s="3"/>
-      <c r="E157" s="55"/>
-      <c r="F157" s="43" t="s">
+      <c r="E157" s="47"/>
+      <c r="F157" s="38" t="s">
         <v>319</v>
       </c>
     </row>
@@ -4459,8 +4451,8 @@
         <v>1248</v>
       </c>
       <c r="D158" s="3"/>
-      <c r="E158" s="55"/>
-      <c r="F158" s="43" t="s">
+      <c r="E158" s="47"/>
+      <c r="F158" s="38" t="s">
         <v>310</v>
       </c>
     </row>
@@ -4475,8 +4467,8 @@
         <v>1176</v>
       </c>
       <c r="D159" s="3"/>
-      <c r="E159" s="55"/>
-      <c r="F159" s="43"/>
+      <c r="E159" s="47"/>
+      <c r="F159" s="38"/>
     </row>
     <row r="160" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
@@ -4489,8 +4481,8 @@
         <v>1344</v>
       </c>
       <c r="D160" s="3"/>
-      <c r="E160" s="55"/>
-      <c r="F160" s="43" t="s">
+      <c r="E160" s="47"/>
+      <c r="F160" s="38" t="s">
         <v>317</v>
       </c>
     </row>
@@ -4505,8 +4497,8 @@
         <v>1272</v>
       </c>
       <c r="D161" s="3"/>
-      <c r="E161" s="55"/>
-      <c r="F161" s="32" t="s">
+      <c r="E161" s="47"/>
+      <c r="F161" s="30" t="s">
         <v>300</v>
       </c>
     </row>
@@ -4521,8 +4513,8 @@
         <v>1067</v>
       </c>
       <c r="D162" s="3"/>
-      <c r="E162" s="55"/>
-      <c r="F162" s="43"/>
+      <c r="E162" s="47"/>
+      <c r="F162" s="38"/>
     </row>
     <row r="163" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
@@ -4535,8 +4527,8 @@
         <v>1173</v>
       </c>
       <c r="D163" s="3"/>
-      <c r="E163" s="55"/>
-      <c r="F163" s="44" t="s">
+      <c r="E163" s="47"/>
+      <c r="F163" s="39" t="s">
         <v>302</v>
       </c>
     </row>
@@ -4551,8 +4543,8 @@
         <v>1280</v>
       </c>
       <c r="D164" s="3"/>
-      <c r="E164" s="55"/>
-      <c r="F164" s="44" t="s">
+      <c r="E164" s="47"/>
+      <c r="F164" s="39" t="s">
         <v>303</v>
       </c>
     </row>
@@ -4567,8 +4559,8 @@
         <v>1306</v>
       </c>
       <c r="D165" s="3"/>
-      <c r="E165" s="55"/>
-      <c r="F165" s="43" t="s">
+      <c r="E165" s="47"/>
+      <c r="F165" s="38" t="s">
         <v>312</v>
       </c>
     </row>
@@ -4583,8 +4575,8 @@
         <v>1387</v>
       </c>
       <c r="D166" s="3"/>
-      <c r="E166" s="55"/>
-      <c r="F166" s="43"/>
+      <c r="E166" s="47"/>
+      <c r="F166" s="38"/>
     </row>
     <row r="167" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
@@ -4597,8 +4589,8 @@
         <v>1493</v>
       </c>
       <c r="D167" s="3"/>
-      <c r="E167" s="55"/>
-      <c r="F167" s="43" t="s">
+      <c r="E167" s="47"/>
+      <c r="F167" s="38" t="s">
         <v>305</v>
       </c>
     </row>
@@ -4613,8 +4605,8 @@
         <v>1414</v>
       </c>
       <c r="D168" s="3"/>
-      <c r="E168" s="55"/>
-      <c r="F168" s="43" t="s">
+      <c r="E168" s="47"/>
+      <c r="F168" s="38" t="s">
         <v>315</v>
       </c>
     </row>
@@ -4629,8 +4621,8 @@
         <v>1600</v>
       </c>
       <c r="D169" s="3"/>
-      <c r="E169" s="55"/>
-      <c r="F169" s="44" t="s">
+      <c r="E169" s="47"/>
+      <c r="F169" s="39" t="s">
         <v>314</v>
       </c>
     </row>
@@ -4645,8 +4637,8 @@
         <v>1760</v>
       </c>
       <c r="D170" s="3"/>
-      <c r="E170" s="55"/>
-      <c r="F170" s="44" t="s">
+      <c r="E170" s="47"/>
+      <c r="F170" s="39" t="s">
         <v>304</v>
       </c>
     </row>
@@ -4661,8 +4653,8 @@
         <v>1920</v>
       </c>
       <c r="D171" s="3"/>
-      <c r="E171" s="55"/>
-      <c r="F171" s="43" t="s">
+      <c r="E171" s="47"/>
+      <c r="F171" s="38" t="s">
         <v>311</v>
       </c>
     </row>
@@ -4677,8 +4669,8 @@
         <v>2052</v>
       </c>
       <c r="D172" s="3"/>
-      <c r="E172" s="55"/>
-      <c r="F172" s="43"/>
+      <c r="E172" s="47"/>
+      <c r="F172" s="38"/>
     </row>
     <row r="173" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
@@ -4691,8 +4683,8 @@
         <v>1680</v>
       </c>
       <c r="D173" s="3"/>
-      <c r="E173" s="55"/>
-      <c r="F173" s="43" t="s">
+      <c r="E173" s="47"/>
+      <c r="F173" s="38" t="s">
         <v>299</v>
       </c>
     </row>
@@ -4707,8 +4699,8 @@
         <v>1493</v>
       </c>
       <c r="D174" s="3"/>
-      <c r="E174" s="55"/>
-      <c r="F174" s="43"/>
+      <c r="E174" s="47"/>
+      <c r="F174" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/docs/Homes List.xlsx
+++ b/docs/Homes List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9df306d6984b8b22/Documents/GitHub/Wix-Products/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="435" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92435532-986C-472E-95B4-DB15893A9E29}"/>
+  <xr:revisionPtr revIDLastSave="464" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94028A43-9042-4354-99F1-2C2527B85336}"/>
   <bookViews>
-    <workbookView xWindow="5390" yWindow="2510" windowWidth="28800" windowHeight="15380" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="333">
   <si>
     <t xml:space="preserve">Golden West </t>
   </si>
@@ -1203,6 +1203,36 @@
   </si>
   <si>
     <t>https://momento360.com/e/uc/bf08fdeb310d4a1996f01686e98407b6</t>
+  </si>
+  <si>
+    <t>360 Tour / Materport</t>
+  </si>
+  <si>
+    <t>https://my.matterport.com/show/?play=1&amp;m=MgaR4onYsZB</t>
+  </si>
+  <si>
+    <t>https://my.matterport.com/show/?play=1&amp;m=fKycYYa7n6n</t>
+  </si>
+  <si>
+    <t>https://my.matterport.com/show?play=1&amp;lang=en-US&amp;m=DaQBmJEBKY6</t>
+  </si>
+  <si>
+    <t>https://my.matterport.com/show/?play=1&amp;m=iUG3qkNrKfa</t>
+  </si>
+  <si>
+    <t>https://my.matterport.com/show/?play=1&amp;m=QkyD1Gqr67p</t>
+  </si>
+  <si>
+    <t>https://my.matterport.com/show/?m=o6SZeYvAzTd</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Imagine.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Satisfaction.pdf</t>
+  </si>
+  <si>
+    <t>https://my.matterport.com/show?play=1&amp;lang=en-US&amp;m=FgFZPzopwY2</t>
   </si>
 </sst>
 </file>
@@ -1438,7 +1468,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1566,11 +1596,30 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1937,19 +1986,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69257E43-B717-415B-87B6-EDDB262DB689}">
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr defaultRowHeight="19" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.26953125" customWidth="1"/>
     <col min="2" max="2" width="4.26953125" customWidth="1"/>
     <col min="3" max="3" width="9.90625" customWidth="1"/>
     <col min="4" max="4" width="2.1796875" customWidth="1"/>
-    <col min="5" max="5" width="87.7265625" customWidth="1"/>
+    <col min="5" max="5" width="93.81640625" customWidth="1"/>
     <col min="6" max="6" width="70.453125" customWidth="1"/>
-    <col min="7" max="7" width="11.26953125" customWidth="1"/>
+    <col min="7" max="7" width="52.90625" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="30"/>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -1960,8 +2010,9 @@
       <c r="F1" s="30" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G1" s="30"/>
+    </row>
+    <row r="2" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="30"/>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -1972,18 +2023,20 @@
       <c r="F2" s="30" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="52" t="s">
+      <c r="G2" s="30"/>
+    </row>
+    <row r="3" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-    </row>
-    <row r="4" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="52"/>
+    </row>
+    <row r="4" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>72</v>
       </c>
@@ -2000,11 +2053,14 @@
       <c r="F4" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="H4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
         <v>3</v>
       </c>
@@ -2021,8 +2077,9 @@
       <c r="F5" s="14" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G5" s="56"/>
+    </row>
+    <row r="6" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -2037,11 +2094,12 @@
       <c r="F6" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="56"/>
+      <c r="H6" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -2058,11 +2116,12 @@
       <c r="F7" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="56"/>
+      <c r="H7" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -2077,8 +2136,9 @@
         <v>175</v>
       </c>
       <c r="F8" s="34"/>
-    </row>
-    <row r="9" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G8" s="57"/>
+    </row>
+    <row r="9" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -2095,8 +2155,9 @@
       <c r="F9" s="32" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G9" s="58"/>
+    </row>
+    <row r="10" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -2113,8 +2174,9 @@
       <c r="F10" s="33" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G10" s="59"/>
+    </row>
+    <row r="11" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -2129,8 +2191,9 @@
         <v>178</v>
       </c>
       <c r="F11" s="32"/>
-    </row>
-    <row r="12" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G11" s="58"/>
+    </row>
+    <row r="12" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -2145,8 +2208,9 @@
         <v>179</v>
       </c>
       <c r="F12" s="32"/>
-    </row>
-    <row r="13" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G12" s="58"/>
+    </row>
+    <row r="13" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -2163,8 +2227,9 @@
       <c r="F13" s="32" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G13" s="58"/>
+    </row>
+    <row r="14" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -2179,8 +2244,9 @@
         <v>181</v>
       </c>
       <c r="F14" s="32"/>
-    </row>
-    <row r="15" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G14" s="58"/>
+    </row>
+    <row r="15" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -2197,8 +2263,9 @@
       <c r="F15" s="32" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G15" s="58"/>
+    </row>
+    <row r="16" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -2213,8 +2280,9 @@
         <v>182</v>
       </c>
       <c r="F16" s="32"/>
-    </row>
-    <row r="17" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G16" s="58"/>
+    </row>
+    <row r="17" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -2231,8 +2299,9 @@
       <c r="F17" s="32" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G17" s="58"/>
+    </row>
+    <row r="18" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -2247,8 +2316,9 @@
         <v>184</v>
       </c>
       <c r="F18" s="32"/>
-    </row>
-    <row r="19" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G18" s="58"/>
+    </row>
+    <row r="19" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -2263,8 +2333,9 @@
         <v>185</v>
       </c>
       <c r="F19" s="32"/>
-    </row>
-    <row r="20" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G19" s="58"/>
+    </row>
+    <row r="20" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -2281,8 +2352,9 @@
       <c r="F20" s="32" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G20" s="58"/>
+    </row>
+    <row r="21" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -2299,8 +2371,9 @@
       <c r="F21" s="32" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G21" s="58"/>
+    </row>
+    <row r="22" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -2315,8 +2388,9 @@
         <v>188</v>
       </c>
       <c r="F22" s="32"/>
-    </row>
-    <row r="23" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G22" s="58"/>
+    </row>
+    <row r="23" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -2331,8 +2405,9 @@
         <v>189</v>
       </c>
       <c r="F23" s="32"/>
-    </row>
-    <row r="24" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G23" s="58"/>
+    </row>
+    <row r="24" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -2349,8 +2424,9 @@
       <c r="F24" s="33" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G24" s="59"/>
+    </row>
+    <row r="25" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -2367,8 +2443,9 @@
       <c r="F25" s="32" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G25" s="58"/>
+    </row>
+    <row r="26" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -2385,8 +2462,9 @@
       <c r="F26" s="32" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G26" s="58"/>
+    </row>
+    <row r="27" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -2403,8 +2481,9 @@
       <c r="F27" s="33" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G27" s="59"/>
+    </row>
+    <row r="28" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
@@ -2421,8 +2500,9 @@
       <c r="F28" s="32" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G28" s="58"/>
+    </row>
+    <row r="29" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -2439,8 +2519,9 @@
       <c r="F29" s="32" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G29" s="58"/>
+    </row>
+    <row r="30" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
@@ -2457,8 +2538,9 @@
       <c r="F30" s="33" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G30" s="59"/>
+    </row>
+    <row r="31" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -2473,8 +2555,9 @@
         <v>197</v>
       </c>
       <c r="F31" s="32"/>
-    </row>
-    <row r="32" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G31" s="58"/>
+    </row>
+    <row r="32" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
@@ -2489,8 +2572,9 @@
         <v>198</v>
       </c>
       <c r="F32" s="32"/>
-    </row>
-    <row r="33" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G32" s="58"/>
+    </row>
+    <row r="33" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
@@ -2507,8 +2591,9 @@
       <c r="F33" s="32" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G33" s="58"/>
+    </row>
+    <row r="34" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
@@ -2525,8 +2610,9 @@
       <c r="F34" s="32" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G34" s="58"/>
+    </row>
+    <row r="35" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
@@ -2541,8 +2627,9 @@
         <v>201</v>
       </c>
       <c r="F35" s="32"/>
-    </row>
-    <row r="36" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G35" s="58"/>
+    </row>
+    <row r="36" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
@@ -2559,8 +2646,9 @@
       <c r="F36" s="33" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G36" s="59"/>
+    </row>
+    <row r="37" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
@@ -2575,8 +2663,9 @@
         <v>203</v>
       </c>
       <c r="F37" s="32"/>
-    </row>
-    <row r="38" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G37" s="58"/>
+    </row>
+    <row r="38" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -2593,8 +2682,9 @@
       <c r="F38" s="32" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G38" s="58"/>
+    </row>
+    <row r="39" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="16" t="s">
         <v>37</v>
       </c>
@@ -2611,8 +2701,9 @@
       <c r="F39" s="35" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G39" s="58"/>
+    </row>
+    <row r="40" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="15" t="s">
         <v>72</v>
       </c>
@@ -2629,8 +2720,11 @@
       <c r="F40" s="15" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G40" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="20" t="s">
         <v>38</v>
       </c>
@@ -2645,8 +2739,11 @@
         <v>206</v>
       </c>
       <c r="F41" s="31"/>
-    </row>
-    <row r="42" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G41" s="58" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>39</v>
       </c>
@@ -2659,8 +2756,9 @@
       <c r="D42" s="3"/>
       <c r="E42" s="32"/>
       <c r="F42" s="32"/>
-    </row>
-    <row r="43" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G42" s="58"/>
+    </row>
+    <row r="43" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>40</v>
       </c>
@@ -2675,8 +2773,11 @@
       <c r="F43" s="33" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G43" s="56" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>41</v>
       </c>
@@ -2689,8 +2790,9 @@
       <c r="D44" s="3"/>
       <c r="E44" s="32"/>
       <c r="F44" s="32"/>
-    </row>
-    <row r="45" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G44" s="58"/>
+    </row>
+    <row r="45" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>42</v>
       </c>
@@ -2703,8 +2805,11 @@
       <c r="D45" s="3"/>
       <c r="E45" s="32"/>
       <c r="F45" s="32"/>
-    </row>
-    <row r="46" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G45" s="58" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>43</v>
       </c>
@@ -2719,8 +2824,9 @@
       <c r="F46" s="32" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G46" s="58"/>
+    </row>
+    <row r="47" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>44</v>
       </c>
@@ -2733,8 +2839,9 @@
       <c r="D47" s="3"/>
       <c r="E47" s="32"/>
       <c r="F47" s="32"/>
-    </row>
-    <row r="48" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G47" s="58"/>
+    </row>
+    <row r="48" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>45</v>
       </c>
@@ -2749,8 +2856,11 @@
       <c r="F48" s="32" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G48" s="58" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>46</v>
       </c>
@@ -2763,8 +2873,9 @@
       <c r="D49" s="3"/>
       <c r="E49" s="32"/>
       <c r="F49" s="32"/>
-    </row>
-    <row r="50" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G49" s="58"/>
+    </row>
+    <row r="50" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>47</v>
       </c>
@@ -2779,8 +2890,9 @@
       <c r="F50" s="33" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G50" s="59"/>
+    </row>
+    <row r="51" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>48</v>
       </c>
@@ -2793,8 +2905,9 @@
       <c r="D51" s="3"/>
       <c r="E51" s="32"/>
       <c r="F51" s="32"/>
-    </row>
-    <row r="52" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G51" s="58"/>
+    </row>
+    <row r="52" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>49</v>
       </c>
@@ -2807,8 +2920,11 @@
       <c r="D52" s="3"/>
       <c r="E52" s="32"/>
       <c r="F52" s="32"/>
-    </row>
-    <row r="53" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G52" s="56" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>50</v>
       </c>
@@ -2821,8 +2937,9 @@
       <c r="D53" s="3"/>
       <c r="E53" s="32"/>
       <c r="F53" s="32"/>
-    </row>
-    <row r="54" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G53" s="58"/>
+    </row>
+    <row r="54" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>51</v>
       </c>
@@ -2837,8 +2954,9 @@
       <c r="F54" s="32" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G54" s="58"/>
+    </row>
+    <row r="55" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>52</v>
       </c>
@@ -2851,8 +2969,9 @@
       <c r="D55" s="3"/>
       <c r="E55" s="32"/>
       <c r="F55" s="32"/>
-    </row>
-    <row r="56" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G55" s="58"/>
+    </row>
+    <row r="56" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>53</v>
       </c>
@@ -2865,8 +2984,11 @@
       <c r="D56" s="3"/>
       <c r="E56" s="32"/>
       <c r="F56" s="32"/>
-    </row>
-    <row r="57" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G56" s="58" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>54</v>
       </c>
@@ -2879,8 +3001,9 @@
       <c r="D57" s="3"/>
       <c r="E57" s="32"/>
       <c r="F57" s="32"/>
-    </row>
-    <row r="58" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G57" s="58"/>
+    </row>
+    <row r="58" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>55</v>
       </c>
@@ -2893,8 +3016,9 @@
       <c r="D58" s="3"/>
       <c r="E58" s="32"/>
       <c r="F58" s="32"/>
-    </row>
-    <row r="59" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G58" s="58"/>
+    </row>
+    <row r="59" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>56</v>
       </c>
@@ -2907,8 +3031,9 @@
       <c r="D59" s="3"/>
       <c r="E59" s="32"/>
       <c r="F59" s="32"/>
-    </row>
-    <row r="60" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G59" s="58"/>
+    </row>
+    <row r="60" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>57</v>
       </c>
@@ -2923,8 +3048,9 @@
       <c r="F60" s="32" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G60" s="58"/>
+    </row>
+    <row r="61" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>58</v>
       </c>
@@ -2937,18 +3063,20 @@
       <c r="D61" s="3"/>
       <c r="E61" s="32"/>
       <c r="F61" s="32"/>
-    </row>
-    <row r="62" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="53" t="s">
+      <c r="G61" s="58"/>
+    </row>
+    <row r="62" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B62" s="53"/>
-      <c r="C62" s="53"/>
-      <c r="D62" s="53"/>
-      <c r="E62" s="53"/>
-      <c r="F62" s="53"/>
-    </row>
-    <row r="63" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="54"/>
+      <c r="C62" s="54"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="60"/>
+    </row>
+    <row r="63" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="15" t="s">
         <v>72</v>
       </c>
@@ -2965,8 +3093,11 @@
       <c r="F63" s="15" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G63" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="21">
         <v>1001</v>
       </c>
@@ -2981,8 +3112,11 @@
         <v>208</v>
       </c>
       <c r="F64" s="31"/>
-    </row>
-    <row r="65" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G64" s="58" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
         <v>1002</v>
       </c>
@@ -2997,8 +3131,9 @@
         <v>241</v>
       </c>
       <c r="F65" s="32"/>
-    </row>
-    <row r="66" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G65" s="58"/>
+    </row>
+    <row r="66" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>1003</v>
       </c>
@@ -3013,8 +3148,9 @@
         <v>242</v>
       </c>
       <c r="F66" s="32"/>
-    </row>
-    <row r="67" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G66" s="58"/>
+    </row>
+    <row r="67" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>1004</v>
       </c>
@@ -3029,8 +3165,9 @@
         <v>243</v>
       </c>
       <c r="F67" s="32"/>
-    </row>
-    <row r="68" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G67" s="58"/>
+    </row>
+    <row r="68" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
         <v>1005</v>
       </c>
@@ -3045,8 +3182,9 @@
         <v>244</v>
       </c>
       <c r="F68" s="32"/>
-    </row>
-    <row r="69" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G68" s="58"/>
+    </row>
+    <row r="69" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>1006</v>
       </c>
@@ -3061,8 +3199,9 @@
         <v>245</v>
       </c>
       <c r="F69" s="32"/>
-    </row>
-    <row r="70" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G69" s="58"/>
+    </row>
+    <row r="70" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
         <v>1007</v>
       </c>
@@ -3077,8 +3216,9 @@
         <v>246</v>
       </c>
       <c r="F70" s="32"/>
-    </row>
-    <row r="71" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G70" s="58"/>
+    </row>
+    <row r="71" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>1008</v>
       </c>
@@ -3093,8 +3233,9 @@
         <v>247</v>
       </c>
       <c r="F71" s="32"/>
-    </row>
-    <row r="72" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G71" s="58"/>
+    </row>
+    <row r="72" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
         <v>1009</v>
       </c>
@@ -3109,8 +3250,9 @@
         <v>248</v>
       </c>
       <c r="F72" s="32"/>
-    </row>
-    <row r="73" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G72" s="58"/>
+    </row>
+    <row r="73" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
         <v>1010</v>
       </c>
@@ -3125,8 +3267,9 @@
         <v>249</v>
       </c>
       <c r="F73" s="32"/>
-    </row>
-    <row r="74" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G73" s="58"/>
+    </row>
+    <row r="74" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5">
         <v>2015</v>
       </c>
@@ -3141,8 +3284,9 @@
         <v>250</v>
       </c>
       <c r="F74" s="32"/>
-    </row>
-    <row r="75" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G74" s="58"/>
+    </row>
+    <row r="75" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5">
         <v>2017</v>
       </c>
@@ -3157,8 +3301,9 @@
         <v>251</v>
       </c>
       <c r="F75" s="32"/>
-    </row>
-    <row r="76" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G75" s="58"/>
+    </row>
+    <row r="76" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
         <v>2019</v>
       </c>
@@ -3173,8 +3318,9 @@
         <v>252</v>
       </c>
       <c r="F76" s="32"/>
-    </row>
-    <row r="77" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G76" s="58"/>
+    </row>
+    <row r="77" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
         <v>2021</v>
       </c>
@@ -3189,8 +3335,9 @@
         <v>253</v>
       </c>
       <c r="F77" s="32"/>
-    </row>
-    <row r="78" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G77" s="58"/>
+    </row>
+    <row r="78" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
         <v>2022</v>
       </c>
@@ -3205,8 +3352,9 @@
         <v>254</v>
       </c>
       <c r="F78" s="32"/>
-    </row>
-    <row r="79" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G78" s="58"/>
+    </row>
+    <row r="79" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>2023</v>
       </c>
@@ -3221,8 +3369,9 @@
         <v>255</v>
       </c>
       <c r="F79" s="32"/>
-    </row>
-    <row r="80" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G79" s="58"/>
+    </row>
+    <row r="80" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
         <v>2024</v>
       </c>
@@ -3237,8 +3386,9 @@
         <v>256</v>
       </c>
       <c r="F80" s="32"/>
-    </row>
-    <row r="81" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G80" s="58"/>
+    </row>
+    <row r="81" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
         <v>2025</v>
       </c>
@@ -3253,8 +3403,9 @@
         <v>257</v>
       </c>
       <c r="F81" s="32"/>
-    </row>
-    <row r="82" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G81" s="58"/>
+    </row>
+    <row r="82" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
         <v>2028</v>
       </c>
@@ -3269,8 +3420,9 @@
         <v>258</v>
       </c>
       <c r="F82" s="32"/>
-    </row>
-    <row r="83" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G82" s="58"/>
+    </row>
+    <row r="83" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
         <v>2029</v>
       </c>
@@ -3285,8 +3437,9 @@
         <v>259</v>
       </c>
       <c r="F83" s="32"/>
-    </row>
-    <row r="84" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G83" s="58"/>
+    </row>
+    <row r="84" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="5">
         <v>2030</v>
       </c>
@@ -3301,8 +3454,9 @@
         <v>260</v>
       </c>
       <c r="F84" s="32"/>
-    </row>
-    <row r="85" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G84" s="58"/>
+    </row>
+    <row r="85" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
         <v>2031</v>
       </c>
@@ -3317,8 +3471,9 @@
         <v>261</v>
       </c>
       <c r="F85" s="32"/>
-    </row>
-    <row r="86" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G85" s="58"/>
+    </row>
+    <row r="86" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="5">
         <v>2032</v>
       </c>
@@ -3333,8 +3488,9 @@
         <v>262</v>
       </c>
       <c r="F86" s="32"/>
-    </row>
-    <row r="87" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G86" s="58"/>
+    </row>
+    <row r="87" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
         <v>2033</v>
       </c>
@@ -3349,8 +3505,9 @@
         <v>263</v>
       </c>
       <c r="F87" s="32"/>
-    </row>
-    <row r="88" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G87" s="58"/>
+    </row>
+    <row r="88" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="5">
         <v>2034</v>
       </c>
@@ -3365,8 +3522,9 @@
         <v>264</v>
       </c>
       <c r="F88" s="32"/>
-    </row>
-    <row r="89" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G88" s="58"/>
+    </row>
+    <row r="89" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
         <v>2035</v>
       </c>
@@ -3381,8 +3539,9 @@
         <v>265</v>
       </c>
       <c r="F89" s="32"/>
-    </row>
-    <row r="90" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G89" s="58"/>
+    </row>
+    <row r="90" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="5">
         <v>2036</v>
       </c>
@@ -3397,8 +3556,9 @@
         <v>266</v>
       </c>
       <c r="F90" s="32"/>
-    </row>
-    <row r="91" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G90" s="58"/>
+    </row>
+    <row r="91" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>2037</v>
       </c>
@@ -3413,8 +3573,9 @@
         <v>267</v>
       </c>
       <c r="F91" s="32"/>
-    </row>
-    <row r="92" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G91" s="58"/>
+    </row>
+    <row r="92" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="22">
         <v>2038</v>
       </c>
@@ -3429,8 +3590,9 @@
         <v>268</v>
       </c>
       <c r="F92" s="35"/>
-    </row>
-    <row r="93" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G92" s="58"/>
+    </row>
+    <row r="93" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="15" t="s">
         <v>72</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="F93" s="15" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G93" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="21">
         <v>2017</v>
       </c>
@@ -3461,8 +3626,9 @@
       <c r="D94" s="23"/>
       <c r="E94" s="46"/>
       <c r="F94" s="31"/>
-    </row>
-    <row r="95" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G94" s="58"/>
+    </row>
+    <row r="95" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
         <v>2019</v>
       </c>
@@ -3475,8 +3641,9 @@
       <c r="D95" s="6"/>
       <c r="E95" s="47"/>
       <c r="F95" s="32"/>
-    </row>
-    <row r="96" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G95" s="58"/>
+    </row>
+    <row r="96" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="5">
         <v>2021</v>
       </c>
@@ -3489,8 +3656,9 @@
       <c r="D96" s="6"/>
       <c r="E96" s="47"/>
       <c r="F96" s="32"/>
-    </row>
-    <row r="97" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G96" s="58"/>
+    </row>
+    <row r="97" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
         <v>2022</v>
       </c>
@@ -3503,8 +3671,9 @@
       <c r="D97" s="6"/>
       <c r="E97" s="47"/>
       <c r="F97" s="32"/>
-    </row>
-    <row r="98" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G97" s="58"/>
+    </row>
+    <row r="98" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="5">
         <v>2023</v>
       </c>
@@ -3517,8 +3686,9 @@
       <c r="D98" s="6"/>
       <c r="E98" s="47"/>
       <c r="F98" s="32"/>
-    </row>
-    <row r="99" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G98" s="58"/>
+    </row>
+    <row r="99" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>2024</v>
       </c>
@@ -3531,8 +3701,9 @@
       <c r="D99" s="6"/>
       <c r="E99" s="47"/>
       <c r="F99" s="32"/>
-    </row>
-    <row r="100" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G99" s="58"/>
+    </row>
+    <row r="100" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
         <v>2025</v>
       </c>
@@ -3545,8 +3716,9 @@
       <c r="D100" s="6"/>
       <c r="E100" s="47"/>
       <c r="F100" s="32"/>
-    </row>
-    <row r="101" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G100" s="58"/>
+    </row>
+    <row r="101" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>2029</v>
       </c>
@@ -3559,8 +3731,9 @@
       <c r="D101" s="3"/>
       <c r="E101" s="47"/>
       <c r="F101" s="32"/>
-    </row>
-    <row r="102" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G101" s="58"/>
+    </row>
+    <row r="102" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
         <v>2031</v>
       </c>
@@ -3573,8 +3746,9 @@
       <c r="D102" s="6"/>
       <c r="E102" s="47"/>
       <c r="F102" s="32"/>
-    </row>
-    <row r="103" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G102" s="58"/>
+    </row>
+    <row r="103" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
         <v>2034</v>
       </c>
@@ -3587,8 +3761,9 @@
       <c r="D103" s="6"/>
       <c r="E103" s="47"/>
       <c r="F103" s="32"/>
-    </row>
-    <row r="104" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G103" s="58"/>
+    </row>
+    <row r="104" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
         <v>2035</v>
       </c>
@@ -3601,8 +3776,9 @@
       <c r="D104" s="6"/>
       <c r="E104" s="47"/>
       <c r="F104" s="32"/>
-    </row>
-    <row r="105" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G104" s="58"/>
+    </row>
+    <row r="105" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>2037</v>
       </c>
@@ -3615,8 +3791,9 @@
       <c r="D105" s="6"/>
       <c r="E105" s="47"/>
       <c r="F105" s="32"/>
-    </row>
-    <row r="106" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G105" s="58"/>
+    </row>
+    <row r="106" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="22">
         <v>2038</v>
       </c>
@@ -3629,8 +3806,9 @@
       <c r="D106" s="24"/>
       <c r="E106" s="48"/>
       <c r="F106" s="35"/>
-    </row>
-    <row r="107" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G106" s="58"/>
+    </row>
+    <row r="107" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="15" t="s">
         <v>72</v>
       </c>
@@ -3647,8 +3825,11 @@
       <c r="F107" s="15" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G107" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="27">
         <v>5015</v>
       </c>
@@ -3663,8 +3844,9 @@
         <v>207</v>
       </c>
       <c r="F108" s="31"/>
-    </row>
-    <row r="109" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G108" s="58"/>
+    </row>
+    <row r="109" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="7">
         <v>5017</v>
       </c>
@@ -3679,8 +3861,9 @@
         <v>269</v>
       </c>
       <c r="F109" s="32"/>
-    </row>
-    <row r="110" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G109" s="58"/>
+    </row>
+    <row r="110" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="7">
         <v>5019</v>
       </c>
@@ -3695,8 +3878,9 @@
         <v>270</v>
       </c>
       <c r="F110" s="32"/>
-    </row>
-    <row r="111" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G110" s="58"/>
+    </row>
+    <row r="111" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="7">
         <v>5021</v>
       </c>
@@ -3711,8 +3895,9 @@
         <v>271</v>
       </c>
       <c r="F111" s="32"/>
-    </row>
-    <row r="112" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G111" s="58"/>
+    </row>
+    <row r="112" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="7">
         <v>5022</v>
       </c>
@@ -3727,8 +3912,9 @@
         <v>272</v>
       </c>
       <c r="F112" s="32"/>
-    </row>
-    <row r="113" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G112" s="58"/>
+    </row>
+    <row r="113" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="7">
         <v>5023</v>
       </c>
@@ -3743,8 +3929,9 @@
         <v>273</v>
       </c>
       <c r="F113" s="32"/>
-    </row>
-    <row r="114" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G113" s="58"/>
+    </row>
+    <row r="114" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="7">
         <v>5024</v>
       </c>
@@ -3759,8 +3946,9 @@
         <v>274</v>
       </c>
       <c r="F114" s="32"/>
-    </row>
-    <row r="115" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G114" s="58"/>
+    </row>
+    <row r="115" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="7">
         <v>5025</v>
       </c>
@@ -3775,8 +3963,9 @@
         <v>275</v>
       </c>
       <c r="F115" s="32"/>
-    </row>
-    <row r="116" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G115" s="58"/>
+    </row>
+    <row r="116" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="7">
         <v>5028</v>
       </c>
@@ -3791,8 +3980,9 @@
         <v>276</v>
       </c>
       <c r="F116" s="32"/>
-    </row>
-    <row r="117" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G116" s="58"/>
+    </row>
+    <row r="117" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="7">
         <v>5029</v>
       </c>
@@ -3807,8 +3997,9 @@
         <v>277</v>
       </c>
       <c r="F117" s="32"/>
-    </row>
-    <row r="118" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G117" s="58"/>
+    </row>
+    <row r="118" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="7">
         <v>5030</v>
       </c>
@@ -3823,8 +4014,9 @@
         <v>278</v>
       </c>
       <c r="F118" s="32"/>
-    </row>
-    <row r="119" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G118" s="58"/>
+    </row>
+    <row r="119" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="7">
         <v>5031</v>
       </c>
@@ -3839,8 +4031,9 @@
         <v>279</v>
       </c>
       <c r="F119" s="32"/>
-    </row>
-    <row r="120" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G119" s="58"/>
+    </row>
+    <row r="120" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="7">
         <v>5032</v>
       </c>
@@ -3855,8 +4048,9 @@
         <v>280</v>
       </c>
       <c r="F120" s="32"/>
-    </row>
-    <row r="121" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G120" s="58"/>
+    </row>
+    <row r="121" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="7">
         <v>5033</v>
       </c>
@@ -3871,8 +4065,9 @@
         <v>281</v>
       </c>
       <c r="F121" s="32"/>
-    </row>
-    <row r="122" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G121" s="58"/>
+    </row>
+    <row r="122" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="7">
         <v>5034</v>
       </c>
@@ -3887,8 +4082,9 @@
         <v>282</v>
       </c>
       <c r="F122" s="32"/>
-    </row>
-    <row r="123" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G122" s="58"/>
+    </row>
+    <row r="123" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="7">
         <v>5035</v>
       </c>
@@ -3903,8 +4099,9 @@
         <v>283</v>
       </c>
       <c r="F123" s="32"/>
-    </row>
-    <row r="124" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G123" s="58"/>
+    </row>
+    <row r="124" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="7">
         <v>5036</v>
       </c>
@@ -3919,8 +4116,9 @@
         <v>284</v>
       </c>
       <c r="F124" s="32"/>
-    </row>
-    <row r="125" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G124" s="58"/>
+    </row>
+    <row r="125" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="7">
         <v>5037</v>
       </c>
@@ -3935,8 +4133,9 @@
         <v>285</v>
       </c>
       <c r="F125" s="32"/>
-    </row>
-    <row r="126" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G125" s="58"/>
+    </row>
+    <row r="126" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="25">
         <v>5038</v>
       </c>
@@ -3953,8 +4152,9 @@
       <c r="F126" s="19" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G126" s="56"/>
+    </row>
+    <row r="127" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="15" t="s">
         <v>72</v>
       </c>
@@ -3971,8 +4171,11 @@
       <c r="F127" s="15" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G127" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="28" t="s">
         <v>60</v>
       </c>
@@ -3987,8 +4190,9 @@
         <v>287</v>
       </c>
       <c r="F128" s="31"/>
-    </row>
-    <row r="129" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G128" s="58"/>
+    </row>
+    <row r="129" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="8" t="s">
         <v>61</v>
       </c>
@@ -4003,8 +4207,9 @@
         <v>288</v>
       </c>
       <c r="F129" s="32"/>
-    </row>
-    <row r="130" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G129" s="58"/>
+    </row>
+    <row r="130" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="8" t="s">
         <v>62</v>
       </c>
@@ -4019,8 +4224,9 @@
         <v>289</v>
       </c>
       <c r="F130" s="32"/>
-    </row>
-    <row r="131" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G130" s="58"/>
+    </row>
+    <row r="131" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="8" t="s">
         <v>63</v>
       </c>
@@ -4035,8 +4241,9 @@
         <v>290</v>
       </c>
       <c r="F131" s="32"/>
-    </row>
-    <row r="132" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G131" s="58"/>
+    </row>
+    <row r="132" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="8" t="s">
         <v>64</v>
       </c>
@@ -4051,8 +4258,9 @@
         <v>291</v>
       </c>
       <c r="F132" s="32"/>
-    </row>
-    <row r="133" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G132" s="58"/>
+    </row>
+    <row r="133" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="8" t="s">
         <v>65</v>
       </c>
@@ -4067,8 +4275,9 @@
         <v>292</v>
       </c>
       <c r="F133" s="32"/>
-    </row>
-    <row r="134" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G133" s="58"/>
+    </row>
+    <row r="134" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="8" t="s">
         <v>66</v>
       </c>
@@ -4083,8 +4292,9 @@
         <v>293</v>
       </c>
       <c r="F134" s="32"/>
-    </row>
-    <row r="135" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G134" s="58"/>
+    </row>
+    <row r="135" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="8" t="s">
         <v>67</v>
       </c>
@@ -4099,8 +4309,9 @@
         <v>294</v>
       </c>
       <c r="F135" s="32"/>
-    </row>
-    <row r="136" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G135" s="58"/>
+    </row>
+    <row r="136" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="8" t="s">
         <v>68</v>
       </c>
@@ -4115,8 +4326,9 @@
         <v>295</v>
       </c>
       <c r="F136" s="32"/>
-    </row>
-    <row r="137" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G136" s="58"/>
+    </row>
+    <row r="137" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="8" t="s">
         <v>69</v>
       </c>
@@ -4131,8 +4343,9 @@
         <v>296</v>
       </c>
       <c r="F137" s="32"/>
-    </row>
-    <row r="138" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G137" s="58"/>
+    </row>
+    <row r="138" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="26" t="s">
         <v>70</v>
       </c>
@@ -4147,8 +4360,9 @@
         <v>297</v>
       </c>
       <c r="F138" s="35"/>
-    </row>
-    <row r="139" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G138" s="58"/>
+    </row>
+    <row r="139" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="15" t="s">
         <v>72</v>
       </c>
@@ -4165,8 +4379,11 @@
       <c r="F139" s="15" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G139" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="28" t="s">
         <v>65</v>
       </c>
@@ -4179,8 +4396,9 @@
       <c r="D140" s="23"/>
       <c r="E140" s="51"/>
       <c r="F140" s="31"/>
-    </row>
-    <row r="141" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G140" s="58"/>
+    </row>
+    <row r="141" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="8" t="s">
         <v>63</v>
       </c>
@@ -4193,8 +4411,9 @@
       <c r="D141" s="6"/>
       <c r="E141" s="47"/>
       <c r="F141" s="32"/>
-    </row>
-    <row r="142" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G141" s="58"/>
+    </row>
+    <row r="142" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="8" t="s">
         <v>67</v>
       </c>
@@ -4207,18 +4426,20 @@
       <c r="D142" s="6"/>
       <c r="E142" s="47"/>
       <c r="F142" s="32"/>
-    </row>
-    <row r="143" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="54" t="s">
+      <c r="G142" s="58"/>
+    </row>
+    <row r="143" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A143" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="B143" s="54"/>
-      <c r="C143" s="54"/>
-      <c r="D143" s="54"/>
-      <c r="E143" s="54"/>
-      <c r="F143" s="54"/>
-    </row>
-    <row r="144" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B143" s="55"/>
+      <c r="C143" s="55"/>
+      <c r="D143" s="55"/>
+      <c r="E143" s="55"/>
+      <c r="F143" s="55"/>
+      <c r="G143" s="61"/>
+    </row>
+    <row r="144" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="15" t="s">
         <v>72</v>
       </c>
@@ -4235,8 +4456,11 @@
       <c r="F144" s="15" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G144" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="12" t="s">
         <v>121</v>
       </c>
@@ -4247,12 +4471,15 @@
         <v>533</v>
       </c>
       <c r="D145" s="13"/>
-      <c r="E145" s="51"/>
+      <c r="E145" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F145" s="37" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G145" s="62"/>
+    </row>
+    <row r="146" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>122</v>
       </c>
@@ -4263,10 +4490,13 @@
         <v>640</v>
       </c>
       <c r="D146" s="3"/>
-      <c r="E146" s="47"/>
+      <c r="E146" s="50" t="s">
+        <v>331</v>
+      </c>
       <c r="F146" s="38"/>
-    </row>
-    <row r="147" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G146" s="62"/>
+    </row>
+    <row r="147" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>123</v>
       </c>
@@ -4277,12 +4507,15 @@
         <v>800</v>
       </c>
       <c r="D147" s="3"/>
-      <c r="E147" s="47"/>
+      <c r="E147" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F147" s="38" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G147" s="62"/>
+    </row>
+    <row r="148" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>124</v>
       </c>
@@ -4293,12 +4526,15 @@
         <v>880</v>
       </c>
       <c r="D148" s="3"/>
-      <c r="E148" s="47"/>
+      <c r="E148" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F148" s="38" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G148" s="62"/>
+    </row>
+    <row r="149" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>126</v>
       </c>
@@ -4309,12 +4545,15 @@
         <v>660</v>
       </c>
       <c r="D149" s="3"/>
-      <c r="E149" s="47"/>
+      <c r="E149" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F149" s="38" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G149" s="62"/>
+    </row>
+    <row r="150" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>128</v>
       </c>
@@ -4325,10 +4564,13 @@
         <v>780</v>
       </c>
       <c r="D150" s="3"/>
-      <c r="E150" s="47"/>
+      <c r="E150" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F150" s="38"/>
-    </row>
-    <row r="151" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G150" s="62"/>
+    </row>
+    <row r="151" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>130</v>
       </c>
@@ -4339,12 +4581,15 @@
         <v>840</v>
       </c>
       <c r="D151" s="3"/>
-      <c r="E151" s="47"/>
+      <c r="E151" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F151" s="38" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G151" s="62"/>
+    </row>
+    <row r="152" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>131</v>
       </c>
@@ -4355,12 +4600,15 @@
         <v>900</v>
       </c>
       <c r="D152" s="3"/>
-      <c r="E152" s="47"/>
+      <c r="E152" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F152" s="38" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G152" s="62"/>
+    </row>
+    <row r="153" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>133</v>
       </c>
@@ -4371,12 +4619,15 @@
         <v>990</v>
       </c>
       <c r="D153" s="3"/>
-      <c r="E153" s="47"/>
+      <c r="E153" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F153" s="38" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G153" s="62"/>
+    </row>
+    <row r="154" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>135</v>
       </c>
@@ -4387,12 +4638,15 @@
         <v>1080</v>
       </c>
       <c r="D154" s="3"/>
-      <c r="E154" s="47"/>
+      <c r="E154" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F154" s="39" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G154" s="63"/>
+    </row>
+    <row r="155" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>136</v>
       </c>
@@ -4403,12 +4657,15 @@
         <v>1140</v>
       </c>
       <c r="D155" s="3"/>
-      <c r="E155" s="47"/>
+      <c r="E155" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F155" s="38" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G155" s="62"/>
+    </row>
+    <row r="156" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>138</v>
       </c>
@@ -4419,12 +4676,15 @@
         <v>1056</v>
       </c>
       <c r="D156" s="3"/>
-      <c r="E156" s="47"/>
+      <c r="E156" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F156" s="38" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G156" s="62"/>
+    </row>
+    <row r="157" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>139</v>
       </c>
@@ -4435,12 +4695,15 @@
         <v>1152</v>
       </c>
       <c r="D157" s="3"/>
-      <c r="E157" s="47"/>
+      <c r="E157" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F157" s="38" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G157" s="62"/>
+    </row>
+    <row r="158" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>141</v>
       </c>
@@ -4451,12 +4714,15 @@
         <v>1248</v>
       </c>
       <c r="D158" s="3"/>
-      <c r="E158" s="47"/>
+      <c r="E158" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F158" s="38" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G158" s="62"/>
+    </row>
+    <row r="159" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>143</v>
       </c>
@@ -4467,10 +4733,13 @@
         <v>1176</v>
       </c>
       <c r="D159" s="3"/>
-      <c r="E159" s="47"/>
+      <c r="E159" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F159" s="38"/>
-    </row>
-    <row r="160" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G159" s="62"/>
+    </row>
+    <row r="160" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>316</v>
       </c>
@@ -4481,12 +4750,15 @@
         <v>1344</v>
       </c>
       <c r="D160" s="3"/>
-      <c r="E160" s="47"/>
+      <c r="E160" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F160" s="38" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G160" s="62"/>
+    </row>
+    <row r="161" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>145</v>
       </c>
@@ -4497,12 +4769,15 @@
         <v>1272</v>
       </c>
       <c r="D161" s="3"/>
-      <c r="E161" s="47"/>
+      <c r="E161" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F161" s="30" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="162" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G161" s="30"/>
+    </row>
+    <row r="162" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>147</v>
       </c>
@@ -4513,10 +4788,13 @@
         <v>1067</v>
       </c>
       <c r="D162" s="3"/>
-      <c r="E162" s="47"/>
+      <c r="E162" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F162" s="38"/>
-    </row>
-    <row r="163" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G162" s="62"/>
+    </row>
+    <row r="163" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>149</v>
       </c>
@@ -4527,12 +4805,15 @@
         <v>1173</v>
       </c>
       <c r="D163" s="3"/>
-      <c r="E163" s="47"/>
+      <c r="E163" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F163" s="39" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G163" s="63"/>
+    </row>
+    <row r="164" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>150</v>
       </c>
@@ -4543,12 +4824,15 @@
         <v>1280</v>
       </c>
       <c r="D164" s="3"/>
-      <c r="E164" s="47"/>
+      <c r="E164" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F164" s="39" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="165" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G164" s="63"/>
+    </row>
+    <row r="165" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>151</v>
       </c>
@@ -4559,12 +4843,15 @@
         <v>1306</v>
       </c>
       <c r="D165" s="3"/>
-      <c r="E165" s="47"/>
+      <c r="E165" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F165" s="38" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="166" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G165" s="62"/>
+    </row>
+    <row r="166" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>153</v>
       </c>
@@ -4575,10 +4862,13 @@
         <v>1387</v>
       </c>
       <c r="D166" s="3"/>
-      <c r="E166" s="47"/>
+      <c r="E166" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F166" s="38"/>
-    </row>
-    <row r="167" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G166" s="62"/>
+    </row>
+    <row r="167" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>154</v>
       </c>
@@ -4589,12 +4879,15 @@
         <v>1493</v>
       </c>
       <c r="D167" s="3"/>
-      <c r="E167" s="47"/>
+      <c r="E167" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F167" s="38" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="168" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G167" s="62"/>
+    </row>
+    <row r="168" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>155</v>
       </c>
@@ -4605,12 +4898,15 @@
         <v>1414</v>
       </c>
       <c r="D168" s="3"/>
-      <c r="E168" s="47"/>
+      <c r="E168" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F168" s="38" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="169" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G168" s="62"/>
+    </row>
+    <row r="169" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>157</v>
       </c>
@@ -4621,12 +4917,15 @@
         <v>1600</v>
       </c>
       <c r="D169" s="3"/>
-      <c r="E169" s="47"/>
+      <c r="E169" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F169" s="39" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="170" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G169" s="63"/>
+    </row>
+    <row r="170" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>159</v>
       </c>
@@ -4637,12 +4936,15 @@
         <v>1760</v>
       </c>
       <c r="D170" s="3"/>
-      <c r="E170" s="47"/>
+      <c r="E170" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F170" s="39" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="171" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G170" s="63"/>
+    </row>
+    <row r="171" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>161</v>
       </c>
@@ -4653,12 +4955,15 @@
         <v>1920</v>
       </c>
       <c r="D171" s="3"/>
-      <c r="E171" s="47"/>
+      <c r="E171" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F171" s="38" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="172" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G171" s="62"/>
+    </row>
+    <row r="172" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>162</v>
       </c>
@@ -4669,10 +4974,13 @@
         <v>2052</v>
       </c>
       <c r="D172" s="3"/>
-      <c r="E172" s="47"/>
+      <c r="E172" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F172" s="38"/>
-    </row>
-    <row r="173" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G172" s="62"/>
+    </row>
+    <row r="173" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>164</v>
       </c>
@@ -4683,12 +4991,15 @@
         <v>1680</v>
       </c>
       <c r="D173" s="3"/>
-      <c r="E173" s="47"/>
+      <c r="E173" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F173" s="38" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="174" spans="1:6" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G173" s="62"/>
+    </row>
+    <row r="174" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>166</v>
       </c>
@@ -4699,8 +5010,11 @@
         <v>1493</v>
       </c>
       <c r="D174" s="3"/>
-      <c r="E174" s="47"/>
+      <c r="E174" s="50" t="s">
+        <v>330</v>
+      </c>
       <c r="F174" s="38"/>
+      <c r="G174" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4792,6 +5106,11 @@
     <hyperlink ref="F5" r:id="rId81" xr:uid="{AD6F7F6C-6CC4-4F5A-97D9-293FAF7AD4C6}"/>
     <hyperlink ref="F6" r:id="rId82" xr:uid="{6A4738D8-2CCC-40F0-A75D-AED17777BD7F}"/>
     <hyperlink ref="F7" r:id="rId83" xr:uid="{A1EAB810-3396-4438-9B7E-658BC583633E}"/>
+    <hyperlink ref="G43" r:id="rId84" xr:uid="{8B55708E-95ED-4853-9BBE-6271E4E5B327}"/>
+    <hyperlink ref="G52" r:id="rId85" xr:uid="{83D93986-820A-426C-8C24-B961323BADFE}"/>
+    <hyperlink ref="E145" r:id="rId86" xr:uid="{95272B36-1B3E-4E9F-A78F-B49AAE3263D2}"/>
+    <hyperlink ref="E146:E174" r:id="rId87" display="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Imagine.pdf" xr:uid="{D958AEE0-FAA3-4065-B126-6557F87E05A9}"/>
+    <hyperlink ref="E146" r:id="rId88" xr:uid="{43838F99-75E5-4924-A97E-2531FB82672F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Homes List.xlsx
+++ b/docs/Homes List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9df306d6984b8b22/Documents/GitHub/Wix-Products/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="464" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94028A43-9042-4354-99F1-2C2527B85336}"/>
+  <xr:revisionPtr revIDLastSave="465" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF1763A6-4735-4032-B8CE-865778A9227A}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
+    <workbookView minimized="1" xWindow="5390" yWindow="2510" windowWidth="28800" windowHeight="15380" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="334">
   <si>
     <t xml:space="preserve">Golden West </t>
   </si>
@@ -1233,6 +1233,9 @@
   </si>
   <si>
     <t>https://my.matterport.com/show?play=1&amp;lang=en-US&amp;m=FgFZPzopwY2</t>
+  </si>
+  <si>
+    <t>https://my.matterport.com/show/?play=1&amp;m=Mac4ayKuY7Q</t>
   </si>
 </sst>
 </file>
@@ -1468,7 +1471,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1596,6 +1599,21 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1604,22 +1622,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2026,14 +2028,14 @@
       <c r="G2" s="30"/>
     </row>
     <row r="3" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
       <c r="G3" s="52"/>
     </row>
     <row r="4" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -2077,7 +2079,7 @@
       <c r="F5" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="G5" s="56"/>
+      <c r="G5" s="53"/>
     </row>
     <row r="6" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
@@ -2094,7 +2096,7 @@
       <c r="F6" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="G6" s="56"/>
+      <c r="G6" s="53"/>
       <c r="H6" t="s">
         <v>174</v>
       </c>
@@ -2116,7 +2118,7 @@
       <c r="F7" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="G7" s="56"/>
+      <c r="G7" s="53"/>
       <c r="H7" t="s">
         <v>173</v>
       </c>
@@ -2136,7 +2138,7 @@
         <v>175</v>
       </c>
       <c r="F8" s="34"/>
-      <c r="G8" s="57"/>
+      <c r="G8" s="54"/>
     </row>
     <row r="9" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
@@ -2155,7 +2157,7 @@
       <c r="F9" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="G9" s="58"/>
+      <c r="G9" s="30"/>
     </row>
     <row r="10" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
@@ -2174,7 +2176,7 @@
       <c r="F10" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="G10" s="59"/>
+      <c r="G10" s="55"/>
     </row>
     <row r="11" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
@@ -2191,7 +2193,7 @@
         <v>178</v>
       </c>
       <c r="F11" s="32"/>
-      <c r="G11" s="58"/>
+      <c r="G11" s="30"/>
     </row>
     <row r="12" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
@@ -2208,7 +2210,7 @@
         <v>179</v>
       </c>
       <c r="F12" s="32"/>
-      <c r="G12" s="58"/>
+      <c r="G12" s="30"/>
     </row>
     <row r="13" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
@@ -2227,7 +2229,7 @@
       <c r="F13" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="G13" s="58"/>
+      <c r="G13" s="30"/>
     </row>
     <row r="14" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
@@ -2244,7 +2246,7 @@
         <v>181</v>
       </c>
       <c r="F14" s="32"/>
-      <c r="G14" s="58"/>
+      <c r="G14" s="30"/>
     </row>
     <row r="15" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
@@ -2263,7 +2265,7 @@
       <c r="F15" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="G15" s="58"/>
+      <c r="G15" s="30"/>
     </row>
     <row r="16" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
@@ -2280,7 +2282,7 @@
         <v>182</v>
       </c>
       <c r="F16" s="32"/>
-      <c r="G16" s="58"/>
+      <c r="G16" s="30"/>
     </row>
     <row r="17" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
@@ -2299,7 +2301,7 @@
       <c r="F17" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="G17" s="58"/>
+      <c r="G17" s="30"/>
     </row>
     <row r="18" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
@@ -2316,7 +2318,7 @@
         <v>184</v>
       </c>
       <c r="F18" s="32"/>
-      <c r="G18" s="58"/>
+      <c r="G18" s="30"/>
     </row>
     <row r="19" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
@@ -2333,7 +2335,7 @@
         <v>185</v>
       </c>
       <c r="F19" s="32"/>
-      <c r="G19" s="58"/>
+      <c r="G19" s="30"/>
     </row>
     <row r="20" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
@@ -2352,7 +2354,7 @@
       <c r="F20" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="G20" s="58"/>
+      <c r="G20" s="30"/>
     </row>
     <row r="21" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
@@ -2371,7 +2373,7 @@
       <c r="F21" s="32" t="s">
         <v>221</v>
       </c>
-      <c r="G21" s="58"/>
+      <c r="G21" s="30"/>
     </row>
     <row r="22" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
@@ -2388,7 +2390,7 @@
         <v>188</v>
       </c>
       <c r="F22" s="32"/>
-      <c r="G22" s="58"/>
+      <c r="G22" s="30"/>
     </row>
     <row r="23" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
@@ -2405,7 +2407,7 @@
         <v>189</v>
       </c>
       <c r="F23" s="32"/>
-      <c r="G23" s="58"/>
+      <c r="G23" s="30"/>
     </row>
     <row r="24" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
@@ -2424,7 +2426,7 @@
       <c r="F24" s="33" t="s">
         <v>226</v>
       </c>
-      <c r="G24" s="59"/>
+      <c r="G24" s="55"/>
     </row>
     <row r="25" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
@@ -2443,7 +2445,7 @@
       <c r="F25" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="G25" s="58"/>
+      <c r="G25" s="30"/>
     </row>
     <row r="26" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
@@ -2462,7 +2464,7 @@
       <c r="F26" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="G26" s="58"/>
+      <c r="G26" s="30"/>
     </row>
     <row r="27" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
@@ -2481,7 +2483,7 @@
       <c r="F27" s="33" t="s">
         <v>227</v>
       </c>
-      <c r="G27" s="59"/>
+      <c r="G27" s="55"/>
     </row>
     <row r="28" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
@@ -2500,7 +2502,7 @@
       <c r="F28" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="G28" s="58"/>
+      <c r="G28" s="30"/>
     </row>
     <row r="29" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
@@ -2519,7 +2521,7 @@
       <c r="F29" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="G29" s="58"/>
+      <c r="G29" s="30"/>
     </row>
     <row r="30" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
@@ -2538,7 +2540,7 @@
       <c r="F30" s="33" t="s">
         <v>230</v>
       </c>
-      <c r="G30" s="59"/>
+      <c r="G30" s="55"/>
     </row>
     <row r="31" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
@@ -2555,7 +2557,7 @@
         <v>197</v>
       </c>
       <c r="F31" s="32"/>
-      <c r="G31" s="58"/>
+      <c r="G31" s="30"/>
     </row>
     <row r="32" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
@@ -2572,7 +2574,7 @@
         <v>198</v>
       </c>
       <c r="F32" s="32"/>
-      <c r="G32" s="58"/>
+      <c r="G32" s="30"/>
     </row>
     <row r="33" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
@@ -2591,7 +2593,7 @@
       <c r="F33" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="G33" s="58"/>
+      <c r="G33" s="30"/>
     </row>
     <row r="34" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
@@ -2610,7 +2612,7 @@
       <c r="F34" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="G34" s="58"/>
+      <c r="G34" s="30"/>
     </row>
     <row r="35" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
@@ -2627,7 +2629,7 @@
         <v>201</v>
       </c>
       <c r="F35" s="32"/>
-      <c r="G35" s="58"/>
+      <c r="G35" s="30"/>
     </row>
     <row r="36" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
@@ -2646,7 +2648,7 @@
       <c r="F36" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="G36" s="59"/>
+      <c r="G36" s="55"/>
     </row>
     <row r="37" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
@@ -2663,7 +2665,7 @@
         <v>203</v>
       </c>
       <c r="F37" s="32"/>
-      <c r="G37" s="58"/>
+      <c r="G37" s="30"/>
     </row>
     <row r="38" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
@@ -2682,7 +2684,7 @@
       <c r="F38" s="32" t="s">
         <v>233</v>
       </c>
-      <c r="G38" s="58"/>
+      <c r="G38" s="30"/>
     </row>
     <row r="39" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="16" t="s">
@@ -2701,7 +2703,7 @@
       <c r="F39" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="G39" s="58"/>
+      <c r="G39" s="30"/>
     </row>
     <row r="40" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="15" t="s">
@@ -2739,7 +2741,7 @@
         <v>206</v>
       </c>
       <c r="F41" s="31"/>
-      <c r="G41" s="58" t="s">
+      <c r="G41" s="30" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2756,7 +2758,9 @@
       <c r="D42" s="3"/>
       <c r="E42" s="32"/>
       <c r="F42" s="32"/>
-      <c r="G42" s="58"/>
+      <c r="G42" s="30" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="43" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
@@ -2773,7 +2777,7 @@
       <c r="F43" s="33" t="s">
         <v>235</v>
       </c>
-      <c r="G43" s="56" t="s">
+      <c r="G43" s="53" t="s">
         <v>325</v>
       </c>
     </row>
@@ -2790,7 +2794,7 @@
       <c r="D44" s="3"/>
       <c r="E44" s="32"/>
       <c r="F44" s="32"/>
-      <c r="G44" s="58"/>
+      <c r="G44" s="30"/>
     </row>
     <row r="45" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
@@ -2805,7 +2809,7 @@
       <c r="D45" s="3"/>
       <c r="E45" s="32"/>
       <c r="F45" s="32"/>
-      <c r="G45" s="58" t="s">
+      <c r="G45" s="30" t="s">
         <v>326</v>
       </c>
     </row>
@@ -2824,7 +2828,7 @@
       <c r="F46" s="32" t="s">
         <v>236</v>
       </c>
-      <c r="G46" s="58"/>
+      <c r="G46" s="30"/>
     </row>
     <row r="47" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
@@ -2839,7 +2843,7 @@
       <c r="D47" s="3"/>
       <c r="E47" s="32"/>
       <c r="F47" s="32"/>
-      <c r="G47" s="58"/>
+      <c r="G47" s="30"/>
     </row>
     <row r="48" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
@@ -2856,7 +2860,7 @@
       <c r="F48" s="32" t="s">
         <v>237</v>
       </c>
-      <c r="G48" s="58" t="s">
+      <c r="G48" s="30" t="s">
         <v>327</v>
       </c>
     </row>
@@ -2873,7 +2877,7 @@
       <c r="D49" s="3"/>
       <c r="E49" s="32"/>
       <c r="F49" s="32"/>
-      <c r="G49" s="58"/>
+      <c r="G49" s="30"/>
     </row>
     <row r="50" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
@@ -2890,7 +2894,7 @@
       <c r="F50" s="33" t="s">
         <v>238</v>
       </c>
-      <c r="G50" s="59"/>
+      <c r="G50" s="55"/>
     </row>
     <row r="51" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
@@ -2905,7 +2909,7 @@
       <c r="D51" s="3"/>
       <c r="E51" s="32"/>
       <c r="F51" s="32"/>
-      <c r="G51" s="58"/>
+      <c r="G51" s="30"/>
     </row>
     <row r="52" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
@@ -2920,7 +2924,7 @@
       <c r="D52" s="3"/>
       <c r="E52" s="32"/>
       <c r="F52" s="32"/>
-      <c r="G52" s="56" t="s">
+      <c r="G52" s="53" t="s">
         <v>328</v>
       </c>
     </row>
@@ -2937,7 +2941,7 @@
       <c r="D53" s="3"/>
       <c r="E53" s="32"/>
       <c r="F53" s="32"/>
-      <c r="G53" s="58"/>
+      <c r="G53" s="30"/>
     </row>
     <row r="54" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
@@ -2954,7 +2958,7 @@
       <c r="F54" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="G54" s="58"/>
+      <c r="G54" s="30"/>
     </row>
     <row r="55" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
@@ -2969,7 +2973,7 @@
       <c r="D55" s="3"/>
       <c r="E55" s="32"/>
       <c r="F55" s="32"/>
-      <c r="G55" s="58"/>
+      <c r="G55" s="30"/>
     </row>
     <row r="56" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
@@ -2984,7 +2988,7 @@
       <c r="D56" s="3"/>
       <c r="E56" s="32"/>
       <c r="F56" s="32"/>
-      <c r="G56" s="58" t="s">
+      <c r="G56" s="30" t="s">
         <v>329</v>
       </c>
     </row>
@@ -3001,7 +3005,7 @@
       <c r="D57" s="3"/>
       <c r="E57" s="32"/>
       <c r="F57" s="32"/>
-      <c r="G57" s="58"/>
+      <c r="G57" s="30"/>
     </row>
     <row r="58" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
@@ -3016,7 +3020,7 @@
       <c r="D58" s="3"/>
       <c r="E58" s="32"/>
       <c r="F58" s="32"/>
-      <c r="G58" s="58"/>
+      <c r="G58" s="30"/>
     </row>
     <row r="59" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
@@ -3031,7 +3035,7 @@
       <c r="D59" s="3"/>
       <c r="E59" s="32"/>
       <c r="F59" s="32"/>
-      <c r="G59" s="58"/>
+      <c r="G59" s="30"/>
     </row>
     <row r="60" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
@@ -3048,7 +3052,7 @@
       <c r="F60" s="32" t="s">
         <v>240</v>
       </c>
-      <c r="G60" s="58"/>
+      <c r="G60" s="30"/>
     </row>
     <row r="61" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
@@ -3063,18 +3067,18 @@
       <c r="D61" s="3"/>
       <c r="E61" s="32"/>
       <c r="F61" s="32"/>
-      <c r="G61" s="58"/>
+      <c r="G61" s="30"/>
     </row>
     <row r="62" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="54" t="s">
+      <c r="A62" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="B62" s="54"/>
-      <c r="C62" s="54"/>
-      <c r="D62" s="54"/>
-      <c r="E62" s="54"/>
-      <c r="F62" s="54"/>
-      <c r="G62" s="60"/>
+      <c r="B62" s="61"/>
+      <c r="C62" s="61"/>
+      <c r="D62" s="61"/>
+      <c r="E62" s="61"/>
+      <c r="F62" s="61"/>
+      <c r="G62" s="56"/>
     </row>
     <row r="63" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="15" t="s">
@@ -3112,7 +3116,7 @@
         <v>208</v>
       </c>
       <c r="F64" s="31"/>
-      <c r="G64" s="58" t="s">
+      <c r="G64" s="30" t="s">
         <v>332</v>
       </c>
     </row>
@@ -3131,7 +3135,7 @@
         <v>241</v>
       </c>
       <c r="F65" s="32"/>
-      <c r="G65" s="58"/>
+      <c r="G65" s="30"/>
     </row>
     <row r="66" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
@@ -3148,7 +3152,7 @@
         <v>242</v>
       </c>
       <c r="F66" s="32"/>
-      <c r="G66" s="58"/>
+      <c r="G66" s="30"/>
     </row>
     <row r="67" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
@@ -3165,7 +3169,7 @@
         <v>243</v>
       </c>
       <c r="F67" s="32"/>
-      <c r="G67" s="58"/>
+      <c r="G67" s="30"/>
     </row>
     <row r="68" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
@@ -3182,7 +3186,7 @@
         <v>244</v>
       </c>
       <c r="F68" s="32"/>
-      <c r="G68" s="58"/>
+      <c r="G68" s="30"/>
     </row>
     <row r="69" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
@@ -3199,7 +3203,7 @@
         <v>245</v>
       </c>
       <c r="F69" s="32"/>
-      <c r="G69" s="58"/>
+      <c r="G69" s="30"/>
     </row>
     <row r="70" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
@@ -3216,7 +3220,7 @@
         <v>246</v>
       </c>
       <c r="F70" s="32"/>
-      <c r="G70" s="58"/>
+      <c r="G70" s="30"/>
     </row>
     <row r="71" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
@@ -3233,7 +3237,7 @@
         <v>247</v>
       </c>
       <c r="F71" s="32"/>
-      <c r="G71" s="58"/>
+      <c r="G71" s="30"/>
     </row>
     <row r="72" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
@@ -3250,7 +3254,7 @@
         <v>248</v>
       </c>
       <c r="F72" s="32"/>
-      <c r="G72" s="58"/>
+      <c r="G72" s="30"/>
     </row>
     <row r="73" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
@@ -3267,7 +3271,7 @@
         <v>249</v>
       </c>
       <c r="F73" s="32"/>
-      <c r="G73" s="58"/>
+      <c r="G73" s="30"/>
     </row>
     <row r="74" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5">
@@ -3284,7 +3288,7 @@
         <v>250</v>
       </c>
       <c r="F74" s="32"/>
-      <c r="G74" s="58"/>
+      <c r="G74" s="30"/>
     </row>
     <row r="75" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5">
@@ -3301,7 +3305,7 @@
         <v>251</v>
       </c>
       <c r="F75" s="32"/>
-      <c r="G75" s="58"/>
+      <c r="G75" s="30"/>
     </row>
     <row r="76" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
@@ -3318,7 +3322,7 @@
         <v>252</v>
       </c>
       <c r="F76" s="32"/>
-      <c r="G76" s="58"/>
+      <c r="G76" s="30"/>
     </row>
     <row r="77" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
@@ -3335,7 +3339,7 @@
         <v>253</v>
       </c>
       <c r="F77" s="32"/>
-      <c r="G77" s="58"/>
+      <c r="G77" s="30"/>
     </row>
     <row r="78" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
@@ -3352,7 +3356,7 @@
         <v>254</v>
       </c>
       <c r="F78" s="32"/>
-      <c r="G78" s="58"/>
+      <c r="G78" s="30"/>
     </row>
     <row r="79" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
@@ -3369,7 +3373,7 @@
         <v>255</v>
       </c>
       <c r="F79" s="32"/>
-      <c r="G79" s="58"/>
+      <c r="G79" s="30"/>
     </row>
     <row r="80" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
@@ -3386,7 +3390,7 @@
         <v>256</v>
       </c>
       <c r="F80" s="32"/>
-      <c r="G80" s="58"/>
+      <c r="G80" s="30"/>
     </row>
     <row r="81" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
@@ -3403,7 +3407,7 @@
         <v>257</v>
       </c>
       <c r="F81" s="32"/>
-      <c r="G81" s="58"/>
+      <c r="G81" s="30"/>
     </row>
     <row r="82" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
@@ -3420,7 +3424,7 @@
         <v>258</v>
       </c>
       <c r="F82" s="32"/>
-      <c r="G82" s="58"/>
+      <c r="G82" s="30"/>
     </row>
     <row r="83" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
@@ -3437,7 +3441,7 @@
         <v>259</v>
       </c>
       <c r="F83" s="32"/>
-      <c r="G83" s="58"/>
+      <c r="G83" s="30"/>
     </row>
     <row r="84" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="5">
@@ -3454,7 +3458,7 @@
         <v>260</v>
       </c>
       <c r="F84" s="32"/>
-      <c r="G84" s="58"/>
+      <c r="G84" s="30"/>
     </row>
     <row r="85" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
@@ -3471,7 +3475,7 @@
         <v>261</v>
       </c>
       <c r="F85" s="32"/>
-      <c r="G85" s="58"/>
+      <c r="G85" s="30"/>
     </row>
     <row r="86" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="5">
@@ -3488,7 +3492,7 @@
         <v>262</v>
       </c>
       <c r="F86" s="32"/>
-      <c r="G86" s="58"/>
+      <c r="G86" s="30"/>
     </row>
     <row r="87" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
@@ -3505,7 +3509,7 @@
         <v>263</v>
       </c>
       <c r="F87" s="32"/>
-      <c r="G87" s="58"/>
+      <c r="G87" s="30"/>
     </row>
     <row r="88" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="5">
@@ -3522,7 +3526,7 @@
         <v>264</v>
       </c>
       <c r="F88" s="32"/>
-      <c r="G88" s="58"/>
+      <c r="G88" s="30"/>
     </row>
     <row r="89" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
@@ -3539,7 +3543,7 @@
         <v>265</v>
       </c>
       <c r="F89" s="32"/>
-      <c r="G89" s="58"/>
+      <c r="G89" s="30"/>
     </row>
     <row r="90" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="5">
@@ -3556,7 +3560,7 @@
         <v>266</v>
       </c>
       <c r="F90" s="32"/>
-      <c r="G90" s="58"/>
+      <c r="G90" s="30"/>
     </row>
     <row r="91" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
@@ -3573,7 +3577,7 @@
         <v>267</v>
       </c>
       <c r="F91" s="32"/>
-      <c r="G91" s="58"/>
+      <c r="G91" s="30"/>
     </row>
     <row r="92" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="22">
@@ -3590,7 +3594,7 @@
         <v>268</v>
       </c>
       <c r="F92" s="35"/>
-      <c r="G92" s="58"/>
+      <c r="G92" s="30"/>
     </row>
     <row r="93" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="15" t="s">
@@ -3626,7 +3630,7 @@
       <c r="D94" s="23"/>
       <c r="E94" s="46"/>
       <c r="F94" s="31"/>
-      <c r="G94" s="58"/>
+      <c r="G94" s="30"/>
     </row>
     <row r="95" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
@@ -3641,7 +3645,7 @@
       <c r="D95" s="6"/>
       <c r="E95" s="47"/>
       <c r="F95" s="32"/>
-      <c r="G95" s="58"/>
+      <c r="G95" s="30"/>
     </row>
     <row r="96" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="5">
@@ -3656,7 +3660,7 @@
       <c r="D96" s="6"/>
       <c r="E96" s="47"/>
       <c r="F96" s="32"/>
-      <c r="G96" s="58"/>
+      <c r="G96" s="30"/>
     </row>
     <row r="97" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
@@ -3671,7 +3675,7 @@
       <c r="D97" s="6"/>
       <c r="E97" s="47"/>
       <c r="F97" s="32"/>
-      <c r="G97" s="58"/>
+      <c r="G97" s="30"/>
     </row>
     <row r="98" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="5">
@@ -3686,7 +3690,7 @@
       <c r="D98" s="6"/>
       <c r="E98" s="47"/>
       <c r="F98" s="32"/>
-      <c r="G98" s="58"/>
+      <c r="G98" s="30"/>
     </row>
     <row r="99" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
@@ -3701,7 +3705,7 @@
       <c r="D99" s="6"/>
       <c r="E99" s="47"/>
       <c r="F99" s="32"/>
-      <c r="G99" s="58"/>
+      <c r="G99" s="30"/>
     </row>
     <row r="100" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
@@ -3716,7 +3720,7 @@
       <c r="D100" s="6"/>
       <c r="E100" s="47"/>
       <c r="F100" s="32"/>
-      <c r="G100" s="58"/>
+      <c r="G100" s="30"/>
     </row>
     <row r="101" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
@@ -3731,7 +3735,7 @@
       <c r="D101" s="3"/>
       <c r="E101" s="47"/>
       <c r="F101" s="32"/>
-      <c r="G101" s="58"/>
+      <c r="G101" s="30"/>
     </row>
     <row r="102" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
@@ -3746,7 +3750,7 @@
       <c r="D102" s="6"/>
       <c r="E102" s="47"/>
       <c r="F102" s="32"/>
-      <c r="G102" s="58"/>
+      <c r="G102" s="30"/>
     </row>
     <row r="103" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
@@ -3761,7 +3765,7 @@
       <c r="D103" s="6"/>
       <c r="E103" s="47"/>
       <c r="F103" s="32"/>
-      <c r="G103" s="58"/>
+      <c r="G103" s="30"/>
     </row>
     <row r="104" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
@@ -3776,7 +3780,7 @@
       <c r="D104" s="6"/>
       <c r="E104" s="47"/>
       <c r="F104" s="32"/>
-      <c r="G104" s="58"/>
+      <c r="G104" s="30"/>
     </row>
     <row r="105" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
@@ -3791,7 +3795,7 @@
       <c r="D105" s="6"/>
       <c r="E105" s="47"/>
       <c r="F105" s="32"/>
-      <c r="G105" s="58"/>
+      <c r="G105" s="30"/>
     </row>
     <row r="106" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="22">
@@ -3806,7 +3810,7 @@
       <c r="D106" s="24"/>
       <c r="E106" s="48"/>
       <c r="F106" s="35"/>
-      <c r="G106" s="58"/>
+      <c r="G106" s="30"/>
     </row>
     <row r="107" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="15" t="s">
@@ -3844,7 +3848,7 @@
         <v>207</v>
       </c>
       <c r="F108" s="31"/>
-      <c r="G108" s="58"/>
+      <c r="G108" s="30"/>
     </row>
     <row r="109" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="7">
@@ -3861,7 +3865,7 @@
         <v>269</v>
       </c>
       <c r="F109" s="32"/>
-      <c r="G109" s="58"/>
+      <c r="G109" s="30"/>
     </row>
     <row r="110" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="7">
@@ -3878,7 +3882,7 @@
         <v>270</v>
       </c>
       <c r="F110" s="32"/>
-      <c r="G110" s="58"/>
+      <c r="G110" s="30"/>
     </row>
     <row r="111" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="7">
@@ -3895,7 +3899,7 @@
         <v>271</v>
       </c>
       <c r="F111" s="32"/>
-      <c r="G111" s="58"/>
+      <c r="G111" s="30"/>
     </row>
     <row r="112" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="7">
@@ -3912,7 +3916,7 @@
         <v>272</v>
       </c>
       <c r="F112" s="32"/>
-      <c r="G112" s="58"/>
+      <c r="G112" s="30"/>
     </row>
     <row r="113" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="7">
@@ -3929,7 +3933,7 @@
         <v>273</v>
       </c>
       <c r="F113" s="32"/>
-      <c r="G113" s="58"/>
+      <c r="G113" s="30"/>
     </row>
     <row r="114" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="7">
@@ -3946,7 +3950,7 @@
         <v>274</v>
       </c>
       <c r="F114" s="32"/>
-      <c r="G114" s="58"/>
+      <c r="G114" s="30"/>
     </row>
     <row r="115" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="7">
@@ -3963,7 +3967,7 @@
         <v>275</v>
       </c>
       <c r="F115" s="32"/>
-      <c r="G115" s="58"/>
+      <c r="G115" s="30"/>
     </row>
     <row r="116" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="7">
@@ -3980,7 +3984,7 @@
         <v>276</v>
       </c>
       <c r="F116" s="32"/>
-      <c r="G116" s="58"/>
+      <c r="G116" s="30"/>
     </row>
     <row r="117" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="7">
@@ -3997,7 +4001,7 @@
         <v>277</v>
       </c>
       <c r="F117" s="32"/>
-      <c r="G117" s="58"/>
+      <c r="G117" s="30"/>
     </row>
     <row r="118" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="7">
@@ -4014,7 +4018,7 @@
         <v>278</v>
       </c>
       <c r="F118" s="32"/>
-      <c r="G118" s="58"/>
+      <c r="G118" s="30"/>
     </row>
     <row r="119" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="7">
@@ -4031,7 +4035,7 @@
         <v>279</v>
       </c>
       <c r="F119" s="32"/>
-      <c r="G119" s="58"/>
+      <c r="G119" s="30"/>
     </row>
     <row r="120" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="7">
@@ -4048,7 +4052,7 @@
         <v>280</v>
       </c>
       <c r="F120" s="32"/>
-      <c r="G120" s="58"/>
+      <c r="G120" s="30"/>
     </row>
     <row r="121" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="7">
@@ -4065,7 +4069,7 @@
         <v>281</v>
       </c>
       <c r="F121" s="32"/>
-      <c r="G121" s="58"/>
+      <c r="G121" s="30"/>
     </row>
     <row r="122" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="7">
@@ -4082,7 +4086,7 @@
         <v>282</v>
       </c>
       <c r="F122" s="32"/>
-      <c r="G122" s="58"/>
+      <c r="G122" s="30"/>
     </row>
     <row r="123" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="7">
@@ -4099,7 +4103,7 @@
         <v>283</v>
       </c>
       <c r="F123" s="32"/>
-      <c r="G123" s="58"/>
+      <c r="G123" s="30"/>
     </row>
     <row r="124" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="7">
@@ -4116,7 +4120,7 @@
         <v>284</v>
       </c>
       <c r="F124" s="32"/>
-      <c r="G124" s="58"/>
+      <c r="G124" s="30"/>
     </row>
     <row r="125" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="7">
@@ -4133,7 +4137,7 @@
         <v>285</v>
       </c>
       <c r="F125" s="32"/>
-      <c r="G125" s="58"/>
+      <c r="G125" s="30"/>
     </row>
     <row r="126" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="25">
@@ -4152,7 +4156,7 @@
       <c r="F126" s="19" t="s">
         <v>322</v>
       </c>
-      <c r="G126" s="56"/>
+      <c r="G126" s="53"/>
     </row>
     <row r="127" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="15" t="s">
@@ -4190,7 +4194,7 @@
         <v>287</v>
       </c>
       <c r="F128" s="31"/>
-      <c r="G128" s="58"/>
+      <c r="G128" s="30"/>
     </row>
     <row r="129" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="8" t="s">
@@ -4207,7 +4211,7 @@
         <v>288</v>
       </c>
       <c r="F129" s="32"/>
-      <c r="G129" s="58"/>
+      <c r="G129" s="30"/>
     </row>
     <row r="130" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="8" t="s">
@@ -4224,7 +4228,7 @@
         <v>289</v>
       </c>
       <c r="F130" s="32"/>
-      <c r="G130" s="58"/>
+      <c r="G130" s="30"/>
     </row>
     <row r="131" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="8" t="s">
@@ -4241,7 +4245,7 @@
         <v>290</v>
       </c>
       <c r="F131" s="32"/>
-      <c r="G131" s="58"/>
+      <c r="G131" s="30"/>
     </row>
     <row r="132" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="8" t="s">
@@ -4258,7 +4262,7 @@
         <v>291</v>
       </c>
       <c r="F132" s="32"/>
-      <c r="G132" s="58"/>
+      <c r="G132" s="30"/>
     </row>
     <row r="133" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="8" t="s">
@@ -4275,7 +4279,7 @@
         <v>292</v>
       </c>
       <c r="F133" s="32"/>
-      <c r="G133" s="58"/>
+      <c r="G133" s="30"/>
     </row>
     <row r="134" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="8" t="s">
@@ -4292,7 +4296,7 @@
         <v>293</v>
       </c>
       <c r="F134" s="32"/>
-      <c r="G134" s="58"/>
+      <c r="G134" s="30"/>
     </row>
     <row r="135" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="8" t="s">
@@ -4309,7 +4313,7 @@
         <v>294</v>
       </c>
       <c r="F135" s="32"/>
-      <c r="G135" s="58"/>
+      <c r="G135" s="30"/>
     </row>
     <row r="136" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="8" t="s">
@@ -4326,7 +4330,7 @@
         <v>295</v>
       </c>
       <c r="F136" s="32"/>
-      <c r="G136" s="58"/>
+      <c r="G136" s="30"/>
     </row>
     <row r="137" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="8" t="s">
@@ -4343,7 +4347,7 @@
         <v>296</v>
       </c>
       <c r="F137" s="32"/>
-      <c r="G137" s="58"/>
+      <c r="G137" s="30"/>
     </row>
     <row r="138" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="26" t="s">
@@ -4360,7 +4364,7 @@
         <v>297</v>
       </c>
       <c r="F138" s="35"/>
-      <c r="G138" s="58"/>
+      <c r="G138" s="30"/>
     </row>
     <row r="139" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="15" t="s">
@@ -4396,7 +4400,7 @@
       <c r="D140" s="23"/>
       <c r="E140" s="51"/>
       <c r="F140" s="31"/>
-      <c r="G140" s="58"/>
+      <c r="G140" s="30"/>
     </row>
     <row r="141" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="8" t="s">
@@ -4411,7 +4415,7 @@
       <c r="D141" s="6"/>
       <c r="E141" s="47"/>
       <c r="F141" s="32"/>
-      <c r="G141" s="58"/>
+      <c r="G141" s="30"/>
     </row>
     <row r="142" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="8" t="s">
@@ -4426,18 +4430,18 @@
       <c r="D142" s="6"/>
       <c r="E142" s="47"/>
       <c r="F142" s="32"/>
-      <c r="G142" s="58"/>
+      <c r="G142" s="30"/>
     </row>
     <row r="143" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="55" t="s">
+      <c r="A143" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="B143" s="55"/>
-      <c r="C143" s="55"/>
-      <c r="D143" s="55"/>
-      <c r="E143" s="55"/>
-      <c r="F143" s="55"/>
-      <c r="G143" s="61"/>
+      <c r="B143" s="62"/>
+      <c r="C143" s="62"/>
+      <c r="D143" s="62"/>
+      <c r="E143" s="62"/>
+      <c r="F143" s="62"/>
+      <c r="G143" s="57"/>
     </row>
     <row r="144" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="15" t="s">
@@ -4477,7 +4481,7 @@
       <c r="F145" s="37" t="s">
         <v>298</v>
       </c>
-      <c r="G145" s="62"/>
+      <c r="G145" s="58"/>
     </row>
     <row r="146" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
@@ -4494,7 +4498,7 @@
         <v>331</v>
       </c>
       <c r="F146" s="38"/>
-      <c r="G146" s="62"/>
+      <c r="G146" s="58"/>
     </row>
     <row r="147" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
@@ -4513,7 +4517,7 @@
       <c r="F147" s="38" t="s">
         <v>306</v>
       </c>
-      <c r="G147" s="62"/>
+      <c r="G147" s="58"/>
     </row>
     <row r="148" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
@@ -4532,7 +4536,7 @@
       <c r="F148" s="38" t="s">
         <v>301</v>
       </c>
-      <c r="G148" s="62"/>
+      <c r="G148" s="58"/>
     </row>
     <row r="149" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
@@ -4551,7 +4555,7 @@
       <c r="F149" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="G149" s="62"/>
+      <c r="G149" s="58"/>
     </row>
     <row r="150" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
@@ -4568,7 +4572,7 @@
         <v>330</v>
       </c>
       <c r="F150" s="38"/>
-      <c r="G150" s="62"/>
+      <c r="G150" s="58"/>
     </row>
     <row r="151" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
@@ -4587,7 +4591,7 @@
       <c r="F151" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="G151" s="62"/>
+      <c r="G151" s="58"/>
     </row>
     <row r="152" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
@@ -4606,7 +4610,7 @@
       <c r="F152" s="38" t="s">
         <v>313</v>
       </c>
-      <c r="G152" s="62"/>
+      <c r="G152" s="58"/>
     </row>
     <row r="153" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
@@ -4625,7 +4629,7 @@
       <c r="F153" s="38" t="s">
         <v>307</v>
       </c>
-      <c r="G153" s="62"/>
+      <c r="G153" s="58"/>
     </row>
     <row r="154" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
@@ -4644,7 +4648,7 @@
       <c r="F154" s="39" t="s">
         <v>321</v>
       </c>
-      <c r="G154" s="63"/>
+      <c r="G154" s="59"/>
     </row>
     <row r="155" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
@@ -4663,7 +4667,7 @@
       <c r="F155" s="38" t="s">
         <v>308</v>
       </c>
-      <c r="G155" s="62"/>
+      <c r="G155" s="58"/>
     </row>
     <row r="156" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
@@ -4682,7 +4686,7 @@
       <c r="F156" s="38" t="s">
         <v>309</v>
       </c>
-      <c r="G156" s="62"/>
+      <c r="G156" s="58"/>
     </row>
     <row r="157" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
@@ -4701,7 +4705,7 @@
       <c r="F157" s="38" t="s">
         <v>319</v>
       </c>
-      <c r="G157" s="62"/>
+      <c r="G157" s="58"/>
     </row>
     <row r="158" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
@@ -4720,7 +4724,7 @@
       <c r="F158" s="38" t="s">
         <v>310</v>
       </c>
-      <c r="G158" s="62"/>
+      <c r="G158" s="58"/>
     </row>
     <row r="159" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
@@ -4737,7 +4741,7 @@
         <v>330</v>
       </c>
       <c r="F159" s="38"/>
-      <c r="G159" s="62"/>
+      <c r="G159" s="58"/>
     </row>
     <row r="160" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
@@ -4756,7 +4760,7 @@
       <c r="F160" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="G160" s="62"/>
+      <c r="G160" s="58"/>
     </row>
     <row r="161" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
@@ -4792,7 +4796,7 @@
         <v>330</v>
       </c>
       <c r="F162" s="38"/>
-      <c r="G162" s="62"/>
+      <c r="G162" s="58"/>
     </row>
     <row r="163" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
@@ -4811,7 +4815,7 @@
       <c r="F163" s="39" t="s">
         <v>302</v>
       </c>
-      <c r="G163" s="63"/>
+      <c r="G163" s="59"/>
     </row>
     <row r="164" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
@@ -4830,7 +4834,7 @@
       <c r="F164" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="G164" s="63"/>
+      <c r="G164" s="59"/>
     </row>
     <row r="165" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
@@ -4849,7 +4853,7 @@
       <c r="F165" s="38" t="s">
         <v>312</v>
       </c>
-      <c r="G165" s="62"/>
+      <c r="G165" s="58"/>
     </row>
     <row r="166" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
@@ -4866,7 +4870,7 @@
         <v>330</v>
       </c>
       <c r="F166" s="38"/>
-      <c r="G166" s="62"/>
+      <c r="G166" s="58"/>
     </row>
     <row r="167" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
@@ -4885,7 +4889,7 @@
       <c r="F167" s="38" t="s">
         <v>305</v>
       </c>
-      <c r="G167" s="62"/>
+      <c r="G167" s="58"/>
     </row>
     <row r="168" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
@@ -4904,7 +4908,7 @@
       <c r="F168" s="38" t="s">
         <v>315</v>
       </c>
-      <c r="G168" s="62"/>
+      <c r="G168" s="58"/>
     </row>
     <row r="169" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
@@ -4923,7 +4927,7 @@
       <c r="F169" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="G169" s="63"/>
+      <c r="G169" s="59"/>
     </row>
     <row r="170" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
@@ -4942,7 +4946,7 @@
       <c r="F170" s="39" t="s">
         <v>304</v>
       </c>
-      <c r="G170" s="63"/>
+      <c r="G170" s="59"/>
     </row>
     <row r="171" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
@@ -4961,7 +4965,7 @@
       <c r="F171" s="38" t="s">
         <v>311</v>
       </c>
-      <c r="G171" s="62"/>
+      <c r="G171" s="58"/>
     </row>
     <row r="172" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
@@ -4978,7 +4982,7 @@
         <v>330</v>
       </c>
       <c r="F172" s="38"/>
-      <c r="G172" s="62"/>
+      <c r="G172" s="58"/>
     </row>
     <row r="173" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
@@ -4997,7 +5001,7 @@
       <c r="F173" s="38" t="s">
         <v>299</v>
       </c>
-      <c r="G173" s="62"/>
+      <c r="G173" s="58"/>
     </row>
     <row r="174" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
@@ -5014,7 +5018,7 @@
         <v>330</v>
       </c>
       <c r="F174" s="38"/>
-      <c r="G174" s="62"/>
+      <c r="G174" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/docs/Homes List.xlsx
+++ b/docs/Homes List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9df306d6984b8b22/Documents/GitHub/Wix-Products/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="465" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF1763A6-4735-4032-B8CE-865778A9227A}"/>
+  <xr:revisionPtr revIDLastSave="468" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69801E01-C8AC-4C98-8B6C-6AB7D990345B}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5390" yWindow="2510" windowWidth="28800" windowHeight="15380" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
+    <workbookView minimized="1" xWindow="4030" yWindow="5820" windowWidth="21600" windowHeight="11180" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="337">
   <si>
     <t xml:space="preserve">Golden West </t>
   </si>
@@ -1236,6 +1236,15 @@
   </si>
   <si>
     <t>https://my.matterport.com/show/?play=1&amp;m=Mac4ayKuY7Q</t>
+  </si>
+  <si>
+    <t>https://my.matterport.com/show/?play=1&amp;m=2x2j67hzTCR</t>
+  </si>
+  <si>
+    <t>https://my.matterport.com/show/?play=1&amp;m=Kz6t3R9fUnF</t>
+  </si>
+  <si>
+    <t>https://my.matterport.com/show/?play=1&amp;m=tiab2vCfpyE</t>
   </si>
 </sst>
 </file>
@@ -1471,7 +1480,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1623,6 +1632,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -3305,7 +3315,9 @@
         <v>251</v>
       </c>
       <c r="F75" s="32"/>
-      <c r="G75" s="30"/>
+      <c r="G75" s="63" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="76" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
@@ -3356,7 +3368,9 @@
         <v>254</v>
       </c>
       <c r="F78" s="32"/>
-      <c r="G78" s="30"/>
+      <c r="G78" s="63" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="79" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
@@ -3373,7 +3387,9 @@
         <v>255</v>
       </c>
       <c r="F79" s="32"/>
-      <c r="G79" s="30"/>
+      <c r="G79" s="63" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="80" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
@@ -5115,6 +5131,9 @@
     <hyperlink ref="E145" r:id="rId86" xr:uid="{95272B36-1B3E-4E9F-A78F-B49AAE3263D2}"/>
     <hyperlink ref="E146:E174" r:id="rId87" display="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Imagine.pdf" xr:uid="{D958AEE0-FAA3-4065-B126-6557F87E05A9}"/>
     <hyperlink ref="E146" r:id="rId88" xr:uid="{43838F99-75E5-4924-A97E-2531FB82672F}"/>
+    <hyperlink ref="G75" r:id="rId89" xr:uid="{2F0FFC39-FD18-42E2-A35A-72A93D0CB54F}"/>
+    <hyperlink ref="G79" r:id="rId90" xr:uid="{AB99604A-9B64-4E9F-A814-DD4D254AE437}"/>
+    <hyperlink ref="G78" r:id="rId91" xr:uid="{B129DBCD-C2C6-4DA8-8342-404C0108A695}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Homes List.xlsx
+++ b/docs/Homes List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9df306d6984b8b22/Documents/GitHub/Wix-Products/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="468" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69801E01-C8AC-4C98-8B6C-6AB7D990345B}"/>
+  <xr:revisionPtr revIDLastSave="476" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{188A2EEA-931E-4939-821E-FBA4B69AA8C4}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4030" yWindow="5820" windowWidth="21600" windowHeight="11180" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="341">
   <si>
     <t xml:space="preserve">Golden West </t>
   </si>
@@ -1245,6 +1245,18 @@
   </si>
   <si>
     <t>https://my.matterport.com/show/?play=1&amp;m=tiab2vCfpyE</t>
+  </si>
+  <si>
+    <t>https://my.matterport.com/show/?play=1&amp;m=2g4gQmXvmHf</t>
+  </si>
+  <si>
+    <t>https://my.matterport.com/show/?play=1&amp;m=933JpxWncFA</t>
+  </si>
+  <si>
+    <t>https://my.matterport.com/show/?play=1&amp;m=KoFoJy1tD99</t>
+  </si>
+  <si>
+    <t>https://my.matterport.com/show/?play=1&amp;m=YCj14AZVvoU</t>
   </si>
 </sst>
 </file>
@@ -1623,6 +1635,7 @@
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1632,7 +1645,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -2001,12 +2013,12 @@
   <dimension ref="A1:H174"/>
   <sheetFormatPr defaultRowHeight="19" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.26953125" customWidth="1"/>
+    <col min="1" max="1" width="25.36328125" customWidth="1"/>
     <col min="2" max="2" width="4.26953125" customWidth="1"/>
-    <col min="3" max="3" width="9.90625" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" customWidth="1"/>
     <col min="4" max="4" width="2.1796875" customWidth="1"/>
-    <col min="5" max="5" width="93.81640625" customWidth="1"/>
-    <col min="6" max="6" width="70.453125" customWidth="1"/>
+    <col min="5" max="5" width="78.7265625" customWidth="1"/>
+    <col min="6" max="6" width="50.1796875" customWidth="1"/>
     <col min="7" max="7" width="52.90625" customWidth="1"/>
     <col min="8" max="8" width="11.26953125" customWidth="1"/>
   </cols>
@@ -2038,14 +2050,14 @@
       <c r="G2" s="30"/>
     </row>
     <row r="3" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
       <c r="G3" s="52"/>
     </row>
     <row r="4" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -3080,14 +3092,14 @@
       <c r="G61" s="30"/>
     </row>
     <row r="62" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="61" t="s">
+      <c r="A62" s="62" t="s">
         <v>59</v>
       </c>
-      <c r="B62" s="61"/>
-      <c r="C62" s="61"/>
-      <c r="D62" s="61"/>
-      <c r="E62" s="61"/>
-      <c r="F62" s="61"/>
+      <c r="B62" s="62"/>
+      <c r="C62" s="62"/>
+      <c r="D62" s="62"/>
+      <c r="E62" s="62"/>
+      <c r="F62" s="62"/>
       <c r="G62" s="56"/>
     </row>
     <row r="63" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -3315,7 +3327,7 @@
         <v>251</v>
       </c>
       <c r="F75" s="32"/>
-      <c r="G75" s="63" t="s">
+      <c r="G75" s="60" t="s">
         <v>334</v>
       </c>
     </row>
@@ -3368,7 +3380,7 @@
         <v>254</v>
       </c>
       <c r="F78" s="32"/>
-      <c r="G78" s="63" t="s">
+      <c r="G78" s="60" t="s">
         <v>336</v>
       </c>
     </row>
@@ -3387,7 +3399,7 @@
         <v>255</v>
       </c>
       <c r="F79" s="32"/>
-      <c r="G79" s="63" t="s">
+      <c r="G79" s="60" t="s">
         <v>335</v>
       </c>
     </row>
@@ -4244,7 +4256,9 @@
         <v>289</v>
       </c>
       <c r="F130" s="32"/>
-      <c r="G130" s="30"/>
+      <c r="G130" s="60" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="131" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="8" t="s">
@@ -4261,7 +4275,9 @@
         <v>290</v>
       </c>
       <c r="F131" s="32"/>
-      <c r="G131" s="30"/>
+      <c r="G131" s="60" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="132" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="8" t="s">
@@ -4278,7 +4294,9 @@
         <v>291</v>
       </c>
       <c r="F132" s="32"/>
-      <c r="G132" s="30"/>
+      <c r="G132" s="60" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="133" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="8" t="s">
@@ -4295,7 +4313,9 @@
         <v>292</v>
       </c>
       <c r="F133" s="32"/>
-      <c r="G133" s="30"/>
+      <c r="G133" s="60" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="134" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="8" t="s">
@@ -4449,14 +4469,14 @@
       <c r="G142" s="30"/>
     </row>
     <row r="143" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="62" t="s">
+      <c r="A143" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="B143" s="62"/>
-      <c r="C143" s="62"/>
-      <c r="D143" s="62"/>
-      <c r="E143" s="62"/>
-      <c r="F143" s="62"/>
+      <c r="B143" s="63"/>
+      <c r="C143" s="63"/>
+      <c r="D143" s="63"/>
+      <c r="E143" s="63"/>
+      <c r="F143" s="63"/>
       <c r="G143" s="57"/>
     </row>
     <row r="144" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -5134,6 +5154,10 @@
     <hyperlink ref="G75" r:id="rId89" xr:uid="{2F0FFC39-FD18-42E2-A35A-72A93D0CB54F}"/>
     <hyperlink ref="G79" r:id="rId90" xr:uid="{AB99604A-9B64-4E9F-A814-DD4D254AE437}"/>
     <hyperlink ref="G78" r:id="rId91" xr:uid="{B129DBCD-C2C6-4DA8-8342-404C0108A695}"/>
+    <hyperlink ref="G130" r:id="rId92" xr:uid="{C6D7B5EE-9444-4217-8255-0989F4C2A972}"/>
+    <hyperlink ref="G133" r:id="rId93" xr:uid="{4C4DD5E8-6291-4B28-B0C2-0AAD57143E00}"/>
+    <hyperlink ref="G131" r:id="rId94" xr:uid="{B88FC6B3-5EEF-4DFD-B2AD-4CC0466B9506}"/>
+    <hyperlink ref="G132" r:id="rId95" xr:uid="{DB565809-20B2-4A11-860A-11B4868E1FBB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Homes List.xlsx
+++ b/docs/Homes List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9df306d6984b8b22/Documents/GitHub/Wix-Products/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="476" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{188A2EEA-931E-4939-821E-FBA4B69AA8C4}"/>
+  <xr:revisionPtr revIDLastSave="531" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08B87910-23E2-4EF9-AF13-3BE3284A6A1E}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="365">
   <si>
     <t xml:space="preserve">Golden West </t>
   </si>
@@ -854,9 +854,6 @@
     <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/DRM/711F.pdf</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/362A.pdf</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Imagine/5015.pdf</t>
   </si>
   <si>
@@ -1257,6 +1254,85 @@
   </si>
   <si>
     <t>https://my.matterport.com/show/?play=1&amp;m=YCj14AZVvoU</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING362A.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING361F.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING382F.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING485F.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING486F.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING524F.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING525F.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING561F.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING563F.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING564F.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING565F.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING605F.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING662F.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING681F.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING684F.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING762G.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING764G.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING601K.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING602K.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING621K.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING682K.pdf</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING362A.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://my.matterport.com/show/?play=1&amp;m=MgaR4onYsZB" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="</t>
+  </si>
+  <si>
+    <t>" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="</t>
+  </si>
+  <si>
+    <t>" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
   </si>
 </sst>
 </file>
@@ -1380,7 +1456,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1400,6 +1476,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1492,7 +1574,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1600,7 +1682,6 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
@@ -1644,6 +1725,11 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1990,7 +2076,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="525" row="2">
+  <wetp:taskpane dockstate="right" visibility="0" width="525" row="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2010,17 +2096,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69257E43-B717-415B-87B6-EDDB262DB689}">
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:Q174"/>
   <sheetFormatPr defaultRowHeight="19" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.36328125" customWidth="1"/>
     <col min="2" max="2" width="4.26953125" customWidth="1"/>
     <col min="3" max="3" width="7.1796875" customWidth="1"/>
     <col min="4" max="4" width="2.1796875" customWidth="1"/>
-    <col min="5" max="5" width="78.7265625" customWidth="1"/>
+    <col min="5" max="5" width="87" customWidth="1"/>
     <col min="6" max="6" width="50.1796875" customWidth="1"/>
     <col min="7" max="7" width="52.90625" customWidth="1"/>
     <col min="8" max="8" width="11.26953125" customWidth="1"/>
+    <col min="12" max="12" width="162.54296875" customWidth="1"/>
+    <col min="13" max="13" width="79.08984375" customWidth="1"/>
+    <col min="14" max="14" width="54" customWidth="1"/>
+    <col min="15" max="15" width="58.54296875" customWidth="1"/>
+    <col min="17" max="17" width="79.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -2032,7 +2123,7 @@
         <v>168</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G1" s="30"/>
     </row>
@@ -2042,23 +2133,23 @@
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
       <c r="E2" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="F2" s="30" t="s">
-        <v>211</v>
-      </c>
       <c r="G2" s="30"/>
     </row>
     <row r="3" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="52"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="51"/>
     </row>
     <row r="4" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
@@ -2075,10 +2166,10 @@
         <v>168</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H4" t="s">
         <v>172</v>
@@ -2099,9 +2190,9 @@
         <v>170</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="G5" s="53"/>
+        <v>221</v>
+      </c>
+      <c r="G5" s="52"/>
     </row>
     <row r="6" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
@@ -2116,9 +2207,9 @@
       <c r="D6" s="3"/>
       <c r="E6" s="42"/>
       <c r="F6" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="G6" s="53"/>
+        <v>213</v>
+      </c>
+      <c r="G6" s="52"/>
       <c r="H6" t="s">
         <v>174</v>
       </c>
@@ -2138,9 +2229,9 @@
         <v>171</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="G7" s="53"/>
+        <v>223</v>
+      </c>
+      <c r="G7" s="52"/>
       <c r="H7" t="s">
         <v>173</v>
       </c>
@@ -2160,7 +2251,7 @@
         <v>175</v>
       </c>
       <c r="F8" s="34"/>
-      <c r="G8" s="54"/>
+      <c r="G8" s="53"/>
     </row>
     <row r="9" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
@@ -2177,7 +2268,7 @@
         <v>176</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G9" s="30"/>
     </row>
@@ -2196,9 +2287,9 @@
         <v>177</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="G10" s="55"/>
+        <v>208</v>
+      </c>
+      <c r="G10" s="54"/>
     </row>
     <row r="11" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
@@ -2249,7 +2340,7 @@
         <v>180</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G13" s="30"/>
     </row>
@@ -2285,7 +2376,7 @@
         <v>169</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G15" s="30"/>
     </row>
@@ -2321,7 +2412,7 @@
         <v>183</v>
       </c>
       <c r="F17" s="32" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G17" s="30"/>
     </row>
@@ -2374,7 +2465,7 @@
         <v>186</v>
       </c>
       <c r="F20" s="32" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G20" s="30"/>
     </row>
@@ -2393,7 +2484,7 @@
         <v>187</v>
       </c>
       <c r="F21" s="32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G21" s="30"/>
     </row>
@@ -2446,9 +2537,9 @@
         <v>190</v>
       </c>
       <c r="F24" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="G24" s="55"/>
+        <v>225</v>
+      </c>
+      <c r="G24" s="54"/>
     </row>
     <row r="25" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
@@ -2465,7 +2556,7 @@
         <v>191</v>
       </c>
       <c r="F25" s="32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G25" s="30"/>
     </row>
@@ -2484,7 +2575,7 @@
         <v>192</v>
       </c>
       <c r="F26" s="32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G26" s="30"/>
     </row>
@@ -2503,9 +2594,9 @@
         <v>193</v>
       </c>
       <c r="F27" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="G27" s="55"/>
+        <v>226</v>
+      </c>
+      <c r="G27" s="54"/>
     </row>
     <row r="28" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
@@ -2522,7 +2613,7 @@
         <v>194</v>
       </c>
       <c r="F28" s="32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G28" s="30"/>
     </row>
@@ -2541,7 +2632,7 @@
         <v>195</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G29" s="30"/>
     </row>
@@ -2560,9 +2651,9 @@
         <v>196</v>
       </c>
       <c r="F30" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="G30" s="55"/>
+        <v>229</v>
+      </c>
+      <c r="G30" s="54"/>
     </row>
     <row r="31" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
@@ -2598,7 +2689,7 @@
       <c r="F32" s="32"/>
       <c r="G32" s="30"/>
     </row>
-    <row r="33" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
@@ -2613,11 +2704,11 @@
         <v>199</v>
       </c>
       <c r="F33" s="32" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G33" s="30"/>
     </row>
-    <row r="34" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,11 +2723,11 @@
         <v>200</v>
       </c>
       <c r="F34" s="32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G34" s="30"/>
     </row>
-    <row r="35" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
@@ -2653,7 +2744,7 @@
       <c r="F35" s="32"/>
       <c r="G35" s="30"/>
     </row>
-    <row r="36" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
@@ -2668,11 +2759,11 @@
         <v>202</v>
       </c>
       <c r="F36" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="G36" s="55"/>
-    </row>
-    <row r="37" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+      <c r="G36" s="54"/>
+    </row>
+    <row r="37" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
@@ -2689,7 +2780,7 @@
       <c r="F37" s="32"/>
       <c r="G37" s="30"/>
     </row>
-    <row r="38" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -2704,11 +2795,11 @@
         <v>204</v>
       </c>
       <c r="F38" s="32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G38" s="30"/>
     </row>
-    <row r="39" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="16" t="s">
         <v>37</v>
       </c>
@@ -2723,11 +2814,11 @@
         <v>205</v>
       </c>
       <c r="F39" s="35" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G39" s="30"/>
     </row>
-    <row r="40" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="15" t="s">
         <v>72</v>
       </c>
@@ -2742,13 +2833,13 @@
         <v>168</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="20" t="s">
         <v>38</v>
       </c>
@@ -2759,15 +2850,33 @@
         <v>852</v>
       </c>
       <c r="D41" s="13"/>
-      <c r="E41" s="45" t="s">
-        <v>206</v>
+      <c r="E41" s="63" t="s">
+        <v>340</v>
       </c>
       <c r="F41" s="31"/>
-      <c r="G41" s="30" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G41" s="59" t="s">
+        <v>323</v>
+      </c>
+      <c r="L41" s="65" t="s">
+        <v>361</v>
+      </c>
+      <c r="M41" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N41" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O41" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q41" t="str">
+        <f>M41&amp;E41&amp;N41&amp;G41&amp;O41</f>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING362A.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://my.matterport.com/show/?play=1&amp;m=MgaR4onYsZB" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>39</v>
       </c>
@@ -2778,13 +2887,31 @@
         <v>958</v>
       </c>
       <c r="D42" s="3"/>
-      <c r="E42" s="32"/>
+      <c r="E42" s="32" t="s">
+        <v>341</v>
+      </c>
       <c r="F42" s="32"/>
       <c r="G42" s="30" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+      <c r="L42" s="64"/>
+      <c r="M42" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N42" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O42" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q42" t="str">
+        <f t="shared" ref="Q42:Q61" si="0">M42&amp;E42&amp;N42&amp;G42&amp;O42</f>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING361F.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://my.matterport.com/show/?play=1&amp;m=Mac4ayKuY7Q" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>40</v>
       </c>
@@ -2795,15 +2922,33 @@
         <v>1026</v>
       </c>
       <c r="D43" s="3"/>
-      <c r="E43" s="32"/>
+      <c r="E43" s="32" t="s">
+        <v>342</v>
+      </c>
       <c r="F43" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="G43" s="53" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+      <c r="G43" s="52" t="s">
+        <v>324</v>
+      </c>
+      <c r="L43" s="64"/>
+      <c r="M43" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N43" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O43" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q43" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING382F.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://my.matterport.com/show/?play=1&amp;m=fKycYYa7n6n" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>41</v>
       </c>
@@ -2814,11 +2959,29 @@
         <v>1296</v>
       </c>
       <c r="D44" s="3"/>
-      <c r="E44" s="32"/>
+      <c r="E44" s="32" t="s">
+        <v>343</v>
+      </c>
       <c r="F44" s="32"/>
       <c r="G44" s="30"/>
-    </row>
-    <row r="45" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L44" s="64"/>
+      <c r="M44" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N44" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O44" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q44" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING485F.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>42</v>
       </c>
@@ -2829,13 +2992,31 @@
         <v>1296</v>
       </c>
       <c r="D45" s="3"/>
-      <c r="E45" s="32"/>
+      <c r="E45" s="32" t="s">
+        <v>344</v>
+      </c>
       <c r="F45" s="32"/>
       <c r="G45" s="30" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+        <v>325</v>
+      </c>
+      <c r="L45" s="64"/>
+      <c r="M45" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N45" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O45" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q45" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING486F.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://my.matterport.com/show?play=1&amp;lang=en-US&amp;m=DaQBmJEBKY6" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>43</v>
       </c>
@@ -2846,13 +3027,31 @@
         <v>1404</v>
       </c>
       <c r="D46" s="3"/>
-      <c r="E46" s="32"/>
+      <c r="E46" s="32" t="s">
+        <v>345</v>
+      </c>
       <c r="F46" s="32" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G46" s="30"/>
-    </row>
-    <row r="47" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L46" s="64"/>
+      <c r="M46" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N46" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O46" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q46" t="str">
+        <f>M46&amp;E46&amp;N46&amp;F46&amp;O46</f>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING524F.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/e5c1afd139f44056a111566c62a66a91" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>44</v>
       </c>
@@ -2863,11 +3062,29 @@
         <v>1404</v>
       </c>
       <c r="D47" s="3"/>
-      <c r="E47" s="32"/>
+      <c r="E47" s="32" t="s">
+        <v>346</v>
+      </c>
       <c r="F47" s="32"/>
       <c r="G47" s="30"/>
-    </row>
-    <row r="48" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L47" s="64"/>
+      <c r="M47" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N47" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O47" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q47" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING525F.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>45</v>
       </c>
@@ -2878,15 +3095,33 @@
         <v>1512</v>
       </c>
       <c r="D48" s="3"/>
-      <c r="E48" s="32"/>
+      <c r="E48" s="32" t="s">
+        <v>347</v>
+      </c>
       <c r="F48" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G48" s="30" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+        <v>326</v>
+      </c>
+      <c r="L48" s="64"/>
+      <c r="M48" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N48" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O48" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q48" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING561F.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://my.matterport.com/show/?play=1&amp;m=iUG3qkNrKfa" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>46</v>
       </c>
@@ -2897,11 +3132,29 @@
         <v>1512</v>
       </c>
       <c r="D49" s="3"/>
-      <c r="E49" s="32"/>
+      <c r="E49" s="32" t="s">
+        <v>348</v>
+      </c>
       <c r="F49" s="32"/>
       <c r="G49" s="30"/>
-    </row>
-    <row r="50" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L49" s="64"/>
+      <c r="M49" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N49" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O49" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q49" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING563F.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>47</v>
       </c>
@@ -2912,13 +3165,31 @@
         <v>1512</v>
       </c>
       <c r="D50" s="3"/>
-      <c r="E50" s="32"/>
+      <c r="E50" s="32" t="s">
+        <v>349</v>
+      </c>
       <c r="F50" s="33" t="s">
-        <v>238</v>
-      </c>
-      <c r="G50" s="55"/>
-    </row>
-    <row r="51" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="G50" s="54"/>
+      <c r="L50" s="64"/>
+      <c r="M50" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N50" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O50" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q50" t="str">
+        <f>M50&amp;E50&amp;N50&amp;F50&amp;O50</f>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING564F.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/d4eebf0274f4454fa5f84f43c9d45ba3" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>48</v>
       </c>
@@ -2929,11 +3200,29 @@
         <v>1512</v>
       </c>
       <c r="D51" s="3"/>
-      <c r="E51" s="32"/>
+      <c r="E51" s="32" t="s">
+        <v>350</v>
+      </c>
       <c r="F51" s="32"/>
       <c r="G51" s="30"/>
-    </row>
-    <row r="52" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L51" s="64"/>
+      <c r="M51" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N51" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O51" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q51" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING565F.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>49</v>
       </c>
@@ -2944,13 +3233,31 @@
         <v>1620</v>
       </c>
       <c r="D52" s="3"/>
-      <c r="E52" s="32"/>
+      <c r="E52" s="32" t="s">
+        <v>351</v>
+      </c>
       <c r="F52" s="32"/>
-      <c r="G52" s="53" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G52" s="52" t="s">
+        <v>327</v>
+      </c>
+      <c r="L52" s="64"/>
+      <c r="M52" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N52" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O52" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q52" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING605F.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://my.matterport.com/show/?play=1&amp;m=QkyD1Gqr67p" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>50</v>
       </c>
@@ -2961,11 +3268,29 @@
         <v>1782</v>
       </c>
       <c r="D53" s="3"/>
-      <c r="E53" s="32"/>
+      <c r="E53" s="32" t="s">
+        <v>352</v>
+      </c>
       <c r="F53" s="32"/>
       <c r="G53" s="30"/>
-    </row>
-    <row r="54" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L53" s="64"/>
+      <c r="M53" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N53" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O53" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q53" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING662F.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>51</v>
       </c>
@@ -2976,13 +3301,31 @@
         <v>1836</v>
       </c>
       <c r="D54" s="3"/>
-      <c r="E54" s="32"/>
+      <c r="E54" s="32" t="s">
+        <v>353</v>
+      </c>
       <c r="F54" s="32" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G54" s="30"/>
-    </row>
-    <row r="55" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L54" s="64"/>
+      <c r="M54" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N54" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O54" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q54" t="str">
+        <f>M54&amp;E54&amp;N54&amp;F54&amp;O54</f>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING681F.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/82c50572b7cb4955a9e8bd9223e45cf0" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>52</v>
       </c>
@@ -2993,11 +3336,29 @@
         <v>1836</v>
       </c>
       <c r="D55" s="3"/>
-      <c r="E55" s="32"/>
+      <c r="E55" s="32" t="s">
+        <v>354</v>
+      </c>
       <c r="F55" s="32"/>
       <c r="G55" s="30"/>
-    </row>
-    <row r="56" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L55" s="64"/>
+      <c r="M55" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N55" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O55" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q55" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING684F.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>53</v>
       </c>
@@ -3008,13 +3369,31 @@
         <v>2280</v>
       </c>
       <c r="D56" s="3"/>
-      <c r="E56" s="32"/>
+      <c r="E56" s="32" t="s">
+        <v>355</v>
+      </c>
       <c r="F56" s="32"/>
       <c r="G56" s="30" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+        <v>328</v>
+      </c>
+      <c r="L56" s="64"/>
+      <c r="M56" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N56" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O56" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q56" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING762G.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://my.matterport.com/show/?m=o6SZeYvAzTd" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>54</v>
       </c>
@@ -3025,11 +3404,29 @@
         <v>2280</v>
       </c>
       <c r="D57" s="3"/>
-      <c r="E57" s="32"/>
+      <c r="E57" s="32" t="s">
+        <v>356</v>
+      </c>
       <c r="F57" s="32"/>
       <c r="G57" s="30"/>
-    </row>
-    <row r="58" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L57" s="64"/>
+      <c r="M57" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N57" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O57" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q57" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING764G.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>55</v>
       </c>
@@ -3040,11 +3437,29 @@
         <v>2347</v>
       </c>
       <c r="D58" s="3"/>
-      <c r="E58" s="32"/>
+      <c r="E58" s="32" t="s">
+        <v>357</v>
+      </c>
       <c r="F58" s="32"/>
       <c r="G58" s="30"/>
-    </row>
-    <row r="59" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L58" s="64"/>
+      <c r="M58" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N58" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O58" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q58" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING601K.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>56</v>
       </c>
@@ -3055,11 +3470,29 @@
         <v>2347</v>
       </c>
       <c r="D59" s="3"/>
-      <c r="E59" s="32"/>
+      <c r="E59" s="32" t="s">
+        <v>358</v>
+      </c>
       <c r="F59" s="32"/>
       <c r="G59" s="30"/>
-    </row>
-    <row r="60" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L59" s="64"/>
+      <c r="M59" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N59" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O59" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q59" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING602K.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>57</v>
       </c>
@@ -3070,13 +3503,31 @@
         <v>2038</v>
       </c>
       <c r="D60" s="3"/>
-      <c r="E60" s="32"/>
+      <c r="E60" s="32" t="s">
+        <v>359</v>
+      </c>
       <c r="F60" s="32" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G60" s="30"/>
-    </row>
-    <row r="61" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L60" s="64"/>
+      <c r="M60" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N60" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O60" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q60" t="str">
+        <f>M60&amp;E60&amp;N60&amp;F60&amp;O60</f>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING621K.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/3d33004720554c6c96b4f5dfbb605b25" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>58</v>
       </c>
@@ -3087,22 +3538,43 @@
         <v>2654</v>
       </c>
       <c r="D61" s="3"/>
-      <c r="E61" s="32"/>
+      <c r="E61" s="32" t="s">
+        <v>360</v>
+      </c>
       <c r="F61" s="32"/>
       <c r="G61" s="30"/>
-    </row>
-    <row r="62" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="62" t="s">
+      <c r="L61" s="64"/>
+      <c r="M61" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="N61" s="65" t="s">
+        <v>363</v>
+      </c>
+      <c r="O61" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q61" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/ING/ING682K.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="B62" s="62"/>
-      <c r="C62" s="62"/>
-      <c r="D62" s="62"/>
-      <c r="E62" s="62"/>
-      <c r="F62" s="62"/>
-      <c r="G62" s="56"/>
-    </row>
-    <row r="63" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="61"/>
+      <c r="C62" s="61"/>
+      <c r="D62" s="61"/>
+      <c r="E62" s="61"/>
+      <c r="F62" s="61"/>
+      <c r="G62" s="55"/>
+      <c r="L62" s="64"/>
+      <c r="M62" s="63"/>
+      <c r="N62" s="64"/>
+    </row>
+    <row r="63" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="15" t="s">
         <v>72</v>
       </c>
@@ -3117,13 +3589,13 @@
         <v>168</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G63" s="15" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="21">
         <v>1001</v>
       </c>
@@ -3135,11 +3607,11 @@
       </c>
       <c r="D64" s="13"/>
       <c r="E64" s="41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F64" s="31"/>
       <c r="G64" s="30" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -3154,7 +3626,7 @@
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="41" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F65" s="32"/>
       <c r="G65" s="30"/>
@@ -3171,7 +3643,7 @@
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F66" s="32"/>
       <c r="G66" s="30"/>
@@ -3188,7 +3660,7 @@
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="41" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F67" s="32"/>
       <c r="G67" s="30"/>
@@ -3205,7 +3677,7 @@
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F68" s="32"/>
       <c r="G68" s="30"/>
@@ -3222,7 +3694,7 @@
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F69" s="32"/>
       <c r="G69" s="30"/>
@@ -3239,7 +3711,7 @@
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="41" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F70" s="32"/>
       <c r="G70" s="30"/>
@@ -3256,7 +3728,7 @@
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="41" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F71" s="32"/>
       <c r="G71" s="30"/>
@@ -3273,7 +3745,7 @@
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="41" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F72" s="32"/>
       <c r="G72" s="30"/>
@@ -3290,7 +3762,7 @@
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="41" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F73" s="32"/>
       <c r="G73" s="30"/>
@@ -3307,7 +3779,7 @@
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="41" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F74" s="32"/>
       <c r="G74" s="30"/>
@@ -3324,11 +3796,11 @@
       </c>
       <c r="D75" s="6"/>
       <c r="E75" s="41" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F75" s="32"/>
-      <c r="G75" s="60" t="s">
-        <v>334</v>
+      <c r="G75" s="59" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -3343,7 +3815,7 @@
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="41" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F76" s="32"/>
       <c r="G76" s="30"/>
@@ -3360,7 +3832,7 @@
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="41" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F77" s="32"/>
       <c r="G77" s="30"/>
@@ -3377,11 +3849,11 @@
       </c>
       <c r="D78" s="6"/>
       <c r="E78" s="41" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F78" s="32"/>
-      <c r="G78" s="60" t="s">
-        <v>336</v>
+      <c r="G78" s="59" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -3396,11 +3868,11 @@
       </c>
       <c r="D79" s="6"/>
       <c r="E79" s="41" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F79" s="32"/>
-      <c r="G79" s="60" t="s">
-        <v>335</v>
+      <c r="G79" s="59" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -3415,7 +3887,7 @@
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="41" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F80" s="32"/>
       <c r="G80" s="30"/>
@@ -3432,7 +3904,7 @@
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F81" s="32"/>
       <c r="G81" s="30"/>
@@ -3449,7 +3921,7 @@
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="41" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F82" s="32"/>
       <c r="G82" s="30"/>
@@ -3466,7 +3938,7 @@
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="41" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F83" s="32"/>
       <c r="G83" s="30"/>
@@ -3483,7 +3955,7 @@
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="41" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F84" s="32"/>
       <c r="G84" s="30"/>
@@ -3500,7 +3972,7 @@
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="41" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F85" s="32"/>
       <c r="G85" s="30"/>
@@ -3517,7 +3989,7 @@
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="41" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F86" s="32"/>
       <c r="G86" s="30"/>
@@ -3534,7 +4006,7 @@
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="41" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F87" s="32"/>
       <c r="G87" s="30"/>
@@ -3551,7 +4023,7 @@
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="41" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F88" s="32"/>
       <c r="G88" s="30"/>
@@ -3568,7 +4040,7 @@
       </c>
       <c r="D89" s="6"/>
       <c r="E89" s="41" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F89" s="32"/>
       <c r="G89" s="30"/>
@@ -3585,7 +4057,7 @@
       </c>
       <c r="D90" s="6"/>
       <c r="E90" s="41" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F90" s="32"/>
       <c r="G90" s="30"/>
@@ -3602,7 +4074,7 @@
       </c>
       <c r="D91" s="6"/>
       <c r="E91" s="41" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F91" s="32"/>
       <c r="G91" s="30"/>
@@ -3619,7 +4091,7 @@
       </c>
       <c r="D92" s="18"/>
       <c r="E92" s="41" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F92" s="35"/>
       <c r="G92" s="30"/>
@@ -3639,10 +4111,10 @@
         <v>168</v>
       </c>
       <c r="F93" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G93" s="15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -3656,7 +4128,7 @@
         <v>1440</v>
       </c>
       <c r="D94" s="23"/>
-      <c r="E94" s="46"/>
+      <c r="E94" s="45"/>
       <c r="F94" s="31"/>
       <c r="G94" s="30"/>
     </row>
@@ -3671,7 +4143,7 @@
         <v>1440</v>
       </c>
       <c r="D95" s="6"/>
-      <c r="E95" s="47"/>
+      <c r="E95" s="46"/>
       <c r="F95" s="32"/>
       <c r="G95" s="30"/>
     </row>
@@ -3686,7 +4158,7 @@
         <v>1680</v>
       </c>
       <c r="D96" s="6"/>
-      <c r="E96" s="47"/>
+      <c r="E96" s="46"/>
       <c r="F96" s="32"/>
       <c r="G96" s="30"/>
     </row>
@@ -3701,7 +4173,7 @@
         <v>1680</v>
       </c>
       <c r="D97" s="6"/>
-      <c r="E97" s="47"/>
+      <c r="E97" s="46"/>
       <c r="F97" s="32"/>
       <c r="G97" s="30"/>
     </row>
@@ -3716,7 +4188,7 @@
         <v>1680</v>
       </c>
       <c r="D98" s="6"/>
-      <c r="E98" s="47"/>
+      <c r="E98" s="46"/>
       <c r="F98" s="32"/>
       <c r="G98" s="30"/>
     </row>
@@ -3731,7 +4203,7 @@
         <v>1800</v>
       </c>
       <c r="D99" s="6"/>
-      <c r="E99" s="47"/>
+      <c r="E99" s="46"/>
       <c r="F99" s="32"/>
       <c r="G99" s="30"/>
     </row>
@@ -3746,7 +4218,7 @@
         <v>2040</v>
       </c>
       <c r="D100" s="6"/>
-      <c r="E100" s="47"/>
+      <c r="E100" s="46"/>
       <c r="F100" s="32"/>
       <c r="G100" s="30"/>
     </row>
@@ -3761,7 +4233,7 @@
         <v>960</v>
       </c>
       <c r="D101" s="3"/>
-      <c r="E101" s="47"/>
+      <c r="E101" s="46"/>
       <c r="F101" s="32"/>
       <c r="G101" s="30"/>
     </row>
@@ -3776,7 +4248,7 @@
         <v>1440</v>
       </c>
       <c r="D102" s="6"/>
-      <c r="E102" s="47"/>
+      <c r="E102" s="46"/>
       <c r="F102" s="32"/>
       <c r="G102" s="30"/>
     </row>
@@ -3791,7 +4263,7 @@
         <v>1800</v>
       </c>
       <c r="D103" s="6"/>
-      <c r="E103" s="47"/>
+      <c r="E103" s="46"/>
       <c r="F103" s="32"/>
       <c r="G103" s="30"/>
     </row>
@@ -3806,7 +4278,7 @@
         <v>2160</v>
       </c>
       <c r="D104" s="6"/>
-      <c r="E104" s="47"/>
+      <c r="E104" s="46"/>
       <c r="F104" s="32"/>
       <c r="G104" s="30"/>
     </row>
@@ -3821,7 +4293,7 @@
         <v>1413</v>
       </c>
       <c r="D105" s="6"/>
-      <c r="E105" s="47"/>
+      <c r="E105" s="46"/>
       <c r="F105" s="32"/>
       <c r="G105" s="30"/>
     </row>
@@ -3836,7 +4308,7 @@
         <v>1024</v>
       </c>
       <c r="D106" s="24"/>
-      <c r="E106" s="48"/>
+      <c r="E106" s="47"/>
       <c r="F106" s="35"/>
       <c r="G106" s="30"/>
     </row>
@@ -3855,10 +4327,10 @@
         <v>168</v>
       </c>
       <c r="F107" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G107" s="15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -3872,8 +4344,8 @@
         <v>1173</v>
       </c>
       <c r="D108" s="23"/>
-      <c r="E108" s="49" t="s">
-        <v>207</v>
+      <c r="E108" s="48" t="s">
+        <v>206</v>
       </c>
       <c r="F108" s="31"/>
       <c r="G108" s="30"/>
@@ -3890,7 +4362,7 @@
       </c>
       <c r="D109" s="6"/>
       <c r="E109" s="36" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F109" s="32"/>
       <c r="G109" s="30"/>
@@ -3907,7 +4379,7 @@
       </c>
       <c r="D110" s="6"/>
       <c r="E110" s="36" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F110" s="32"/>
       <c r="G110" s="30"/>
@@ -3924,7 +4396,7 @@
       </c>
       <c r="D111" s="6"/>
       <c r="E111" s="36" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F111" s="32"/>
       <c r="G111" s="30"/>
@@ -3941,7 +4413,7 @@
       </c>
       <c r="D112" s="6"/>
       <c r="E112" s="36" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F112" s="32"/>
       <c r="G112" s="30"/>
@@ -3958,7 +4430,7 @@
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="36" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F113" s="32"/>
       <c r="G113" s="30"/>
@@ -3975,7 +4447,7 @@
       </c>
       <c r="D114" s="6"/>
       <c r="E114" s="36" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F114" s="32"/>
       <c r="G114" s="30"/>
@@ -3992,7 +4464,7 @@
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="36" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F115" s="32"/>
       <c r="G115" s="30"/>
@@ -4009,7 +4481,7 @@
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="36" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F116" s="32"/>
       <c r="G116" s="30"/>
@@ -4026,7 +4498,7 @@
       </c>
       <c r="D117" s="3"/>
       <c r="E117" s="36" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F117" s="32"/>
       <c r="G117" s="30"/>
@@ -4043,7 +4515,7 @@
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="36" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F118" s="32"/>
       <c r="G118" s="30"/>
@@ -4060,7 +4532,7 @@
       </c>
       <c r="D119" s="6"/>
       <c r="E119" s="36" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F119" s="32"/>
       <c r="G119" s="30"/>
@@ -4077,7 +4549,7 @@
       </c>
       <c r="D120" s="6"/>
       <c r="E120" s="36" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F120" s="32"/>
       <c r="G120" s="30"/>
@@ -4094,7 +4566,7 @@
       </c>
       <c r="D121" s="6"/>
       <c r="E121" s="36" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F121" s="32"/>
       <c r="G121" s="30"/>
@@ -4111,7 +4583,7 @@
       </c>
       <c r="D122" s="6"/>
       <c r="E122" s="36" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F122" s="32"/>
       <c r="G122" s="30"/>
@@ -4128,7 +4600,7 @@
       </c>
       <c r="D123" s="6"/>
       <c r="E123" s="36" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F123" s="32"/>
       <c r="G123" s="30"/>
@@ -4145,7 +4617,7 @@
       </c>
       <c r="D124" s="6"/>
       <c r="E124" s="36" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F124" s="32"/>
       <c r="G124" s="30"/>
@@ -4162,7 +4634,7 @@
       </c>
       <c r="D125" s="6"/>
       <c r="E125" s="36" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F125" s="32"/>
       <c r="G125" s="30"/>
@@ -4178,13 +4650,13 @@
         <v>839</v>
       </c>
       <c r="D126" s="18"/>
-      <c r="E126" s="50" t="s">
-        <v>286</v>
+      <c r="E126" s="49" t="s">
+        <v>285</v>
       </c>
       <c r="F126" s="19" t="s">
-        <v>322</v>
-      </c>
-      <c r="G126" s="53"/>
+        <v>321</v>
+      </c>
+      <c r="G126" s="52"/>
     </row>
     <row r="127" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="15" t="s">
@@ -4201,10 +4673,10 @@
         <v>168</v>
       </c>
       <c r="F127" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G127" s="15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -4218,8 +4690,8 @@
         <v>2293</v>
       </c>
       <c r="D128" s="23"/>
-      <c r="E128" s="46" t="s">
-        <v>287</v>
+      <c r="E128" s="45" t="s">
+        <v>286</v>
       </c>
       <c r="F128" s="31"/>
       <c r="G128" s="30"/>
@@ -4235,8 +4707,8 @@
         <v>2800</v>
       </c>
       <c r="D129" s="6"/>
-      <c r="E129" s="50" t="s">
-        <v>288</v>
+      <c r="E129" s="49" t="s">
+        <v>287</v>
       </c>
       <c r="F129" s="32"/>
       <c r="G129" s="30"/>
@@ -4253,11 +4725,11 @@
       </c>
       <c r="D130" s="6"/>
       <c r="E130" s="36" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F130" s="32"/>
-      <c r="G130" s="60" t="s">
-        <v>337</v>
+      <c r="G130" s="59" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -4272,11 +4744,11 @@
       </c>
       <c r="D131" s="6"/>
       <c r="E131" s="36" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F131" s="32"/>
-      <c r="G131" s="60" t="s">
-        <v>339</v>
+      <c r="G131" s="59" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -4291,11 +4763,11 @@
       </c>
       <c r="D132" s="6"/>
       <c r="E132" s="36" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F132" s="32"/>
-      <c r="G132" s="60" t="s">
-        <v>340</v>
+      <c r="G132" s="59" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -4310,11 +4782,11 @@
       </c>
       <c r="D133" s="6"/>
       <c r="E133" s="36" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F133" s="32"/>
-      <c r="G133" s="60" t="s">
-        <v>338</v>
+      <c r="G133" s="59" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -4329,7 +4801,7 @@
       </c>
       <c r="D134" s="6"/>
       <c r="E134" s="36" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F134" s="32"/>
       <c r="G134" s="30"/>
@@ -4346,7 +4818,7 @@
       </c>
       <c r="D135" s="6"/>
       <c r="E135" s="36" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F135" s="32"/>
       <c r="G135" s="30"/>
@@ -4363,7 +4835,7 @@
       </c>
       <c r="D136" s="6"/>
       <c r="E136" s="36" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F136" s="32"/>
       <c r="G136" s="30"/>
@@ -4380,7 +4852,7 @@
       </c>
       <c r="D137" s="6"/>
       <c r="E137" s="36" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F137" s="32"/>
       <c r="G137" s="30"/>
@@ -4396,8 +4868,8 @@
         <v>1944</v>
       </c>
       <c r="D138" s="24"/>
-      <c r="E138" s="50" t="s">
-        <v>297</v>
+      <c r="E138" s="49" t="s">
+        <v>296</v>
       </c>
       <c r="F138" s="35"/>
       <c r="G138" s="30"/>
@@ -4417,10 +4889,10 @@
         <v>168</v>
       </c>
       <c r="F139" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G139" s="15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -4434,7 +4906,7 @@
         <v>2100</v>
       </c>
       <c r="D140" s="23"/>
-      <c r="E140" s="51"/>
+      <c r="E140" s="50"/>
       <c r="F140" s="31"/>
       <c r="G140" s="30"/>
     </row>
@@ -4449,7 +4921,7 @@
         <v>1560</v>
       </c>
       <c r="D141" s="6"/>
-      <c r="E141" s="47"/>
+      <c r="E141" s="46"/>
       <c r="F141" s="32"/>
       <c r="G141" s="30"/>
     </row>
@@ -4464,20 +4936,20 @@
         <v>1800</v>
       </c>
       <c r="D142" s="6"/>
-      <c r="E142" s="47"/>
+      <c r="E142" s="46"/>
       <c r="F142" s="32"/>
       <c r="G142" s="30"/>
     </row>
     <row r="143" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="63" t="s">
+      <c r="A143" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="B143" s="63"/>
-      <c r="C143" s="63"/>
-      <c r="D143" s="63"/>
-      <c r="E143" s="63"/>
-      <c r="F143" s="63"/>
-      <c r="G143" s="57"/>
+      <c r="B143" s="62"/>
+      <c r="C143" s="62"/>
+      <c r="D143" s="62"/>
+      <c r="E143" s="62"/>
+      <c r="F143" s="62"/>
+      <c r="G143" s="56"/>
     </row>
     <row r="144" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="15" t="s">
@@ -4494,10 +4966,10 @@
         <v>168</v>
       </c>
       <c r="F144" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G144" s="15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -4511,13 +4983,13 @@
         <v>533</v>
       </c>
       <c r="D145" s="13"/>
-      <c r="E145" s="50" t="s">
-        <v>330</v>
+      <c r="E145" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F145" s="37" t="s">
-        <v>298</v>
-      </c>
-      <c r="G145" s="58"/>
+        <v>297</v>
+      </c>
+      <c r="G145" s="57"/>
     </row>
     <row r="146" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
@@ -4530,11 +5002,11 @@
         <v>640</v>
       </c>
       <c r="D146" s="3"/>
-      <c r="E146" s="50" t="s">
-        <v>331</v>
+      <c r="E146" s="49" t="s">
+        <v>330</v>
       </c>
       <c r="F146" s="38"/>
-      <c r="G146" s="58"/>
+      <c r="G146" s="57"/>
     </row>
     <row r="147" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
@@ -4547,13 +5019,13 @@
         <v>800</v>
       </c>
       <c r="D147" s="3"/>
-      <c r="E147" s="50" t="s">
-        <v>330</v>
+      <c r="E147" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F147" s="38" t="s">
-        <v>306</v>
-      </c>
-      <c r="G147" s="58"/>
+        <v>305</v>
+      </c>
+      <c r="G147" s="57"/>
     </row>
     <row r="148" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
@@ -4566,13 +5038,13 @@
         <v>880</v>
       </c>
       <c r="D148" s="3"/>
-      <c r="E148" s="50" t="s">
-        <v>330</v>
+      <c r="E148" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F148" s="38" t="s">
-        <v>301</v>
-      </c>
-      <c r="G148" s="58"/>
+        <v>300</v>
+      </c>
+      <c r="G148" s="57"/>
     </row>
     <row r="149" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
@@ -4585,13 +5057,13 @@
         <v>660</v>
       </c>
       <c r="D149" s="3"/>
-      <c r="E149" s="50" t="s">
-        <v>330</v>
+      <c r="E149" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F149" s="38" t="s">
-        <v>320</v>
-      </c>
-      <c r="G149" s="58"/>
+        <v>319</v>
+      </c>
+      <c r="G149" s="57"/>
     </row>
     <row r="150" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
@@ -4604,11 +5076,11 @@
         <v>780</v>
       </c>
       <c r="D150" s="3"/>
-      <c r="E150" s="50" t="s">
-        <v>330</v>
+      <c r="E150" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F150" s="38"/>
-      <c r="G150" s="58"/>
+      <c r="G150" s="57"/>
     </row>
     <row r="151" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
@@ -4621,13 +5093,13 @@
         <v>840</v>
       </c>
       <c r="D151" s="3"/>
-      <c r="E151" s="50" t="s">
-        <v>330</v>
+      <c r="E151" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F151" s="38" t="s">
-        <v>318</v>
-      </c>
-      <c r="G151" s="58"/>
+        <v>317</v>
+      </c>
+      <c r="G151" s="57"/>
     </row>
     <row r="152" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
@@ -4640,13 +5112,13 @@
         <v>900</v>
       </c>
       <c r="D152" s="3"/>
-      <c r="E152" s="50" t="s">
-        <v>330</v>
+      <c r="E152" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F152" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="G152" s="58"/>
+        <v>312</v>
+      </c>
+      <c r="G152" s="57"/>
     </row>
     <row r="153" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
@@ -4659,13 +5131,13 @@
         <v>990</v>
       </c>
       <c r="D153" s="3"/>
-      <c r="E153" s="50" t="s">
-        <v>330</v>
+      <c r="E153" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F153" s="38" t="s">
-        <v>307</v>
-      </c>
-      <c r="G153" s="58"/>
+        <v>306</v>
+      </c>
+      <c r="G153" s="57"/>
     </row>
     <row r="154" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
@@ -4678,13 +5150,13 @@
         <v>1080</v>
       </c>
       <c r="D154" s="3"/>
-      <c r="E154" s="50" t="s">
-        <v>330</v>
+      <c r="E154" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F154" s="39" t="s">
-        <v>321</v>
-      </c>
-      <c r="G154" s="59"/>
+        <v>320</v>
+      </c>
+      <c r="G154" s="58"/>
     </row>
     <row r="155" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
@@ -4697,13 +5169,13 @@
         <v>1140</v>
       </c>
       <c r="D155" s="3"/>
-      <c r="E155" s="50" t="s">
-        <v>330</v>
+      <c r="E155" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F155" s="38" t="s">
-        <v>308</v>
-      </c>
-      <c r="G155" s="58"/>
+        <v>307</v>
+      </c>
+      <c r="G155" s="57"/>
     </row>
     <row r="156" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
@@ -4716,13 +5188,13 @@
         <v>1056</v>
       </c>
       <c r="D156" s="3"/>
-      <c r="E156" s="50" t="s">
-        <v>330</v>
+      <c r="E156" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F156" s="38" t="s">
-        <v>309</v>
-      </c>
-      <c r="G156" s="58"/>
+        <v>308</v>
+      </c>
+      <c r="G156" s="57"/>
     </row>
     <row r="157" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
@@ -4735,13 +5207,13 @@
         <v>1152</v>
       </c>
       <c r="D157" s="3"/>
-      <c r="E157" s="50" t="s">
-        <v>330</v>
+      <c r="E157" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F157" s="38" t="s">
-        <v>319</v>
-      </c>
-      <c r="G157" s="58"/>
+        <v>318</v>
+      </c>
+      <c r="G157" s="57"/>
     </row>
     <row r="158" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
@@ -4754,13 +5226,13 @@
         <v>1248</v>
       </c>
       <c r="D158" s="3"/>
-      <c r="E158" s="50" t="s">
-        <v>330</v>
+      <c r="E158" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F158" s="38" t="s">
-        <v>310</v>
-      </c>
-      <c r="G158" s="58"/>
+        <v>309</v>
+      </c>
+      <c r="G158" s="57"/>
     </row>
     <row r="159" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
@@ -4773,15 +5245,15 @@
         <v>1176</v>
       </c>
       <c r="D159" s="3"/>
-      <c r="E159" s="50" t="s">
-        <v>330</v>
+      <c r="E159" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F159" s="38"/>
-      <c r="G159" s="58"/>
+      <c r="G159" s="57"/>
     </row>
     <row r="160" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>98</v>
@@ -4790,13 +5262,13 @@
         <v>1344</v>
       </c>
       <c r="D160" s="3"/>
-      <c r="E160" s="50" t="s">
-        <v>330</v>
+      <c r="E160" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F160" s="38" t="s">
-        <v>317</v>
-      </c>
-      <c r="G160" s="58"/>
+        <v>316</v>
+      </c>
+      <c r="G160" s="57"/>
     </row>
     <row r="161" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
@@ -4809,11 +5281,11 @@
         <v>1272</v>
       </c>
       <c r="D161" s="3"/>
-      <c r="E161" s="50" t="s">
-        <v>330</v>
+      <c r="E161" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F161" s="30" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G161" s="30"/>
     </row>
@@ -4828,11 +5300,11 @@
         <v>1067</v>
       </c>
       <c r="D162" s="3"/>
-      <c r="E162" s="50" t="s">
-        <v>330</v>
+      <c r="E162" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F162" s="38"/>
-      <c r="G162" s="58"/>
+      <c r="G162" s="57"/>
     </row>
     <row r="163" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
@@ -4845,13 +5317,13 @@
         <v>1173</v>
       </c>
       <c r="D163" s="3"/>
-      <c r="E163" s="50" t="s">
-        <v>330</v>
+      <c r="E163" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F163" s="39" t="s">
-        <v>302</v>
-      </c>
-      <c r="G163" s="59"/>
+        <v>301</v>
+      </c>
+      <c r="G163" s="58"/>
     </row>
     <row r="164" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
@@ -4864,13 +5336,13 @@
         <v>1280</v>
       </c>
       <c r="D164" s="3"/>
-      <c r="E164" s="50" t="s">
-        <v>330</v>
+      <c r="E164" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F164" s="39" t="s">
-        <v>303</v>
-      </c>
-      <c r="G164" s="59"/>
+        <v>302</v>
+      </c>
+      <c r="G164" s="58"/>
     </row>
     <row r="165" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
@@ -4883,13 +5355,13 @@
         <v>1306</v>
       </c>
       <c r="D165" s="3"/>
-      <c r="E165" s="50" t="s">
-        <v>330</v>
+      <c r="E165" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F165" s="38" t="s">
-        <v>312</v>
-      </c>
-      <c r="G165" s="58"/>
+        <v>311</v>
+      </c>
+      <c r="G165" s="57"/>
     </row>
     <row r="166" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
@@ -4902,11 +5374,11 @@
         <v>1387</v>
       </c>
       <c r="D166" s="3"/>
-      <c r="E166" s="50" t="s">
-        <v>330</v>
+      <c r="E166" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F166" s="38"/>
-      <c r="G166" s="58"/>
+      <c r="G166" s="57"/>
     </row>
     <row r="167" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
@@ -4919,13 +5391,13 @@
         <v>1493</v>
       </c>
       <c r="D167" s="3"/>
-      <c r="E167" s="50" t="s">
-        <v>330</v>
+      <c r="E167" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F167" s="38" t="s">
-        <v>305</v>
-      </c>
-      <c r="G167" s="58"/>
+        <v>304</v>
+      </c>
+      <c r="G167" s="57"/>
     </row>
     <row r="168" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
@@ -4938,13 +5410,13 @@
         <v>1414</v>
       </c>
       <c r="D168" s="3"/>
-      <c r="E168" s="50" t="s">
-        <v>330</v>
+      <c r="E168" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F168" s="38" t="s">
-        <v>315</v>
-      </c>
-      <c r="G168" s="58"/>
+        <v>314</v>
+      </c>
+      <c r="G168" s="57"/>
     </row>
     <row r="169" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
@@ -4957,13 +5429,13 @@
         <v>1600</v>
       </c>
       <c r="D169" s="3"/>
-      <c r="E169" s="50" t="s">
-        <v>330</v>
+      <c r="E169" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F169" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="G169" s="59"/>
+        <v>313</v>
+      </c>
+      <c r="G169" s="58"/>
     </row>
     <row r="170" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
@@ -4976,13 +5448,13 @@
         <v>1760</v>
       </c>
       <c r="D170" s="3"/>
-      <c r="E170" s="50" t="s">
-        <v>330</v>
+      <c r="E170" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F170" s="39" t="s">
-        <v>304</v>
-      </c>
-      <c r="G170" s="59"/>
+        <v>303</v>
+      </c>
+      <c r="G170" s="58"/>
     </row>
     <row r="171" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
@@ -4995,13 +5467,13 @@
         <v>1920</v>
       </c>
       <c r="D171" s="3"/>
-      <c r="E171" s="50" t="s">
-        <v>330</v>
+      <c r="E171" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F171" s="38" t="s">
-        <v>311</v>
-      </c>
-      <c r="G171" s="58"/>
+        <v>310</v>
+      </c>
+      <c r="G171" s="57"/>
     </row>
     <row r="172" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
@@ -5014,11 +5486,11 @@
         <v>2052</v>
       </c>
       <c r="D172" s="3"/>
-      <c r="E172" s="50" t="s">
-        <v>330</v>
+      <c r="E172" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F172" s="38"/>
-      <c r="G172" s="58"/>
+      <c r="G172" s="57"/>
     </row>
     <row r="173" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
@@ -5031,13 +5503,13 @@
         <v>1680</v>
       </c>
       <c r="D173" s="3"/>
-      <c r="E173" s="50" t="s">
-        <v>330</v>
+      <c r="E173" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F173" s="38" t="s">
-        <v>299</v>
-      </c>
-      <c r="G173" s="58"/>
+        <v>298</v>
+      </c>
+      <c r="G173" s="57"/>
     </row>
     <row r="174" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
@@ -5050,11 +5522,11 @@
         <v>1493</v>
       </c>
       <c r="D174" s="3"/>
-      <c r="E174" s="50" t="s">
-        <v>330</v>
+      <c r="E174" s="49" t="s">
+        <v>329</v>
       </c>
       <c r="F174" s="38"/>
-      <c r="G174" s="58"/>
+      <c r="G174" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5158,6 +5630,7 @@
     <hyperlink ref="G133" r:id="rId93" xr:uid="{4C4DD5E8-6291-4B28-B0C2-0AAD57143E00}"/>
     <hyperlink ref="G131" r:id="rId94" xr:uid="{B88FC6B3-5EEF-4DFD-B2AD-4CC0466B9506}"/>
     <hyperlink ref="G132" r:id="rId95" xr:uid="{DB565809-20B2-4A11-860A-11B4868E1FBB}"/>
+    <hyperlink ref="G41" r:id="rId96" xr:uid="{3B4FD59A-0AB6-4ED4-B8F2-C2742B70518C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Homes List.xlsx
+++ b/docs/Homes List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9df306d6984b8b22/Documents/GitHub/Wix-Products/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="531" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08B87910-23E2-4EF9-AF13-3BE3284A6A1E}"/>
+  <xr:revisionPtr revIDLastSave="532" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{742C59FC-AD93-47E5-B1BA-400061572C27}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
+    <workbookView xWindow="4560" yWindow="4560" windowWidth="28800" windowHeight="15370" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1717,6 +1717,11 @@
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1725,11 +1730,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2141,14 +2141,14 @@
       <c r="G2" s="30"/>
     </row>
     <row r="3" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
       <c r="G3" s="51"/>
     </row>
     <row r="4" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -2850,23 +2850,23 @@
         <v>852</v>
       </c>
       <c r="D41" s="13"/>
-      <c r="E41" s="63" t="s">
+      <c r="E41" s="60" t="s">
         <v>340</v>
       </c>
       <c r="F41" s="31"/>
       <c r="G41" s="59" t="s">
         <v>323</v>
       </c>
-      <c r="L41" s="65" t="s">
+      <c r="L41" s="62" t="s">
         <v>361</v>
       </c>
-      <c r="M41" s="65" t="s">
+      <c r="M41" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N41" s="65" t="s">
+      <c r="N41" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O41" s="65" t="s">
+      <c r="O41" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q41" t="str">
@@ -2894,14 +2894,14 @@
       <c r="G42" s="30" t="s">
         <v>332</v>
       </c>
-      <c r="L42" s="64"/>
-      <c r="M42" s="65" t="s">
+      <c r="L42" s="61"/>
+      <c r="M42" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N42" s="65" t="s">
+      <c r="N42" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O42" s="65" t="s">
+      <c r="O42" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q42" t="str">
@@ -2931,14 +2931,14 @@
       <c r="G43" s="52" t="s">
         <v>324</v>
       </c>
-      <c r="L43" s="64"/>
-      <c r="M43" s="65" t="s">
+      <c r="L43" s="61"/>
+      <c r="M43" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N43" s="65" t="s">
+      <c r="N43" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O43" s="65" t="s">
+      <c r="O43" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q43" t="str">
@@ -2964,14 +2964,14 @@
       </c>
       <c r="F44" s="32"/>
       <c r="G44" s="30"/>
-      <c r="L44" s="64"/>
-      <c r="M44" s="65" t="s">
+      <c r="L44" s="61"/>
+      <c r="M44" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N44" s="65" t="s">
+      <c r="N44" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O44" s="65" t="s">
+      <c r="O44" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q44" t="str">
@@ -2999,14 +2999,14 @@
       <c r="G45" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="L45" s="64"/>
-      <c r="M45" s="65" t="s">
+      <c r="L45" s="61"/>
+      <c r="M45" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N45" s="65" t="s">
+      <c r="N45" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O45" s="65" t="s">
+      <c r="O45" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q45" t="str">
@@ -3034,14 +3034,14 @@
         <v>235</v>
       </c>
       <c r="G46" s="30"/>
-      <c r="L46" s="64"/>
-      <c r="M46" s="65" t="s">
+      <c r="L46" s="61"/>
+      <c r="M46" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N46" s="65" t="s">
+      <c r="N46" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O46" s="65" t="s">
+      <c r="O46" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q46" t="str">
@@ -3067,14 +3067,14 @@
       </c>
       <c r="F47" s="32"/>
       <c r="G47" s="30"/>
-      <c r="L47" s="64"/>
-      <c r="M47" s="65" t="s">
+      <c r="L47" s="61"/>
+      <c r="M47" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N47" s="65" t="s">
+      <c r="N47" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O47" s="65" t="s">
+      <c r="O47" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q47" t="str">
@@ -3104,14 +3104,14 @@
       <c r="G48" s="30" t="s">
         <v>326</v>
       </c>
-      <c r="L48" s="64"/>
-      <c r="M48" s="65" t="s">
+      <c r="L48" s="61"/>
+      <c r="M48" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N48" s="65" t="s">
+      <c r="N48" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O48" s="65" t="s">
+      <c r="O48" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q48" t="str">
@@ -3137,14 +3137,14 @@
       </c>
       <c r="F49" s="32"/>
       <c r="G49" s="30"/>
-      <c r="L49" s="64"/>
-      <c r="M49" s="65" t="s">
+      <c r="L49" s="61"/>
+      <c r="M49" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N49" s="65" t="s">
+      <c r="N49" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O49" s="65" t="s">
+      <c r="O49" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q49" t="str">
@@ -3172,14 +3172,14 @@
         <v>237</v>
       </c>
       <c r="G50" s="54"/>
-      <c r="L50" s="64"/>
-      <c r="M50" s="65" t="s">
+      <c r="L50" s="61"/>
+      <c r="M50" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N50" s="65" t="s">
+      <c r="N50" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O50" s="65" t="s">
+      <c r="O50" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q50" t="str">
@@ -3205,14 +3205,14 @@
       </c>
       <c r="F51" s="32"/>
       <c r="G51" s="30"/>
-      <c r="L51" s="64"/>
-      <c r="M51" s="65" t="s">
+      <c r="L51" s="61"/>
+      <c r="M51" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N51" s="65" t="s">
+      <c r="N51" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O51" s="65" t="s">
+      <c r="O51" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q51" t="str">
@@ -3240,14 +3240,14 @@
       <c r="G52" s="52" t="s">
         <v>327</v>
       </c>
-      <c r="L52" s="64"/>
-      <c r="M52" s="65" t="s">
+      <c r="L52" s="61"/>
+      <c r="M52" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N52" s="65" t="s">
+      <c r="N52" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O52" s="65" t="s">
+      <c r="O52" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q52" t="str">
@@ -3273,14 +3273,14 @@
       </c>
       <c r="F53" s="32"/>
       <c r="G53" s="30"/>
-      <c r="L53" s="64"/>
-      <c r="M53" s="65" t="s">
+      <c r="L53" s="61"/>
+      <c r="M53" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N53" s="65" t="s">
+      <c r="N53" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O53" s="65" t="s">
+      <c r="O53" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q53" t="str">
@@ -3308,14 +3308,14 @@
         <v>238</v>
       </c>
       <c r="G54" s="30"/>
-      <c r="L54" s="64"/>
-      <c r="M54" s="65" t="s">
+      <c r="L54" s="61"/>
+      <c r="M54" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N54" s="65" t="s">
+      <c r="N54" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O54" s="65" t="s">
+      <c r="O54" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q54" t="str">
@@ -3341,14 +3341,14 @@
       </c>
       <c r="F55" s="32"/>
       <c r="G55" s="30"/>
-      <c r="L55" s="64"/>
-      <c r="M55" s="65" t="s">
+      <c r="L55" s="61"/>
+      <c r="M55" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N55" s="65" t="s">
+      <c r="N55" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O55" s="65" t="s">
+      <c r="O55" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q55" t="str">
@@ -3376,14 +3376,14 @@
       <c r="G56" s="30" t="s">
         <v>328</v>
       </c>
-      <c r="L56" s="64"/>
-      <c r="M56" s="65" t="s">
+      <c r="L56" s="61"/>
+      <c r="M56" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N56" s="65" t="s">
+      <c r="N56" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O56" s="65" t="s">
+      <c r="O56" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q56" t="str">
@@ -3409,14 +3409,14 @@
       </c>
       <c r="F57" s="32"/>
       <c r="G57" s="30"/>
-      <c r="L57" s="64"/>
-      <c r="M57" s="65" t="s">
+      <c r="L57" s="61"/>
+      <c r="M57" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N57" s="65" t="s">
+      <c r="N57" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O57" s="65" t="s">
+      <c r="O57" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q57" t="str">
@@ -3442,14 +3442,14 @@
       </c>
       <c r="F58" s="32"/>
       <c r="G58" s="30"/>
-      <c r="L58" s="64"/>
-      <c r="M58" s="65" t="s">
+      <c r="L58" s="61"/>
+      <c r="M58" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N58" s="65" t="s">
+      <c r="N58" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O58" s="65" t="s">
+      <c r="O58" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q58" t="str">
@@ -3475,14 +3475,14 @@
       </c>
       <c r="F59" s="32"/>
       <c r="G59" s="30"/>
-      <c r="L59" s="64"/>
-      <c r="M59" s="65" t="s">
+      <c r="L59" s="61"/>
+      <c r="M59" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N59" s="65" t="s">
+      <c r="N59" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O59" s="65" t="s">
+      <c r="O59" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q59" t="str">
@@ -3510,14 +3510,14 @@
         <v>239</v>
       </c>
       <c r="G60" s="30"/>
-      <c r="L60" s="64"/>
-      <c r="M60" s="65" t="s">
+      <c r="L60" s="61"/>
+      <c r="M60" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N60" s="65" t="s">
+      <c r="N60" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O60" s="65" t="s">
+      <c r="O60" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q60" t="str">
@@ -3543,14 +3543,14 @@
       </c>
       <c r="F61" s="32"/>
       <c r="G61" s="30"/>
-      <c r="L61" s="64"/>
-      <c r="M61" s="65" t="s">
+      <c r="L61" s="61"/>
+      <c r="M61" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="N61" s="65" t="s">
+      <c r="N61" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="O61" s="65" t="s">
+      <c r="O61" s="62" t="s">
         <v>364</v>
       </c>
       <c r="Q61" t="str">
@@ -3561,18 +3561,18 @@
       </c>
     </row>
     <row r="62" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="61" t="s">
+      <c r="A62" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="B62" s="61"/>
-      <c r="C62" s="61"/>
-      <c r="D62" s="61"/>
-      <c r="E62" s="61"/>
-      <c r="F62" s="61"/>
+      <c r="B62" s="64"/>
+      <c r="C62" s="64"/>
+      <c r="D62" s="64"/>
+      <c r="E62" s="64"/>
+      <c r="F62" s="64"/>
       <c r="G62" s="55"/>
-      <c r="L62" s="64"/>
-      <c r="M62" s="63"/>
-      <c r="N62" s="64"/>
+      <c r="L62" s="61"/>
+      <c r="M62" s="60"/>
+      <c r="N62" s="61"/>
     </row>
     <row r="63" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="15" t="s">
@@ -4941,14 +4941,14 @@
       <c r="G142" s="30"/>
     </row>
     <row r="143" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="62" t="s">
+      <c r="A143" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="B143" s="62"/>
-      <c r="C143" s="62"/>
-      <c r="D143" s="62"/>
-      <c r="E143" s="62"/>
-      <c r="F143" s="62"/>
+      <c r="B143" s="65"/>
+      <c r="C143" s="65"/>
+      <c r="D143" s="65"/>
+      <c r="E143" s="65"/>
+      <c r="F143" s="65"/>
       <c r="G143" s="56"/>
     </row>
     <row r="144" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -5284,7 +5284,7 @@
       <c r="E161" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="F161" s="30" t="s">
+      <c r="F161" s="59" t="s">
         <v>299</v>
       </c>
       <c r="G161" s="30"/>
@@ -5631,6 +5631,7 @@
     <hyperlink ref="G131" r:id="rId94" xr:uid="{B88FC6B3-5EEF-4DFD-B2AD-4CC0466B9506}"/>
     <hyperlink ref="G132" r:id="rId95" xr:uid="{DB565809-20B2-4A11-860A-11B4868E1FBB}"/>
     <hyperlink ref="G41" r:id="rId96" xr:uid="{3B4FD59A-0AB6-4ED4-B8F2-C2742B70518C}"/>
+    <hyperlink ref="F161" r:id="rId97" xr:uid="{31F5BEED-4304-4333-9E5A-1BCFBD485562}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Homes List.xlsx
+++ b/docs/Homes List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9df306d6984b8b22/Documents/GitHub/Wix-Products/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cadel\OneDrive\Documents\GitHub\Wix-Products\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="532" documentId="8_{B2DED620-90B7-4684-A3F4-AF4309055B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{742C59FC-AD93-47E5-B1BA-400061572C27}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1202DC-4188-4456-B815-098903535963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="4560" windowWidth="28800" windowHeight="15370" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{D9C4D26D-31FE-48E8-B474-91DCB44BBA2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="423">
   <si>
     <t xml:space="preserve">Golden West </t>
   </si>
@@ -629,9 +629,6 @@
     <t>Still The One</t>
   </si>
   <si>
-    <t>Born to Run</t>
-  </si>
-  <si>
     <t>15' x 60'</t>
   </si>
   <si>
@@ -665,9 +662,6 @@
     <t>24' x 52'</t>
   </si>
   <si>
-    <t>Stand by Me (Porch)</t>
-  </si>
-  <si>
     <t>24' x 52' / 46'</t>
   </si>
   <si>
@@ -734,9 +728,6 @@
     <t>30' x 56'</t>
   </si>
   <si>
-    <t>Lean on Me</t>
-  </si>
-  <si>
     <t>27' x 56'</t>
   </si>
   <si>
@@ -749,18 +740,6 @@
     <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/DRM/Casita.pdf</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/DRM/481M.pdf</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>PDF Blury</t>
-  </si>
-  <si>
-    <t>PDF Missing</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/DRM/521M.pdf</t>
   </si>
   <si>
@@ -1333,13 +1312,268 @@
   </si>
   <si>
     <t>" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Respect.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Yesterday.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Layla.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Shout.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Superfly.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Limelight.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Still_The_One.pdf</t>
+  </si>
+  <si>
+    <t>Born To Run</t>
+  </si>
+  <si>
+    <t>Lean On Me</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Good_Vibrations.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Born_To_Run.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Rhythm_Nation.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Move_On_Up.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Sweet_Coroline.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Rising_Sun.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Here_Comes_The_Sun.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Three_Little_Birds.pdf</t>
+  </si>
+  <si>
+    <t>Stand By Me (Porch)</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/My_Girl.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Sweet_Dreams.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Beautiful_Morning.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Under_Pressure.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Stand_By_Me.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Whole_Lotta_Love.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Johnny_B_Goode.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Free_Bird.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Staying_Alive.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Brown_Eyed_Girl.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Rocket_Man.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Hey_Jude.pdf</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Lean_On_Me.pdf</t>
+  </si>
+  <si>
+    <t>Github Link Fomula</t>
+  </si>
+  <si>
+    <t>Final Link Formula</t>
+  </si>
+  <si>
+    <t>End Result Here</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Imagine.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/1eeef250340a418d9cbdd09dc39f9fe4" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Satisfaction.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Respect.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/051f4e3081b841b99f6416795279f117" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Good_Vibrations.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/37f9938dcde54573805b2a7d92f0a1a8" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Yesterday.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/42205040200945fbb5aa4c064ae81611" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Layla.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Still_The_One.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/7717e6eb85734832869d6f9b6052ebba" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Born_To_Run.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/78461eacbe8f493587113fd7158e7e45" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Rhythm_Nation.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/e6656cfc4f184010a758bf06dc03d44c" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Move_On_Up.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/8cedcb708e2b4188b2913be4a3e755de" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Sweet_Coroline.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/479f8bedba354a3cbcd38f750d2b5ee1" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Rising_Sun.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/947aaf514af34f30a3b1b74ad6d53f86" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Here_Comes_The_Sun.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/401387cf236a4cb29231fb05c16da963" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Three_Little_Birds.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/38b5f1e44d5f4ef991878af7089a65da" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Stand_By_Me.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/My_Girl.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/b7986d5c12bb435d87caee93a693c170" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Whole_Lotta_Love.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/8ff1bfaf8f1b44b196157f476b9d15e6" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Sweet_Dreams.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Beautiful_Morning.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/9641df1bdecf4eb8b682635658efbe5b" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Under_Pressure.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/4b4d091ffa6e4822a8e1166cf12be1af" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Johnny_B_Goode.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/4b0b4b7c1aa54dff9cf60b1e21bc192a" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Free_Bird.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Shout.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/c2f4608676e24913942d72cd08374f85" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Staying_Alive.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/6f069a2a8e794fe7b2b912468c0e5efd" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Brown_Eyed_Girl.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/095791f5a6084c54ac115b04d6becdb7" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Rocket_Man.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/7adf3930fcb64740986c55e34aa3d850" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Hey_Jude.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/fa694db04a254e98b483023c8b1a7517" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Superfly.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Limelight.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/52c10d9e02824495a80923576db9ef72" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Lean_On_Me.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1420,13 +1654,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -1442,18 +1669,19 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <i/>
       <sz val="12"/>
       <color rgb="FF222222"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1470,11 +1698,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1485,8 +1708,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1501,19 +1729,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1559,11 +1774,171 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1571,10 +1946,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1603,138 +1978,116 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="17" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Bad" xfId="1" builtinId="27"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Input" xfId="2" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1753,10 +2106,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2096,105 +2445,104 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69257E43-B717-415B-87B6-EDDB262DB689}">
-  <dimension ref="A1:Q174"/>
-  <sheetFormatPr defaultRowHeight="19" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:T174"/>
+  <sheetFormatPr defaultRowHeight="19" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="25.36328125" customWidth="1"/>
-    <col min="2" max="2" width="4.26953125" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" customWidth="1"/>
-    <col min="4" max="4" width="2.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.33203125" customWidth="1"/>
+    <col min="2" max="2" width="4.25" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" customWidth="1"/>
+    <col min="4" max="4" width="2.1640625" customWidth="1"/>
     <col min="5" max="5" width="87" customWidth="1"/>
-    <col min="6" max="6" width="50.1796875" customWidth="1"/>
-    <col min="7" max="7" width="52.90625" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" customWidth="1"/>
-    <col min="12" max="12" width="162.54296875" customWidth="1"/>
-    <col min="13" max="13" width="79.08984375" customWidth="1"/>
+    <col min="6" max="6" width="63.83203125" customWidth="1"/>
+    <col min="7" max="7" width="73.9140625" customWidth="1"/>
+    <col min="8" max="8" width="11.25" customWidth="1"/>
+    <col min="12" max="12" width="81.6640625" customWidth="1"/>
+    <col min="13" max="13" width="100.58203125" customWidth="1"/>
     <col min="14" max="14" width="54" customWidth="1"/>
-    <col min="15" max="15" width="58.54296875" customWidth="1"/>
-    <col min="17" max="17" width="79.453125" customWidth="1"/>
+    <col min="15" max="15" width="121.25" customWidth="1"/>
+    <col min="17" max="17" width="55.83203125" customWidth="1"/>
+    <col min="18" max="18" width="32.9140625" customWidth="1"/>
+    <col min="20" max="20" width="148.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30"/>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="G1" s="30"/>
-    </row>
-    <row r="2" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="F2" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="G2" s="30"/>
-    </row>
-    <row r="3" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="63" t="s">
+    <row r="1" spans="1:7" ht="19" customHeight="1">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="G1" s="11"/>
+    </row>
+    <row r="2" spans="1:7" ht="19" customHeight="1">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="G2" s="11"/>
+    </row>
+    <row r="3" spans="1:7" ht="19" customHeight="1">
+      <c r="A3" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="51"/>
-    </row>
-    <row r="4" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="26"/>
+    </row>
+    <row r="4" spans="1:7" ht="19" customHeight="1">
+      <c r="A4" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>322</v>
-      </c>
-      <c r="H4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
+      <c r="D4" s="12"/>
+      <c r="E4" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="3">
         <v>409</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="41" t="s">
-        <v>170</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="G5" s="52"/>
-    </row>
-    <row r="6" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D5" s="3"/>
+      <c r="E5" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" spans="1:7" ht="19" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -2205,16 +2553,13 @@
         <v>540</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="42"/>
+      <c r="E6" s="35"/>
       <c r="F6" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="G6" s="52"/>
-      <c r="H6" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="1:7" ht="19" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -2225,18 +2570,13 @@
         <v>648</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="42" t="s">
-        <v>171</v>
-      </c>
+      <c r="E7" s="35"/>
       <c r="F7" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="G7" s="52"/>
-      <c r="H7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+        <v>216</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" spans="1:7" ht="19" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -2247,13 +2587,13 @@
         <v>702</v>
       </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="43" t="s">
-        <v>175</v>
-      </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="53"/>
-    </row>
-    <row r="9" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E8" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:7" ht="19" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -2264,15 +2604,15 @@
         <v>756</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="F9" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="G9" s="30"/>
-    </row>
-    <row r="10" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E9" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="G9" s="12"/>
+    </row>
+    <row r="10" spans="1:7" ht="19" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -2283,15 +2623,15 @@
         <v>810</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="G10" s="54"/>
-    </row>
-    <row r="11" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E10" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="G10" s="13"/>
+    </row>
+    <row r="11" spans="1:7" ht="19" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -2302,13 +2642,13 @@
         <v>891</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="43" t="s">
-        <v>178</v>
-      </c>
-      <c r="F11" s="32"/>
-      <c r="G11" s="30"/>
-    </row>
-    <row r="12" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E11" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+    </row>
+    <row r="12" spans="1:7" ht="19" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -2319,13 +2659,13 @@
         <v>840</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="F12" s="32"/>
-      <c r="G12" s="30"/>
-    </row>
-    <row r="13" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E12" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+    </row>
+    <row r="13" spans="1:7" ht="19" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -2336,15 +2676,15 @@
         <v>900</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="F13" s="32" t="s">
-        <v>217</v>
-      </c>
-      <c r="G13" s="30"/>
-    </row>
-    <row r="14" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E13" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="G13" s="12"/>
+    </row>
+    <row r="14" spans="1:7" ht="19" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -2355,13 +2695,13 @@
         <v>990</v>
       </c>
       <c r="D14" s="3"/>
-      <c r="E14" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="F14" s="32"/>
-      <c r="G14" s="30"/>
-    </row>
-    <row r="15" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E14" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+    </row>
+    <row r="15" spans="1:7" ht="19" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -2372,15 +2712,15 @@
         <v>547</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="43" t="s">
-        <v>169</v>
-      </c>
-      <c r="F15" s="32" t="s">
-        <v>222</v>
-      </c>
-      <c r="G15" s="30"/>
-    </row>
-    <row r="16" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E15" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="G15" s="12"/>
+    </row>
+    <row r="16" spans="1:7" ht="19" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -2391,13 +2731,13 @@
         <v>800</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="43" t="s">
-        <v>182</v>
-      </c>
-      <c r="F16" s="32"/>
-      <c r="G16" s="30"/>
-    </row>
-    <row r="17" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E16" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+    </row>
+    <row r="17" spans="1:7" ht="19" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -2408,15 +2748,15 @@
         <v>944</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="43" t="s">
-        <v>183</v>
-      </c>
-      <c r="F17" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="G17" s="30"/>
-    </row>
-    <row r="18" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E17" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="G17" s="12"/>
+    </row>
+    <row r="18" spans="1:7" ht="19" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -2427,13 +2767,13 @@
         <v>1101</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="F18" s="32"/>
-      <c r="G18" s="30"/>
-    </row>
-    <row r="19" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E18" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+    </row>
+    <row r="19" spans="1:7" ht="19" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -2444,13 +2784,13 @@
         <v>864</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="43" t="s">
-        <v>185</v>
-      </c>
-      <c r="F19" s="32"/>
-      <c r="G19" s="30"/>
-    </row>
-    <row r="20" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E19" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+    </row>
+    <row r="20" spans="1:7" ht="19" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -2461,15 +2801,15 @@
         <v>900</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>219</v>
-      </c>
-      <c r="G20" s="30"/>
-    </row>
-    <row r="21" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E20" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="G20" s="12"/>
+    </row>
+    <row r="21" spans="1:7" ht="19" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -2480,15 +2820,15 @@
         <v>900</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="G21" s="30"/>
-    </row>
-    <row r="22" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E21" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="G21" s="12"/>
+    </row>
+    <row r="22" spans="1:7" ht="19" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -2499,13 +2839,13 @@
         <v>1152</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="43" t="s">
-        <v>188</v>
-      </c>
-      <c r="F22" s="32"/>
-      <c r="G22" s="30"/>
-    </row>
-    <row r="23" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E22" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+    </row>
+    <row r="23" spans="1:7" ht="19" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -2516,13 +2856,13 @@
         <v>1176</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="F23" s="32"/>
-      <c r="G23" s="30"/>
-    </row>
-    <row r="24" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E23" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+    </row>
+    <row r="24" spans="1:7" ht="19" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -2533,15 +2873,15 @@
         <v>1188</v>
       </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="F24" s="33" t="s">
-        <v>225</v>
-      </c>
-      <c r="G24" s="54"/>
-    </row>
-    <row r="25" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E24" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="G24" s="13"/>
+    </row>
+    <row r="25" spans="1:7" ht="19" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -2552,15 +2892,15 @@
         <v>1188</v>
       </c>
       <c r="D25" s="3"/>
-      <c r="E25" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="F25" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="G25" s="30"/>
-    </row>
-    <row r="26" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E25" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="G25" s="12"/>
+    </row>
+    <row r="26" spans="1:7" ht="19" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,15 +2911,15 @@
         <v>1296</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="F26" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="G26" s="30"/>
-    </row>
-    <row r="27" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E26" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="G26" s="12"/>
+    </row>
+    <row r="27" spans="1:7" ht="19" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -2590,15 +2930,15 @@
         <v>1296</v>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="F27" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="G27" s="54"/>
-    </row>
-    <row r="28" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E27" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="G27" s="13"/>
+    </row>
+    <row r="28" spans="1:7" ht="19" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,15 +2949,15 @@
         <v>1296</v>
       </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="43" t="s">
-        <v>194</v>
-      </c>
-      <c r="F28" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="G28" s="30"/>
-    </row>
-    <row r="29" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E28" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="G28" s="12"/>
+    </row>
+    <row r="29" spans="1:7" ht="19" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -2628,15 +2968,15 @@
         <v>1296</v>
       </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="F29" s="32" t="s">
-        <v>228</v>
-      </c>
-      <c r="G29" s="30"/>
-    </row>
-    <row r="30" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E29" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="G29" s="12"/>
+    </row>
+    <row r="30" spans="1:7" ht="19" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
@@ -2647,15 +2987,15 @@
         <v>1296</v>
       </c>
       <c r="D30" s="3"/>
-      <c r="E30" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="F30" s="33" t="s">
-        <v>229</v>
-      </c>
-      <c r="G30" s="54"/>
-    </row>
-    <row r="31" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E30" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="G30" s="13"/>
+    </row>
+    <row r="31" spans="1:7" ht="19" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -2666,13 +3006,13 @@
         <v>1404</v>
       </c>
       <c r="D31" s="3"/>
-      <c r="E31" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="F31" s="32"/>
-      <c r="G31" s="30"/>
-    </row>
-    <row r="32" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E31" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+    </row>
+    <row r="32" spans="1:7" ht="19" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
@@ -2683,13 +3023,13 @@
         <v>1512</v>
       </c>
       <c r="D32" s="3"/>
-      <c r="E32" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="F32" s="32"/>
-      <c r="G32" s="30"/>
-    </row>
-    <row r="33" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E32" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+    </row>
+    <row r="33" spans="1:17" ht="19" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
@@ -2700,15 +3040,15 @@
         <v>1512</v>
       </c>
       <c r="D33" s="3"/>
-      <c r="E33" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="F33" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="G33" s="30"/>
-    </row>
-    <row r="34" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E33" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="G33" s="12"/>
+    </row>
+    <row r="34" spans="1:17" ht="19" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
@@ -2719,15 +3059,15 @@
         <v>1512</v>
       </c>
       <c r="D34" s="3"/>
-      <c r="E34" s="43" t="s">
-        <v>200</v>
-      </c>
-      <c r="F34" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="G34" s="30"/>
-    </row>
-    <row r="35" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E34" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="G34" s="12"/>
+    </row>
+    <row r="35" spans="1:17" ht="19" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
@@ -2738,13 +3078,13 @@
         <v>1512</v>
       </c>
       <c r="D35" s="3"/>
-      <c r="E35" s="43" t="s">
-        <v>201</v>
-      </c>
-      <c r="F35" s="32"/>
-      <c r="G35" s="30"/>
-    </row>
-    <row r="36" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E35" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+    </row>
+    <row r="36" spans="1:17" ht="19" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
@@ -2755,15 +3095,15 @@
         <v>1620</v>
       </c>
       <c r="D36" s="3"/>
-      <c r="E36" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="F36" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G36" s="54"/>
-    </row>
-    <row r="37" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E36" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="G36" s="13"/>
+    </row>
+    <row r="37" spans="1:17" ht="19" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
@@ -2774,13 +3114,13 @@
         <v>1836</v>
       </c>
       <c r="D37" s="3"/>
-      <c r="E37" s="43" t="s">
-        <v>203</v>
-      </c>
-      <c r="F37" s="32"/>
-      <c r="G37" s="30"/>
-    </row>
-    <row r="38" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E37" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+    </row>
+    <row r="38" spans="1:17" ht="19" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -2791,83 +3131,83 @@
         <v>1836</v>
       </c>
       <c r="D38" s="3"/>
-      <c r="E38" s="43" t="s">
-        <v>204</v>
-      </c>
-      <c r="F38" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="G38" s="30"/>
-    </row>
-    <row r="39" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="16" t="s">
+      <c r="E38" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="G38" s="12"/>
+    </row>
+    <row r="39" spans="1:17" ht="19" customHeight="1">
+      <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="18">
+      <c r="C39" s="3">
         <v>1917</v>
       </c>
-      <c r="D39" s="18"/>
-      <c r="E39" s="44" t="s">
+      <c r="D39" s="3"/>
+      <c r="E39" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="G39" s="12"/>
+    </row>
+    <row r="40" spans="1:17" ht="19" customHeight="1">
+      <c r="A40" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B40" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="12"/>
+      <c r="E40" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="F40" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="F39" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="G39" s="30"/>
-    </row>
-    <row r="40" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D40" s="30"/>
-      <c r="E40" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="G40" s="15" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="20" t="s">
+      <c r="G40" s="27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="47.5" customHeight="1">
+      <c r="A41" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C41" s="13">
+      <c r="C41" s="3">
         <v>852</v>
       </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="F41" s="31"/>
-      <c r="G41" s="59" t="s">
-        <v>323</v>
-      </c>
-      <c r="L41" s="62" t="s">
-        <v>361</v>
-      </c>
-      <c r="M41" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N41" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O41" s="62" t="s">
-        <v>364</v>
+      <c r="D41" s="3"/>
+      <c r="E41" s="28" t="s">
+        <v>333</v>
+      </c>
+      <c r="F41" s="12"/>
+      <c r="G41" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L41" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="M41" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N41" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O41" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q41" t="str">
         <f>M41&amp;E41&amp;N41&amp;G41&amp;O41</f>
@@ -2876,7 +3216,7 @@
 &lt;p&gt;&lt;a href="https://my.matterport.com/show/?play=1&amp;m=MgaR4onYsZB" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" ht="47.5" customHeight="1">
       <c r="A42" s="4" t="s">
         <v>39</v>
       </c>
@@ -2887,22 +3227,22 @@
         <v>958</v>
       </c>
       <c r="D42" s="3"/>
-      <c r="E42" s="32" t="s">
-        <v>341</v>
-      </c>
-      <c r="F42" s="32"/>
-      <c r="G42" s="30" t="s">
-        <v>332</v>
-      </c>
-      <c r="L42" s="61"/>
-      <c r="M42" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N42" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O42" s="62" t="s">
-        <v>364</v>
+      <c r="E42" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="L42" s="23"/>
+      <c r="M42" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N42" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O42" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q42" t="str">
         <f t="shared" ref="Q42:Q61" si="0">M42&amp;E42&amp;N42&amp;G42&amp;O42</f>
@@ -2911,7 +3251,7 @@
 &lt;p&gt;&lt;a href="https://my.matterport.com/show/?play=1&amp;m=Mac4ayKuY7Q" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="47.5" customHeight="1">
       <c r="A43" s="4" t="s">
         <v>40</v>
       </c>
@@ -2922,24 +3262,24 @@
         <v>1026</v>
       </c>
       <c r="D43" s="3"/>
-      <c r="E43" s="32" t="s">
-        <v>342</v>
-      </c>
-      <c r="F43" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="G43" s="52" t="s">
-        <v>324</v>
-      </c>
-      <c r="L43" s="61"/>
-      <c r="M43" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N43" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O43" s="62" t="s">
-        <v>364</v>
+      <c r="E43" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="L43" s="23"/>
+      <c r="M43" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N43" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O43" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q43" t="str">
         <f t="shared" si="0"/>
@@ -2948,7 +3288,7 @@
 &lt;p&gt;&lt;a href="https://my.matterport.com/show/?play=1&amp;m=fKycYYa7n6n" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" ht="47.5" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>41</v>
       </c>
@@ -2959,20 +3299,20 @@
         <v>1296</v>
       </c>
       <c r="D44" s="3"/>
-      <c r="E44" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F44" s="32"/>
-      <c r="G44" s="30"/>
-      <c r="L44" s="61"/>
-      <c r="M44" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N44" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O44" s="62" t="s">
-        <v>364</v>
+      <c r="E44" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="L44" s="23"/>
+      <c r="M44" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N44" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O44" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q44" t="str">
         <f t="shared" si="0"/>
@@ -2981,7 +3321,7 @@
 &lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" ht="47.5" customHeight="1">
       <c r="A45" s="4" t="s">
         <v>42</v>
       </c>
@@ -2992,22 +3332,22 @@
         <v>1296</v>
       </c>
       <c r="D45" s="3"/>
-      <c r="E45" s="32" t="s">
-        <v>344</v>
-      </c>
-      <c r="F45" s="32"/>
-      <c r="G45" s="30" t="s">
-        <v>325</v>
-      </c>
-      <c r="L45" s="61"/>
-      <c r="M45" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N45" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O45" s="62" t="s">
-        <v>364</v>
+      <c r="E45" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="L45" s="23"/>
+      <c r="M45" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N45" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O45" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q45" t="str">
         <f t="shared" si="0"/>
@@ -3016,7 +3356,7 @@
 &lt;p&gt;&lt;a href="https://my.matterport.com/show?play=1&amp;lang=en-US&amp;m=DaQBmJEBKY6" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" ht="47.5" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>43</v>
       </c>
@@ -3027,22 +3367,22 @@
         <v>1404</v>
       </c>
       <c r="D46" s="3"/>
-      <c r="E46" s="32" t="s">
-        <v>345</v>
-      </c>
-      <c r="F46" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="G46" s="30"/>
-      <c r="L46" s="61"/>
-      <c r="M46" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N46" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O46" s="62" t="s">
-        <v>364</v>
+      <c r="E46" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="G46" s="12"/>
+      <c r="L46" s="23"/>
+      <c r="M46" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N46" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O46" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q46" t="str">
         <f>M46&amp;E46&amp;N46&amp;F46&amp;O46</f>
@@ -3051,7 +3391,7 @@
 &lt;p&gt;&lt;a href="https://momento360.com/e/uc/e5c1afd139f44056a111566c62a66a91" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" ht="47.5" customHeight="1">
       <c r="A47" s="4" t="s">
         <v>44</v>
       </c>
@@ -3062,20 +3402,20 @@
         <v>1404</v>
       </c>
       <c r="D47" s="3"/>
-      <c r="E47" s="32" t="s">
-        <v>346</v>
-      </c>
-      <c r="F47" s="32"/>
-      <c r="G47" s="30"/>
-      <c r="L47" s="61"/>
-      <c r="M47" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N47" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O47" s="62" t="s">
-        <v>364</v>
+      <c r="E47" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="L47" s="23"/>
+      <c r="M47" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N47" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O47" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q47" t="str">
         <f t="shared" si="0"/>
@@ -3084,7 +3424,7 @@
 &lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" ht="47.5" customHeight="1">
       <c r="A48" s="4" t="s">
         <v>45</v>
       </c>
@@ -3095,24 +3435,24 @@
         <v>1512</v>
       </c>
       <c r="D48" s="3"/>
-      <c r="E48" s="32" t="s">
-        <v>347</v>
-      </c>
-      <c r="F48" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="G48" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="L48" s="61"/>
-      <c r="M48" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N48" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O48" s="62" t="s">
-        <v>364</v>
+      <c r="E48" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="L48" s="23"/>
+      <c r="M48" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N48" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O48" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q48" t="str">
         <f t="shared" si="0"/>
@@ -3121,7 +3461,7 @@
 &lt;p&gt;&lt;a href="https://my.matterport.com/show/?play=1&amp;m=iUG3qkNrKfa" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" ht="47.5" customHeight="1">
       <c r="A49" s="4" t="s">
         <v>46</v>
       </c>
@@ -3132,20 +3472,20 @@
         <v>1512</v>
       </c>
       <c r="D49" s="3"/>
-      <c r="E49" s="32" t="s">
-        <v>348</v>
-      </c>
-      <c r="F49" s="32"/>
-      <c r="G49" s="30"/>
-      <c r="L49" s="61"/>
-      <c r="M49" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N49" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O49" s="62" t="s">
-        <v>364</v>
+      <c r="E49" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="L49" s="23"/>
+      <c r="M49" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N49" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O49" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q49" t="str">
         <f t="shared" si="0"/>
@@ -3154,7 +3494,7 @@
 &lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" ht="47.5" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>47</v>
       </c>
@@ -3165,22 +3505,22 @@
         <v>1512</v>
       </c>
       <c r="D50" s="3"/>
-      <c r="E50" s="32" t="s">
-        <v>349</v>
-      </c>
-      <c r="F50" s="33" t="s">
-        <v>237</v>
-      </c>
-      <c r="G50" s="54"/>
-      <c r="L50" s="61"/>
-      <c r="M50" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N50" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O50" s="62" t="s">
-        <v>364</v>
+      <c r="E50" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="G50" s="13"/>
+      <c r="L50" s="23"/>
+      <c r="M50" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N50" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O50" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q50" t="str">
         <f>M50&amp;E50&amp;N50&amp;F50&amp;O50</f>
@@ -3189,7 +3529,7 @@
 &lt;p&gt;&lt;a href="https://momento360.com/e/uc/d4eebf0274f4454fa5f84f43c9d45ba3" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" ht="47.5" customHeight="1">
       <c r="A51" s="4" t="s">
         <v>48</v>
       </c>
@@ -3200,20 +3540,20 @@
         <v>1512</v>
       </c>
       <c r="D51" s="3"/>
-      <c r="E51" s="32" t="s">
-        <v>350</v>
-      </c>
-      <c r="F51" s="32"/>
-      <c r="G51" s="30"/>
-      <c r="L51" s="61"/>
-      <c r="M51" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N51" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O51" s="62" t="s">
-        <v>364</v>
+      <c r="E51" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="L51" s="23"/>
+      <c r="M51" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N51" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O51" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q51" t="str">
         <f t="shared" si="0"/>
@@ -3222,7 +3562,7 @@
 &lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="52" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" ht="47.5" customHeight="1">
       <c r="A52" s="4" t="s">
         <v>49</v>
       </c>
@@ -3233,22 +3573,22 @@
         <v>1620</v>
       </c>
       <c r="D52" s="3"/>
-      <c r="E52" s="32" t="s">
-        <v>351</v>
-      </c>
-      <c r="F52" s="32"/>
-      <c r="G52" s="52" t="s">
-        <v>327</v>
-      </c>
-      <c r="L52" s="61"/>
-      <c r="M52" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N52" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O52" s="62" t="s">
-        <v>364</v>
+      <c r="E52" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="F52" s="12"/>
+      <c r="G52" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="L52" s="23"/>
+      <c r="M52" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N52" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O52" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q52" t="str">
         <f t="shared" si="0"/>
@@ -3257,7 +3597,7 @@
 &lt;p&gt;&lt;a href="https://my.matterport.com/show/?play=1&amp;m=QkyD1Gqr67p" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" ht="47.5" customHeight="1">
       <c r="A53" s="4" t="s">
         <v>50</v>
       </c>
@@ -3268,20 +3608,20 @@
         <v>1782</v>
       </c>
       <c r="D53" s="3"/>
-      <c r="E53" s="32" t="s">
-        <v>352</v>
-      </c>
-      <c r="F53" s="32"/>
-      <c r="G53" s="30"/>
-      <c r="L53" s="61"/>
-      <c r="M53" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N53" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O53" s="62" t="s">
-        <v>364</v>
+      <c r="E53" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="L53" s="23"/>
+      <c r="M53" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N53" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O53" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q53" t="str">
         <f t="shared" si="0"/>
@@ -3290,7 +3630,7 @@
 &lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" ht="47.5" customHeight="1">
       <c r="A54" s="4" t="s">
         <v>51</v>
       </c>
@@ -3301,22 +3641,22 @@
         <v>1836</v>
       </c>
       <c r="D54" s="3"/>
-      <c r="E54" s="32" t="s">
-        <v>353</v>
-      </c>
-      <c r="F54" s="32" t="s">
-        <v>238</v>
-      </c>
-      <c r="G54" s="30"/>
-      <c r="L54" s="61"/>
-      <c r="M54" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N54" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O54" s="62" t="s">
-        <v>364</v>
+      <c r="E54" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="G54" s="12"/>
+      <c r="L54" s="23"/>
+      <c r="M54" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N54" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O54" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q54" t="str">
         <f>M54&amp;E54&amp;N54&amp;F54&amp;O54</f>
@@ -3325,7 +3665,7 @@
 &lt;p&gt;&lt;a href="https://momento360.com/e/uc/82c50572b7cb4955a9e8bd9223e45cf0" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" ht="47.5" customHeight="1">
       <c r="A55" s="4" t="s">
         <v>52</v>
       </c>
@@ -3336,20 +3676,20 @@
         <v>1836</v>
       </c>
       <c r="D55" s="3"/>
-      <c r="E55" s="32" t="s">
-        <v>354</v>
-      </c>
-      <c r="F55" s="32"/>
-      <c r="G55" s="30"/>
-      <c r="L55" s="61"/>
-      <c r="M55" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N55" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O55" s="62" t="s">
-        <v>364</v>
+      <c r="E55" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="L55" s="23"/>
+      <c r="M55" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N55" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O55" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q55" t="str">
         <f t="shared" si="0"/>
@@ -3358,7 +3698,7 @@
 &lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" ht="47.5" customHeight="1">
       <c r="A56" s="4" t="s">
         <v>53</v>
       </c>
@@ -3369,22 +3709,22 @@
         <v>2280</v>
       </c>
       <c r="D56" s="3"/>
-      <c r="E56" s="32" t="s">
+      <c r="E56" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="L56" s="23"/>
+      <c r="M56" s="24" t="s">
         <v>355</v>
       </c>
-      <c r="F56" s="32"/>
-      <c r="G56" s="30" t="s">
-        <v>328</v>
-      </c>
-      <c r="L56" s="61"/>
-      <c r="M56" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N56" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O56" s="62" t="s">
-        <v>364</v>
+      <c r="N56" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O56" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q56" t="str">
         <f t="shared" si="0"/>
@@ -3393,7 +3733,7 @@
 &lt;p&gt;&lt;a href="https://my.matterport.com/show/?m=o6SZeYvAzTd" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" ht="47.5" customHeight="1">
       <c r="A57" s="4" t="s">
         <v>54</v>
       </c>
@@ -3404,20 +3744,20 @@
         <v>2280</v>
       </c>
       <c r="D57" s="3"/>
-      <c r="E57" s="32" t="s">
+      <c r="E57" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="L57" s="23"/>
+      <c r="M57" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N57" s="24" t="s">
         <v>356</v>
       </c>
-      <c r="F57" s="32"/>
-      <c r="G57" s="30"/>
-      <c r="L57" s="61"/>
-      <c r="M57" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N57" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O57" s="62" t="s">
-        <v>364</v>
+      <c r="O57" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q57" t="str">
         <f t="shared" si="0"/>
@@ -3426,7 +3766,7 @@
 &lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" ht="47.5" customHeight="1">
       <c r="A58" s="4" t="s">
         <v>55</v>
       </c>
@@ -3437,20 +3777,20 @@
         <v>2347</v>
       </c>
       <c r="D58" s="3"/>
-      <c r="E58" s="32" t="s">
+      <c r="E58" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="L58" s="23"/>
+      <c r="M58" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N58" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O58" s="24" t="s">
         <v>357</v>
-      </c>
-      <c r="F58" s="32"/>
-      <c r="G58" s="30"/>
-      <c r="L58" s="61"/>
-      <c r="M58" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N58" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O58" s="62" t="s">
-        <v>364</v>
       </c>
       <c r="Q58" t="str">
         <f t="shared" si="0"/>
@@ -3459,7 +3799,7 @@
 &lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" ht="47.5" customHeight="1">
       <c r="A59" s="4" t="s">
         <v>56</v>
       </c>
@@ -3470,20 +3810,20 @@
         <v>2347</v>
       </c>
       <c r="D59" s="3"/>
-      <c r="E59" s="32" t="s">
-        <v>358</v>
-      </c>
-      <c r="F59" s="32"/>
-      <c r="G59" s="30"/>
-      <c r="L59" s="61"/>
-      <c r="M59" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N59" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O59" s="62" t="s">
-        <v>364</v>
+      <c r="E59" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="L59" s="23"/>
+      <c r="M59" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N59" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O59" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q59" t="str">
         <f t="shared" si="0"/>
@@ -3492,7 +3832,7 @@
 &lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" ht="47.5" customHeight="1">
       <c r="A60" s="4" t="s">
         <v>57</v>
       </c>
@@ -3503,22 +3843,22 @@
         <v>2038</v>
       </c>
       <c r="D60" s="3"/>
-      <c r="E60" s="32" t="s">
-        <v>359</v>
-      </c>
-      <c r="F60" s="32" t="s">
-        <v>239</v>
-      </c>
-      <c r="G60" s="30"/>
-      <c r="L60" s="61"/>
-      <c r="M60" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N60" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O60" s="62" t="s">
-        <v>364</v>
+      <c r="E60" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="G60" s="12"/>
+      <c r="L60" s="23"/>
+      <c r="M60" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N60" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O60" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q60" t="str">
         <f>M60&amp;E60&amp;N60&amp;F60&amp;O60</f>
@@ -3527,7 +3867,7 @@
 &lt;p&gt;&lt;a href="https://momento360.com/e/uc/3d33004720554c6c96b4f5dfbb605b25" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" ht="47.5" customHeight="1">
       <c r="A61" s="4" t="s">
         <v>58</v>
       </c>
@@ -3538,20 +3878,20 @@
         <v>2654</v>
       </c>
       <c r="D61" s="3"/>
-      <c r="E61" s="32" t="s">
-        <v>360</v>
-      </c>
-      <c r="F61" s="32"/>
-      <c r="G61" s="30"/>
-      <c r="L61" s="61"/>
-      <c r="M61" s="62" t="s">
-        <v>362</v>
-      </c>
-      <c r="N61" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="O61" s="62" t="s">
-        <v>364</v>
+      <c r="E61" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="L61" s="23"/>
+      <c r="M61" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="N61" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="O61" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="Q61" t="str">
         <f t="shared" si="0"/>
@@ -3560,61 +3900,61 @@
 &lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="64" t="s">
+    <row r="62" spans="1:17" ht="19" customHeight="1">
+      <c r="A62" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="B62" s="64"/>
-      <c r="C62" s="64"/>
-      <c r="D62" s="64"/>
-      <c r="E62" s="64"/>
-      <c r="F62" s="64"/>
-      <c r="G62" s="55"/>
-      <c r="L62" s="61"/>
-      <c r="M62" s="60"/>
-      <c r="N62" s="61"/>
-    </row>
-    <row r="63" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="15" t="s">
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="29"/>
+      <c r="E62" s="29"/>
+      <c r="F62" s="29"/>
+      <c r="G62" s="30"/>
+      <c r="L62" s="23"/>
+      <c r="M62" s="22"/>
+      <c r="N62" s="23"/>
+    </row>
+    <row r="63" spans="1:17" ht="19" customHeight="1">
+      <c r="A63" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="B63" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C63" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D63" s="30"/>
-      <c r="E63" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="F63" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="G63" s="15" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="21">
+      <c r="D63" s="12"/>
+      <c r="E63" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="F63" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="G63" s="27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" ht="19" customHeight="1">
+      <c r="A64" s="5">
         <v>1001</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C64" s="13">
+      <c r="C64" s="3">
         <v>480</v>
       </c>
-      <c r="D64" s="13"/>
-      <c r="E64" s="41" t="s">
-        <v>207</v>
-      </c>
-      <c r="F64" s="31"/>
-      <c r="G64" s="30" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D64" s="3"/>
+      <c r="E64" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="19" customHeight="1">
       <c r="A65" s="5">
         <v>1002</v>
       </c>
@@ -3625,13 +3965,13 @@
         <v>533</v>
       </c>
       <c r="D65" s="3"/>
-      <c r="E65" s="41" t="s">
-        <v>240</v>
-      </c>
-      <c r="F65" s="32"/>
-      <c r="G65" s="30"/>
-    </row>
-    <row r="66" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E65" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+    </row>
+    <row r="66" spans="1:7" ht="19" customHeight="1">
       <c r="A66" s="5">
         <v>1003</v>
       </c>
@@ -3642,13 +3982,13 @@
         <v>640</v>
       </c>
       <c r="D66" s="3"/>
-      <c r="E66" s="41" t="s">
-        <v>241</v>
-      </c>
-      <c r="F66" s="32"/>
-      <c r="G66" s="30"/>
-    </row>
-    <row r="67" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E66" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+    </row>
+    <row r="67" spans="1:7" ht="19" customHeight="1">
       <c r="A67" s="5">
         <v>1004</v>
       </c>
@@ -3659,13 +3999,13 @@
         <v>746</v>
       </c>
       <c r="D67" s="3"/>
-      <c r="E67" s="41" t="s">
-        <v>242</v>
-      </c>
-      <c r="F67" s="32"/>
-      <c r="G67" s="30"/>
-    </row>
-    <row r="68" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E67" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+    </row>
+    <row r="68" spans="1:7" ht="19" customHeight="1">
       <c r="A68" s="5">
         <v>1005</v>
       </c>
@@ -3676,13 +4016,13 @@
         <v>800</v>
       </c>
       <c r="D68" s="3"/>
-      <c r="E68" s="41" t="s">
-        <v>243</v>
-      </c>
-      <c r="F68" s="32"/>
-      <c r="G68" s="30"/>
-    </row>
-    <row r="69" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E68" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+    </row>
+    <row r="69" spans="1:7" ht="19" customHeight="1">
       <c r="A69" s="5">
         <v>1006</v>
       </c>
@@ -3693,13 +4033,13 @@
         <v>720</v>
       </c>
       <c r="D69" s="3"/>
-      <c r="E69" s="41" t="s">
-        <v>244</v>
-      </c>
-      <c r="F69" s="32"/>
-      <c r="G69" s="30"/>
-    </row>
-    <row r="70" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E69" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+    </row>
+    <row r="70" spans="1:7" ht="19" customHeight="1">
       <c r="A70" s="5">
         <v>1007</v>
       </c>
@@ -3710,13 +4050,13 @@
         <v>840</v>
       </c>
       <c r="D70" s="3"/>
-      <c r="E70" s="41" t="s">
-        <v>245</v>
-      </c>
-      <c r="F70" s="32"/>
-      <c r="G70" s="30"/>
-    </row>
-    <row r="71" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E70" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+    </row>
+    <row r="71" spans="1:7" ht="19" customHeight="1">
       <c r="A71" s="5">
         <v>1008</v>
       </c>
@@ -3727,13 +4067,13 @@
         <v>900</v>
       </c>
       <c r="D71" s="3"/>
-      <c r="E71" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="F71" s="32"/>
-      <c r="G71" s="30"/>
-    </row>
-    <row r="72" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E71" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+    </row>
+    <row r="72" spans="1:7" ht="19" customHeight="1">
       <c r="A72" s="5">
         <v>1009</v>
       </c>
@@ -3744,13 +4084,13 @@
         <v>990</v>
       </c>
       <c r="D72" s="3"/>
-      <c r="E72" s="41" t="s">
-        <v>247</v>
-      </c>
-      <c r="F72" s="32"/>
-      <c r="G72" s="30"/>
-    </row>
-    <row r="73" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E72" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+    </row>
+    <row r="73" spans="1:7" ht="19" customHeight="1">
       <c r="A73" s="5">
         <v>1010</v>
       </c>
@@ -3761,13 +4101,13 @@
         <v>1080</v>
       </c>
       <c r="D73" s="6"/>
-      <c r="E73" s="41" t="s">
-        <v>248</v>
-      </c>
-      <c r="F73" s="32"/>
-      <c r="G73" s="30"/>
-    </row>
-    <row r="74" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E73" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
+    </row>
+    <row r="74" spans="1:7" ht="19" customHeight="1">
       <c r="A74" s="5">
         <v>2015</v>
       </c>
@@ -3778,13 +4118,13 @@
         <v>1173</v>
       </c>
       <c r="D74" s="6"/>
-      <c r="E74" s="41" t="s">
-        <v>249</v>
-      </c>
-      <c r="F74" s="32"/>
-      <c r="G74" s="30"/>
-    </row>
-    <row r="75" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E74" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+    </row>
+    <row r="75" spans="1:7" ht="19" customHeight="1">
       <c r="A75" s="5">
         <v>2017</v>
       </c>
@@ -3795,15 +4135,15 @@
         <v>1280</v>
       </c>
       <c r="D75" s="6"/>
-      <c r="E75" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="F75" s="32"/>
-      <c r="G75" s="59" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E75" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="F75" s="12"/>
+      <c r="G75" s="10" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="19" customHeight="1">
       <c r="A76" s="5">
         <v>2019</v>
       </c>
@@ -3814,13 +4154,13 @@
         <v>1280</v>
       </c>
       <c r="D76" s="6"/>
-      <c r="E76" s="41" t="s">
-        <v>251</v>
-      </c>
-      <c r="F76" s="32"/>
-      <c r="G76" s="30"/>
-    </row>
-    <row r="77" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E76" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+    </row>
+    <row r="77" spans="1:7" ht="19" customHeight="1">
       <c r="A77" s="5">
         <v>2021</v>
       </c>
@@ -3831,13 +4171,13 @@
         <v>1493</v>
       </c>
       <c r="D77" s="6"/>
-      <c r="E77" s="41" t="s">
-        <v>252</v>
-      </c>
-      <c r="F77" s="32"/>
-      <c r="G77" s="30"/>
-    </row>
-    <row r="78" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E77" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
+    </row>
+    <row r="78" spans="1:7" ht="19" customHeight="1">
       <c r="A78" s="5">
         <v>2022</v>
       </c>
@@ -3848,15 +4188,15 @@
         <v>1493</v>
       </c>
       <c r="D78" s="6"/>
-      <c r="E78" s="41" t="s">
-        <v>253</v>
-      </c>
-      <c r="F78" s="32"/>
-      <c r="G78" s="59" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E78" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="F78" s="12"/>
+      <c r="G78" s="10" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="19" customHeight="1">
       <c r="A79" s="5">
         <v>2023</v>
       </c>
@@ -3867,15 +4207,15 @@
         <v>1493</v>
       </c>
       <c r="D79" s="6"/>
-      <c r="E79" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F79" s="32"/>
-      <c r="G79" s="59" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E79" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="F79" s="12"/>
+      <c r="G79" s="10" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="19" customHeight="1">
       <c r="A80" s="5">
         <v>2024</v>
       </c>
@@ -3886,13 +4226,13 @@
         <v>1600</v>
       </c>
       <c r="D80" s="6"/>
-      <c r="E80" s="41" t="s">
-        <v>255</v>
-      </c>
-      <c r="F80" s="32"/>
-      <c r="G80" s="30"/>
-    </row>
-    <row r="81" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E80" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
+    </row>
+    <row r="81" spans="1:7" ht="19" customHeight="1">
       <c r="A81" s="5">
         <v>2025</v>
       </c>
@@ -3903,13 +4243,13 @@
         <v>1814</v>
       </c>
       <c r="D81" s="6"/>
-      <c r="E81" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F81" s="32"/>
-      <c r="G81" s="30"/>
-    </row>
-    <row r="82" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E81" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
+    </row>
+    <row r="82" spans="1:7" ht="19" customHeight="1">
       <c r="A82" s="5">
         <v>2028</v>
       </c>
@@ -3920,13 +4260,13 @@
         <v>2100</v>
       </c>
       <c r="D82" s="6"/>
-      <c r="E82" s="41" t="s">
-        <v>257</v>
-      </c>
-      <c r="F82" s="32"/>
-      <c r="G82" s="30"/>
-    </row>
-    <row r="83" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E82" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
+    </row>
+    <row r="83" spans="1:7" ht="19" customHeight="1">
       <c r="A83" s="5">
         <v>2029</v>
       </c>
@@ -3937,13 +4277,13 @@
         <v>864</v>
       </c>
       <c r="D83" s="3"/>
-      <c r="E83" s="41" t="s">
-        <v>258</v>
-      </c>
-      <c r="F83" s="32"/>
-      <c r="G83" s="30"/>
-    </row>
-    <row r="84" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E83" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
+    </row>
+    <row r="84" spans="1:7" ht="19" customHeight="1">
       <c r="A84" s="5">
         <v>2030</v>
       </c>
@@ -3954,13 +4294,13 @@
         <v>1280</v>
       </c>
       <c r="D84" s="6"/>
-      <c r="E84" s="41" t="s">
-        <v>259</v>
-      </c>
-      <c r="F84" s="32"/>
-      <c r="G84" s="30"/>
-    </row>
-    <row r="85" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E84" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+    </row>
+    <row r="85" spans="1:7" ht="19" customHeight="1">
       <c r="A85" s="5">
         <v>2031</v>
       </c>
@@ -3971,13 +4311,13 @@
         <v>1280</v>
       </c>
       <c r="D85" s="6"/>
-      <c r="E85" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="F85" s="32"/>
-      <c r="G85" s="30"/>
-    </row>
-    <row r="86" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E85" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
+    </row>
+    <row r="86" spans="1:7" ht="19" customHeight="1">
       <c r="A86" s="5">
         <v>2032</v>
       </c>
@@ -3988,13 +4328,13 @@
         <v>1493</v>
       </c>
       <c r="D86" s="6"/>
-      <c r="E86" s="41" t="s">
-        <v>261</v>
-      </c>
-      <c r="F86" s="32"/>
-      <c r="G86" s="30"/>
-    </row>
-    <row r="87" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E86" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
+    </row>
+    <row r="87" spans="1:7" ht="19" customHeight="1">
       <c r="A87" s="5">
         <v>2033</v>
       </c>
@@ -4005,13 +4345,13 @@
         <v>1493</v>
       </c>
       <c r="D87" s="6"/>
-      <c r="E87" s="41" t="s">
-        <v>262</v>
-      </c>
-      <c r="F87" s="32"/>
-      <c r="G87" s="30"/>
-    </row>
-    <row r="88" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E87" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+    </row>
+    <row r="88" spans="1:7" ht="19" customHeight="1">
       <c r="A88" s="5">
         <v>2034</v>
       </c>
@@ -4022,13 +4362,13 @@
         <v>1600</v>
       </c>
       <c r="D88" s="6"/>
-      <c r="E88" s="41" t="s">
-        <v>263</v>
-      </c>
-      <c r="F88" s="32"/>
-      <c r="G88" s="30"/>
-    </row>
-    <row r="89" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E88" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
+    </row>
+    <row r="89" spans="1:7" ht="19" customHeight="1">
       <c r="A89" s="5">
         <v>2035</v>
       </c>
@@ -4039,13 +4379,13 @@
         <v>1920</v>
       </c>
       <c r="D89" s="6"/>
-      <c r="E89" s="41" t="s">
-        <v>264</v>
-      </c>
-      <c r="F89" s="32"/>
-      <c r="G89" s="30"/>
-    </row>
-    <row r="90" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E89" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="F89" s="12"/>
+      <c r="G89" s="12"/>
+    </row>
+    <row r="90" spans="1:7" ht="19" customHeight="1">
       <c r="A90" s="5">
         <v>2036</v>
       </c>
@@ -4056,13 +4396,13 @@
         <v>1056</v>
       </c>
       <c r="D90" s="6"/>
-      <c r="E90" s="41" t="s">
-        <v>265</v>
-      </c>
-      <c r="F90" s="32"/>
-      <c r="G90" s="30"/>
-    </row>
-    <row r="91" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E90" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
+    </row>
+    <row r="91" spans="1:7" ht="19" customHeight="1">
       <c r="A91" s="5">
         <v>2037</v>
       </c>
@@ -4073,66 +4413,66 @@
         <v>1344</v>
       </c>
       <c r="D91" s="6"/>
-      <c r="E91" s="41" t="s">
-        <v>266</v>
-      </c>
-      <c r="F91" s="32"/>
-      <c r="G91" s="30"/>
-    </row>
-    <row r="92" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="22">
+      <c r="E91" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
+    </row>
+    <row r="92" spans="1:7" ht="19" customHeight="1">
+      <c r="A92" s="5">
         <v>2038</v>
       </c>
-      <c r="B92" s="17" t="s">
+      <c r="B92" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C92" s="18">
+      <c r="C92" s="3">
         <v>839</v>
       </c>
-      <c r="D92" s="18"/>
-      <c r="E92" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="F92" s="35"/>
-      <c r="G92" s="30"/>
-    </row>
-    <row r="93" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="15" t="s">
+      <c r="D92" s="3"/>
+      <c r="E92" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
+    </row>
+    <row r="93" spans="1:7" ht="19" customHeight="1">
+      <c r="A93" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B93" s="15" t="s">
+      <c r="B93" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C93" s="15" t="s">
+      <c r="C93" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D93" s="30"/>
-      <c r="E93" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="F93" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="G93" s="15" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="21">
+      <c r="D93" s="12"/>
+      <c r="E93" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="F93" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="G93" s="27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="19" customHeight="1">
+      <c r="A94" s="5">
         <v>2017</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C94" s="23">
+      <c r="C94" s="6">
         <v>1440</v>
       </c>
-      <c r="D94" s="23"/>
-      <c r="E94" s="45"/>
-      <c r="F94" s="31"/>
-      <c r="G94" s="30"/>
-    </row>
-    <row r="95" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D94" s="6"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+    </row>
+    <row r="95" spans="1:7" ht="19" customHeight="1">
       <c r="A95" s="5">
         <v>2019</v>
       </c>
@@ -4143,11 +4483,11 @@
         <v>1440</v>
       </c>
       <c r="D95" s="6"/>
-      <c r="E95" s="46"/>
-      <c r="F95" s="32"/>
-      <c r="G95" s="30"/>
-    </row>
-    <row r="96" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E95" s="20"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
+    </row>
+    <row r="96" spans="1:7" ht="19" customHeight="1">
       <c r="A96" s="5">
         <v>2021</v>
       </c>
@@ -4158,11 +4498,11 @@
         <v>1680</v>
       </c>
       <c r="D96" s="6"/>
-      <c r="E96" s="46"/>
-      <c r="F96" s="32"/>
-      <c r="G96" s="30"/>
-    </row>
-    <row r="97" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E96" s="20"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
+    </row>
+    <row r="97" spans="1:7" ht="19" customHeight="1">
       <c r="A97" s="5">
         <v>2022</v>
       </c>
@@ -4173,11 +4513,11 @@
         <v>1680</v>
       </c>
       <c r="D97" s="6"/>
-      <c r="E97" s="46"/>
-      <c r="F97" s="32"/>
-      <c r="G97" s="30"/>
-    </row>
-    <row r="98" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E97" s="20"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
+    </row>
+    <row r="98" spans="1:7" ht="19" customHeight="1">
       <c r="A98" s="5">
         <v>2023</v>
       </c>
@@ -4188,11 +4528,11 @@
         <v>1680</v>
       </c>
       <c r="D98" s="6"/>
-      <c r="E98" s="46"/>
-      <c r="F98" s="32"/>
-      <c r="G98" s="30"/>
-    </row>
-    <row r="99" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E98" s="20"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
+    </row>
+    <row r="99" spans="1:7" ht="19" customHeight="1">
       <c r="A99" s="5">
         <v>2024</v>
       </c>
@@ -4203,11 +4543,11 @@
         <v>1800</v>
       </c>
       <c r="D99" s="6"/>
-      <c r="E99" s="46"/>
-      <c r="F99" s="32"/>
-      <c r="G99" s="30"/>
-    </row>
-    <row r="100" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E99" s="20"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+    </row>
+    <row r="100" spans="1:7" ht="19" customHeight="1">
       <c r="A100" s="5">
         <v>2025</v>
       </c>
@@ -4218,11 +4558,11 @@
         <v>2040</v>
       </c>
       <c r="D100" s="6"/>
-      <c r="E100" s="46"/>
-      <c r="F100" s="32"/>
-      <c r="G100" s="30"/>
-    </row>
-    <row r="101" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E100" s="20"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
+    </row>
+    <row r="101" spans="1:7" ht="19" customHeight="1">
       <c r="A101" s="5">
         <v>2029</v>
       </c>
@@ -4233,11 +4573,11 @@
         <v>960</v>
       </c>
       <c r="D101" s="3"/>
-      <c r="E101" s="46"/>
-      <c r="F101" s="32"/>
-      <c r="G101" s="30"/>
-    </row>
-    <row r="102" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E101" s="20"/>
+      <c r="F101" s="12"/>
+      <c r="G101" s="12"/>
+    </row>
+    <row r="102" spans="1:7" ht="19" customHeight="1">
       <c r="A102" s="5">
         <v>2031</v>
       </c>
@@ -4248,11 +4588,11 @@
         <v>1440</v>
       </c>
       <c r="D102" s="6"/>
-      <c r="E102" s="46"/>
-      <c r="F102" s="32"/>
-      <c r="G102" s="30"/>
-    </row>
-    <row r="103" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E102" s="20"/>
+      <c r="F102" s="12"/>
+      <c r="G102" s="12"/>
+    </row>
+    <row r="103" spans="1:7" ht="19" customHeight="1">
       <c r="A103" s="5">
         <v>2034</v>
       </c>
@@ -4263,11 +4603,11 @@
         <v>1800</v>
       </c>
       <c r="D103" s="6"/>
-      <c r="E103" s="46"/>
-      <c r="F103" s="32"/>
-      <c r="G103" s="30"/>
-    </row>
-    <row r="104" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E103" s="20"/>
+      <c r="F103" s="12"/>
+      <c r="G103" s="12"/>
+    </row>
+    <row r="104" spans="1:7" ht="19" customHeight="1">
       <c r="A104" s="5">
         <v>2035</v>
       </c>
@@ -4278,11 +4618,11 @@
         <v>2160</v>
       </c>
       <c r="D104" s="6"/>
-      <c r="E104" s="46"/>
-      <c r="F104" s="32"/>
-      <c r="G104" s="30"/>
-    </row>
-    <row r="105" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E104" s="20"/>
+      <c r="F104" s="12"/>
+      <c r="G104" s="12"/>
+    </row>
+    <row r="105" spans="1:7" ht="19" customHeight="1">
       <c r="A105" s="5">
         <v>2037</v>
       </c>
@@ -4293,64 +4633,64 @@
         <v>1413</v>
       </c>
       <c r="D105" s="6"/>
-      <c r="E105" s="46"/>
-      <c r="F105" s="32"/>
-      <c r="G105" s="30"/>
-    </row>
-    <row r="106" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="22">
+      <c r="E105" s="20"/>
+      <c r="F105" s="12"/>
+      <c r="G105" s="12"/>
+    </row>
+    <row r="106" spans="1:7" ht="19" customHeight="1">
+      <c r="A106" s="5">
         <v>2038</v>
       </c>
-      <c r="B106" s="17" t="s">
+      <c r="B106" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C106" s="24">
+      <c r="C106" s="6">
         <v>1024</v>
       </c>
-      <c r="D106" s="24"/>
-      <c r="E106" s="47"/>
-      <c r="F106" s="35"/>
-      <c r="G106" s="30"/>
-    </row>
-    <row r="107" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="15" t="s">
+      <c r="D106" s="6"/>
+      <c r="E106" s="20"/>
+      <c r="F106" s="12"/>
+      <c r="G106" s="12"/>
+    </row>
+    <row r="107" spans="1:7" ht="19" customHeight="1">
+      <c r="A107" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B107" s="15" t="s">
+      <c r="B107" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C107" s="15" t="s">
+      <c r="C107" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D107" s="30"/>
-      <c r="E107" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="F107" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="G107" s="15" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="27">
+      <c r="D107" s="12"/>
+      <c r="E107" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="F107" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="G107" s="27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="19" customHeight="1">
+      <c r="A108" s="7">
         <v>5015</v>
       </c>
-      <c r="B108" s="12" t="s">
+      <c r="B108" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C108" s="23">
+      <c r="C108" s="6">
         <v>1173</v>
       </c>
-      <c r="D108" s="23"/>
-      <c r="E108" s="48" t="s">
-        <v>206</v>
-      </c>
-      <c r="F108" s="31"/>
-      <c r="G108" s="30"/>
-    </row>
-    <row r="109" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D108" s="6"/>
+      <c r="E108" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="F108" s="12"/>
+      <c r="G108" s="12"/>
+    </row>
+    <row r="109" spans="1:7" ht="19" customHeight="1">
       <c r="A109" s="7">
         <v>5017</v>
       </c>
@@ -4361,13 +4701,13 @@
         <v>1280</v>
       </c>
       <c r="D109" s="6"/>
-      <c r="E109" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="F109" s="32"/>
-      <c r="G109" s="30"/>
-    </row>
-    <row r="110" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E109" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="F109" s="12"/>
+      <c r="G109" s="12"/>
+    </row>
+    <row r="110" spans="1:7" ht="19" customHeight="1">
       <c r="A110" s="7">
         <v>5019</v>
       </c>
@@ -4378,13 +4718,13 @@
         <v>1280</v>
       </c>
       <c r="D110" s="6"/>
-      <c r="E110" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="F110" s="32"/>
-      <c r="G110" s="30"/>
-    </row>
-    <row r="111" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E110" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="F110" s="12"/>
+      <c r="G110" s="12"/>
+    </row>
+    <row r="111" spans="1:7" ht="19" customHeight="1">
       <c r="A111" s="7">
         <v>5021</v>
       </c>
@@ -4395,13 +4735,13 @@
         <v>1493</v>
       </c>
       <c r="D111" s="6"/>
-      <c r="E111" s="36" t="s">
-        <v>270</v>
-      </c>
-      <c r="F111" s="32"/>
-      <c r="G111" s="30"/>
-    </row>
-    <row r="112" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E111" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="F111" s="12"/>
+      <c r="G111" s="12"/>
+    </row>
+    <row r="112" spans="1:7" ht="19" customHeight="1">
       <c r="A112" s="7">
         <v>5022</v>
       </c>
@@ -4412,13 +4752,13 @@
         <v>1493</v>
       </c>
       <c r="D112" s="6"/>
-      <c r="E112" s="36" t="s">
-        <v>271</v>
-      </c>
-      <c r="F112" s="32"/>
-      <c r="G112" s="30"/>
-    </row>
-    <row r="113" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E112" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="F112" s="12"/>
+      <c r="G112" s="12"/>
+    </row>
+    <row r="113" spans="1:7" ht="19" customHeight="1">
       <c r="A113" s="7">
         <v>5023</v>
       </c>
@@ -4429,13 +4769,13 @@
         <v>1493</v>
       </c>
       <c r="D113" s="6"/>
-      <c r="E113" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="F113" s="32"/>
-      <c r="G113" s="30"/>
-    </row>
-    <row r="114" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E113" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="F113" s="12"/>
+      <c r="G113" s="12"/>
+    </row>
+    <row r="114" spans="1:7" ht="19" customHeight="1">
       <c r="A114" s="7">
         <v>5024</v>
       </c>
@@ -4446,13 +4786,13 @@
         <v>1600</v>
       </c>
       <c r="D114" s="6"/>
-      <c r="E114" s="36" t="s">
-        <v>273</v>
-      </c>
-      <c r="F114" s="32"/>
-      <c r="G114" s="30"/>
-    </row>
-    <row r="115" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E114" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="F114" s="12"/>
+      <c r="G114" s="12"/>
+    </row>
+    <row r="115" spans="1:7" ht="19" customHeight="1">
       <c r="A115" s="7">
         <v>5025</v>
       </c>
@@ -4463,13 +4803,13 @@
         <v>1814</v>
       </c>
       <c r="D115" s="6"/>
-      <c r="E115" s="36" t="s">
-        <v>274</v>
-      </c>
-      <c r="F115" s="32"/>
-      <c r="G115" s="30"/>
-    </row>
-    <row r="116" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E115" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="F115" s="12"/>
+      <c r="G115" s="12"/>
+    </row>
+    <row r="116" spans="1:7" ht="19" customHeight="1">
       <c r="A116" s="7">
         <v>5028</v>
       </c>
@@ -4480,13 +4820,13 @@
         <v>2100</v>
       </c>
       <c r="D116" s="6"/>
-      <c r="E116" s="36" t="s">
-        <v>275</v>
-      </c>
-      <c r="F116" s="32"/>
-      <c r="G116" s="30"/>
-    </row>
-    <row r="117" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E116" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="F116" s="12"/>
+      <c r="G116" s="12"/>
+    </row>
+    <row r="117" spans="1:7" ht="19" customHeight="1">
       <c r="A117" s="7">
         <v>5029</v>
       </c>
@@ -4497,13 +4837,13 @@
         <v>864</v>
       </c>
       <c r="D117" s="3"/>
-      <c r="E117" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="F117" s="32"/>
-      <c r="G117" s="30"/>
-    </row>
-    <row r="118" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E117" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="F117" s="12"/>
+      <c r="G117" s="12"/>
+    </row>
+    <row r="118" spans="1:7" ht="19" customHeight="1">
       <c r="A118" s="7">
         <v>5030</v>
       </c>
@@ -4514,13 +4854,13 @@
         <v>1280</v>
       </c>
       <c r="D118" s="6"/>
-      <c r="E118" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="F118" s="32"/>
-      <c r="G118" s="30"/>
-    </row>
-    <row r="119" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E118" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="F118" s="12"/>
+      <c r="G118" s="12"/>
+    </row>
+    <row r="119" spans="1:7" ht="19" customHeight="1">
       <c r="A119" s="7">
         <v>5031</v>
       </c>
@@ -4531,13 +4871,13 @@
         <v>1280</v>
       </c>
       <c r="D119" s="6"/>
-      <c r="E119" s="36" t="s">
-        <v>278</v>
-      </c>
-      <c r="F119" s="32"/>
-      <c r="G119" s="30"/>
-    </row>
-    <row r="120" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E119" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="F119" s="12"/>
+      <c r="G119" s="12"/>
+    </row>
+    <row r="120" spans="1:7" ht="19" customHeight="1">
       <c r="A120" s="7">
         <v>5032</v>
       </c>
@@ -4548,13 +4888,13 @@
         <v>1493</v>
       </c>
       <c r="D120" s="6"/>
-      <c r="E120" s="36" t="s">
-        <v>279</v>
-      </c>
-      <c r="F120" s="32"/>
-      <c r="G120" s="30"/>
-    </row>
-    <row r="121" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E120" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="F120" s="12"/>
+      <c r="G120" s="12"/>
+    </row>
+    <row r="121" spans="1:7" ht="19" customHeight="1">
       <c r="A121" s="7">
         <v>5033</v>
       </c>
@@ -4565,13 +4905,13 @@
         <v>1493</v>
       </c>
       <c r="D121" s="6"/>
-      <c r="E121" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="F121" s="32"/>
-      <c r="G121" s="30"/>
-    </row>
-    <row r="122" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E121" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="F121" s="12"/>
+      <c r="G121" s="12"/>
+    </row>
+    <row r="122" spans="1:7" ht="19" customHeight="1">
       <c r="A122" s="7">
         <v>5034</v>
       </c>
@@ -4582,13 +4922,13 @@
         <v>1600</v>
       </c>
       <c r="D122" s="6"/>
-      <c r="E122" s="36" t="s">
-        <v>281</v>
-      </c>
-      <c r="F122" s="32"/>
-      <c r="G122" s="30"/>
-    </row>
-    <row r="123" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E122" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="F122" s="12"/>
+      <c r="G122" s="12"/>
+    </row>
+    <row r="123" spans="1:7" ht="19" customHeight="1">
       <c r="A123" s="7">
         <v>5035</v>
       </c>
@@ -4599,13 +4939,13 @@
         <v>1920</v>
       </c>
       <c r="D123" s="6"/>
-      <c r="E123" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="F123" s="32"/>
-      <c r="G123" s="30"/>
-    </row>
-    <row r="124" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E123" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="F123" s="12"/>
+      <c r="G123" s="12"/>
+    </row>
+    <row r="124" spans="1:7" ht="19" customHeight="1">
       <c r="A124" s="7">
         <v>5036</v>
       </c>
@@ -4616,13 +4956,13 @@
         <v>1056</v>
       </c>
       <c r="D124" s="6"/>
-      <c r="E124" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="F124" s="32"/>
-      <c r="G124" s="30"/>
-    </row>
-    <row r="125" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E124" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="F124" s="12"/>
+      <c r="G124" s="12"/>
+    </row>
+    <row r="125" spans="1:7" ht="19" customHeight="1">
       <c r="A125" s="7">
         <v>5037</v>
       </c>
@@ -4633,70 +4973,70 @@
         <v>1344</v>
       </c>
       <c r="D125" s="6"/>
-      <c r="E125" s="36" t="s">
-        <v>284</v>
-      </c>
-      <c r="F125" s="32"/>
-      <c r="G125" s="30"/>
-    </row>
-    <row r="126" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="25">
+      <c r="E125" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="F125" s="12"/>
+      <c r="G125" s="12"/>
+    </row>
+    <row r="126" spans="1:7" ht="19" customHeight="1">
+      <c r="A126" s="7">
         <v>5038</v>
       </c>
-      <c r="B126" s="17" t="s">
+      <c r="B126" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C126" s="18">
+      <c r="C126" s="3">
         <v>839</v>
       </c>
-      <c r="D126" s="18"/>
-      <c r="E126" s="49" t="s">
-        <v>285</v>
-      </c>
-      <c r="F126" s="19" t="s">
-        <v>321</v>
-      </c>
-      <c r="G126" s="52"/>
-    </row>
-    <row r="127" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="15" t="s">
+      <c r="D126" s="3"/>
+      <c r="E126" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="F126" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="G126" s="10"/>
+    </row>
+    <row r="127" spans="1:7" ht="19" customHeight="1">
+      <c r="A127" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B127" s="15" t="s">
+      <c r="B127" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C127" s="15" t="s">
+      <c r="C127" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D127" s="30"/>
-      <c r="E127" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="F127" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="G127" s="15" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="28" t="s">
+      <c r="D127" s="12"/>
+      <c r="E127" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="F127" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="G127" s="27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="19" customHeight="1">
+      <c r="A128" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B128" s="12" t="s">
+      <c r="B128" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C128" s="23">
+      <c r="C128" s="6">
         <v>2293</v>
       </c>
-      <c r="D128" s="23"/>
-      <c r="E128" s="45" t="s">
-        <v>286</v>
-      </c>
-      <c r="F128" s="31"/>
-      <c r="G128" s="30"/>
-    </row>
-    <row r="129" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D128" s="6"/>
+      <c r="E128" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="F128" s="12"/>
+      <c r="G128" s="12"/>
+    </row>
+    <row r="129" spans="1:20" ht="19" customHeight="1">
       <c r="A129" s="8" t="s">
         <v>61</v>
       </c>
@@ -4707,13 +5047,13 @@
         <v>2800</v>
       </c>
       <c r="D129" s="6"/>
-      <c r="E129" s="49" t="s">
-        <v>287</v>
-      </c>
-      <c r="F129" s="32"/>
-      <c r="G129" s="30"/>
-    </row>
-    <row r="130" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E129" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="F129" s="12"/>
+      <c r="G129" s="12"/>
+    </row>
+    <row r="130" spans="1:20" ht="19" customHeight="1">
       <c r="A130" s="8" t="s">
         <v>62</v>
       </c>
@@ -4724,15 +5064,15 @@
         <v>2240</v>
       </c>
       <c r="D130" s="6"/>
-      <c r="E130" s="36" t="s">
-        <v>288</v>
-      </c>
-      <c r="F130" s="32"/>
-      <c r="G130" s="59" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E130" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="F130" s="12"/>
+      <c r="G130" s="10" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="131" spans="1:20" ht="19" customHeight="1">
       <c r="A131" s="8" t="s">
         <v>63</v>
       </c>
@@ -4743,15 +5083,15 @@
         <v>1387</v>
       </c>
       <c r="D131" s="6"/>
-      <c r="E131" s="36" t="s">
-        <v>289</v>
-      </c>
-      <c r="F131" s="32"/>
-      <c r="G131" s="59" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E131" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="F131" s="12"/>
+      <c r="G131" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="132" spans="1:20" ht="19" customHeight="1">
       <c r="A132" s="8" t="s">
         <v>64</v>
       </c>
@@ -4762,15 +5102,15 @@
         <v>2560</v>
       </c>
       <c r="D132" s="6"/>
-      <c r="E132" s="36" t="s">
-        <v>290</v>
-      </c>
-      <c r="F132" s="32"/>
-      <c r="G132" s="59" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E132" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="F132" s="12"/>
+      <c r="G132" s="10" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20" ht="19" customHeight="1">
       <c r="A133" s="8" t="s">
         <v>65</v>
       </c>
@@ -4781,15 +5121,15 @@
         <v>1867</v>
       </c>
       <c r="D133" s="6"/>
-      <c r="E133" s="36" t="s">
-        <v>291</v>
-      </c>
-      <c r="F133" s="32"/>
-      <c r="G133" s="59" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E133" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="F133" s="12"/>
+      <c r="G133" s="10" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20" ht="19" customHeight="1">
       <c r="A134" s="8" t="s">
         <v>66</v>
       </c>
@@ -4800,13 +5140,13 @@
         <v>1280</v>
       </c>
       <c r="D134" s="6"/>
-      <c r="E134" s="36" t="s">
-        <v>292</v>
-      </c>
-      <c r="F134" s="32"/>
-      <c r="G134" s="30"/>
-    </row>
-    <row r="135" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E134" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="F134" s="12"/>
+      <c r="G134" s="12"/>
+    </row>
+    <row r="135" spans="1:20" ht="19" customHeight="1">
       <c r="A135" s="8" t="s">
         <v>67</v>
       </c>
@@ -4817,13 +5157,13 @@
         <v>1599</v>
       </c>
       <c r="D135" s="6"/>
-      <c r="E135" s="36" t="s">
-        <v>293</v>
-      </c>
-      <c r="F135" s="32"/>
-      <c r="G135" s="30"/>
-    </row>
-    <row r="136" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E135" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="F135" s="12"/>
+      <c r="G135" s="12"/>
+    </row>
+    <row r="136" spans="1:20" ht="19" customHeight="1">
       <c r="A136" s="8" t="s">
         <v>68</v>
       </c>
@@ -4834,13 +5174,13 @@
         <v>1792</v>
       </c>
       <c r="D136" s="6"/>
-      <c r="E136" s="36" t="s">
-        <v>294</v>
-      </c>
-      <c r="F136" s="32"/>
-      <c r="G136" s="30"/>
-    </row>
-    <row r="137" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E136" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="F136" s="12"/>
+      <c r="G136" s="12"/>
+    </row>
+    <row r="137" spans="1:20" ht="19" customHeight="1">
       <c r="A137" s="8" t="s">
         <v>69</v>
       </c>
@@ -4851,66 +5191,66 @@
         <v>1980</v>
       </c>
       <c r="D137" s="6"/>
-      <c r="E137" s="36" t="s">
-        <v>295</v>
-      </c>
-      <c r="F137" s="32"/>
-      <c r="G137" s="30"/>
-    </row>
-    <row r="138" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="26" t="s">
+      <c r="E137" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="F137" s="12"/>
+      <c r="G137" s="12"/>
+    </row>
+    <row r="138" spans="1:20" ht="19" customHeight="1">
+      <c r="A138" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B138" s="17" t="s">
+      <c r="B138" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C138" s="24">
+      <c r="C138" s="6">
         <v>1944</v>
       </c>
-      <c r="D138" s="24"/>
-      <c r="E138" s="49" t="s">
-        <v>296</v>
-      </c>
-      <c r="F138" s="35"/>
-      <c r="G138" s="30"/>
-    </row>
-    <row r="139" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="15" t="s">
+      <c r="D138" s="6"/>
+      <c r="E138" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="F138" s="12"/>
+      <c r="G138" s="12"/>
+    </row>
+    <row r="139" spans="1:20" ht="19" customHeight="1">
+      <c r="A139" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B139" s="15" t="s">
+      <c r="B139" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C139" s="15" t="s">
+      <c r="C139" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D139" s="30"/>
-      <c r="E139" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="F139" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="G139" s="15" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="28" t="s">
+      <c r="D139" s="12"/>
+      <c r="E139" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="F139" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="G139" s="27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20" ht="19" customHeight="1">
+      <c r="A140" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B140" s="29" t="s">
+      <c r="B140" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="C140" s="23">
+      <c r="C140" s="6">
         <v>2100</v>
       </c>
-      <c r="D140" s="23"/>
-      <c r="E140" s="50"/>
-      <c r="F140" s="31"/>
-      <c r="G140" s="30"/>
-    </row>
-    <row r="141" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D140" s="6"/>
+      <c r="E140" s="20"/>
+      <c r="F140" s="12"/>
+      <c r="G140" s="12"/>
+    </row>
+    <row r="141" spans="1:20" ht="19" customHeight="1">
       <c r="A141" s="8" t="s">
         <v>63</v>
       </c>
@@ -4921,11 +5261,11 @@
         <v>1560</v>
       </c>
       <c r="D141" s="6"/>
-      <c r="E141" s="46"/>
-      <c r="F141" s="32"/>
-      <c r="G141" s="30"/>
-    </row>
-    <row r="142" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E141" s="20"/>
+      <c r="F141" s="12"/>
+      <c r="G141" s="12"/>
+    </row>
+    <row r="142" spans="1:20" ht="19" customHeight="1" thickBot="1">
       <c r="A142" s="8" t="s">
         <v>67</v>
       </c>
@@ -4936,62 +5276,110 @@
         <v>1800</v>
       </c>
       <c r="D142" s="6"/>
-      <c r="E142" s="46"/>
-      <c r="F142" s="32"/>
-      <c r="G142" s="30"/>
-    </row>
-    <row r="143" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="65" t="s">
+      <c r="E142" s="20"/>
+      <c r="F142" s="12"/>
+      <c r="G142" s="12"/>
+    </row>
+    <row r="143" spans="1:20" ht="19" customHeight="1">
+      <c r="A143" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="B143" s="65"/>
-      <c r="C143" s="65"/>
-      <c r="D143" s="65"/>
-      <c r="E143" s="65"/>
-      <c r="F143" s="65"/>
-      <c r="G143" s="56"/>
-    </row>
-    <row r="144" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="15" t="s">
+      <c r="B143" s="32"/>
+      <c r="C143" s="32"/>
+      <c r="D143" s="32"/>
+      <c r="E143" s="32"/>
+      <c r="F143" s="32"/>
+      <c r="G143" s="33"/>
+      <c r="L143" s="47" t="s">
+        <v>390</v>
+      </c>
+      <c r="M143" s="47"/>
+      <c r="O143" s="54" t="s">
+        <v>391</v>
+      </c>
+      <c r="P143" s="55"/>
+      <c r="Q143" s="55"/>
+      <c r="R143" s="55"/>
+      <c r="S143" s="55"/>
+      <c r="T143" s="56"/>
+    </row>
+    <row r="144" spans="1:20" ht="19" customHeight="1">
+      <c r="A144" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B144" s="15" t="s">
+      <c r="B144" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C144" s="15" t="s">
+      <c r="C144" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D144" s="30"/>
-      <c r="E144" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="F144" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="G144" s="15" t="s">
+      <c r="D144" s="12"/>
+      <c r="E144" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="F144" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="G144" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="L144" s="36"/>
+      <c r="M144" s="37"/>
+      <c r="O144" s="46" t="s">
+        <v>392</v>
+      </c>
+      <c r="P144" s="41"/>
+      <c r="Q144" s="41"/>
+      <c r="R144" s="41"/>
+      <c r="S144" s="41"/>
+      <c r="T144" s="37"/>
+    </row>
+    <row r="145" spans="1:20" ht="62" customHeight="1">
+      <c r="A145" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C145" s="3">
+        <v>533</v>
+      </c>
+      <c r="D145" s="3"/>
+      <c r="E145" s="15" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B145" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C145" s="13">
-        <v>533</v>
-      </c>
-      <c r="D145" s="13"/>
-      <c r="E145" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F145" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="G145" s="57"/>
-    </row>
-    <row r="146" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F145" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G145" s="3"/>
+      <c r="L145" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M145" s="37" t="str">
+        <f>L145&amp;A145&amp;".pdf"</f>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Imagine.pdf</v>
+      </c>
+      <c r="O145" s="42" t="s">
+        <v>393</v>
+      </c>
+      <c r="P145" s="49" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q145" s="50" t="s">
+        <v>356</v>
+      </c>
+      <c r="R145" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="S145" s="41"/>
+      <c r="T145" s="48" t="str">
+        <f>P145&amp;E145&amp;Q145&amp;F145&amp;R145</f>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Imagine.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/1eeef250340a418d9cbdd09dc39f9fe4" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="146" spans="1:20" ht="19" customHeight="1">
       <c r="A146" s="2" t="s">
         <v>122</v>
       </c>
@@ -5002,13 +5390,39 @@
         <v>640</v>
       </c>
       <c r="D146" s="3"/>
-      <c r="E146" s="49" t="s">
-        <v>330</v>
-      </c>
-      <c r="F146" s="38"/>
-      <c r="G146" s="57"/>
-    </row>
-    <row r="147" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E146" t="s">
+        <v>323</v>
+      </c>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
+      <c r="L146" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M146" s="37" t="str">
+        <f t="shared" ref="M146:M174" si="1">L146&amp;A146&amp;".pdf"</f>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Satisfaction.pdf</v>
+      </c>
+      <c r="O146" s="36" t="s">
+        <v>394</v>
+      </c>
+      <c r="P146" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q146" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R146" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S146" s="41"/>
+      <c r="T146" s="48" t="str">
+        <f t="shared" ref="T146:T174" si="2">P146&amp;E146&amp;Q146&amp;F146&amp;R146</f>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Satisfaction.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20" ht="19" customHeight="1">
       <c r="A147" s="2" t="s">
         <v>123</v>
       </c>
@@ -5019,15 +5433,41 @@
         <v>800</v>
       </c>
       <c r="D147" s="3"/>
-      <c r="E147" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F147" s="38" t="s">
-        <v>305</v>
-      </c>
-      <c r="G147" s="57"/>
-    </row>
-    <row r="148" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E147" t="s">
+        <v>359</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G147" s="3"/>
+      <c r="L147" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M147" s="37" t="str">
+        <f>L147&amp;A147&amp;".pdf"</f>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Respect.pdf</v>
+      </c>
+      <c r="O147" s="36" t="s">
+        <v>395</v>
+      </c>
+      <c r="P147" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q147" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R147" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S147" s="41"/>
+      <c r="T147" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Respect.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/051f4e3081b841b99f6416795279f117" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="148" spans="1:20" ht="19" customHeight="1">
       <c r="A148" s="2" t="s">
         <v>124</v>
       </c>
@@ -5038,15 +5478,41 @@
         <v>880</v>
       </c>
       <c r="D148" s="3"/>
-      <c r="E148" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F148" s="38" t="s">
-        <v>300</v>
-      </c>
-      <c r="G148" s="57"/>
-    </row>
-    <row r="149" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E148" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="G148" s="3"/>
+      <c r="L148" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M148" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Good Vibrations.pdf</v>
+      </c>
+      <c r="O148" s="36" t="s">
+        <v>396</v>
+      </c>
+      <c r="P148" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q148" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R148" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S148" s="41"/>
+      <c r="T148" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Good_Vibrations.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/37f9938dcde54573805b2a7d92f0a1a8" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="149" spans="1:20" ht="19" customHeight="1">
       <c r="A149" s="2" t="s">
         <v>126</v>
       </c>
@@ -5057,15 +5523,41 @@
         <v>660</v>
       </c>
       <c r="D149" s="3"/>
-      <c r="E149" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F149" s="38" t="s">
-        <v>319</v>
-      </c>
-      <c r="G149" s="57"/>
-    </row>
-    <row r="150" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E149" t="s">
+        <v>360</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G149" s="3"/>
+      <c r="L149" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M149" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Yesterday.pdf</v>
+      </c>
+      <c r="O149" s="36" t="s">
+        <v>397</v>
+      </c>
+      <c r="P149" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q149" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R149" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S149" s="41"/>
+      <c r="T149" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Yesterday.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/42205040200945fbb5aa4c064ae81611" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="150" spans="1:20" ht="19" customHeight="1">
       <c r="A150" s="2" t="s">
         <v>128</v>
       </c>
@@ -5076,13 +5568,39 @@
         <v>780</v>
       </c>
       <c r="D150" s="3"/>
-      <c r="E150" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F150" s="38"/>
-      <c r="G150" s="57"/>
-    </row>
-    <row r="151" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E150" t="s">
+        <v>361</v>
+      </c>
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
+      <c r="L150" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M150" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Layla.pdf</v>
+      </c>
+      <c r="O150" s="36" t="s">
+        <v>398</v>
+      </c>
+      <c r="P150" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q150" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R150" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S150" s="41"/>
+      <c r="T150" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Layla.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="151" spans="1:20" ht="19" customHeight="1">
       <c r="A151" s="2" t="s">
         <v>130</v>
       </c>
@@ -5093,55 +5611,133 @@
         <v>840</v>
       </c>
       <c r="D151" s="3"/>
-      <c r="E151" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F151" s="38" t="s">
-        <v>317</v>
-      </c>
-      <c r="G151" s="57"/>
-    </row>
-    <row r="152" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E151" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G151" s="3"/>
+      <c r="L151" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M151" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Still The One.pdf</v>
+      </c>
+      <c r="O151" s="36" t="s">
+        <v>399</v>
+      </c>
+      <c r="P151" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q151" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R151" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S151" s="41"/>
+      <c r="T151" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Still_The_One.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/7717e6eb85734832869d6f9b6052ebba" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="152" spans="1:20" ht="19" customHeight="1">
       <c r="A152" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="C152" s="3">
         <v>900</v>
       </c>
       <c r="D152" s="3"/>
-      <c r="E152" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F152" s="38" t="s">
-        <v>312</v>
-      </c>
-      <c r="G152" s="57"/>
-    </row>
-    <row r="153" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E152" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G152" s="3"/>
+      <c r="L152" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M152" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Born To Run.pdf</v>
+      </c>
+      <c r="O152" s="36" t="s">
+        <v>400</v>
+      </c>
+      <c r="P152" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q152" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R152" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S152" s="41"/>
+      <c r="T152" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Born_To_Run.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/78461eacbe8f493587113fd7158e7e45" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="153" spans="1:20" ht="19" customHeight="1">
       <c r="A153" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="C153" s="3">
         <v>990</v>
       </c>
       <c r="D153" s="3"/>
-      <c r="E153" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F153" s="38" t="s">
-        <v>306</v>
-      </c>
-      <c r="G153" s="57"/>
-    </row>
-    <row r="154" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E153" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G153" s="3"/>
+      <c r="L153" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M153" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Rhythm Nation.pdf</v>
+      </c>
+      <c r="O153" s="36" t="s">
+        <v>401</v>
+      </c>
+      <c r="P153" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q153" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R153" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S153" s="41"/>
+      <c r="T153" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Rhythm_Nation.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/e6656cfc4f184010a758bf06dc03d44c" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20" ht="19" customHeight="1">
       <c r="A154" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>89</v>
@@ -5150,36 +5746,88 @@
         <v>1080</v>
       </c>
       <c r="D154" s="3"/>
-      <c r="E154" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F154" s="39" t="s">
-        <v>320</v>
-      </c>
-      <c r="G154" s="58"/>
-    </row>
-    <row r="155" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E154" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="F154" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="G154" s="34"/>
+      <c r="L154" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M154" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Move On Up.pdf</v>
+      </c>
+      <c r="O154" s="36" t="s">
+        <v>402</v>
+      </c>
+      <c r="P154" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q154" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R154" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S154" s="41"/>
+      <c r="T154" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Move_On_Up.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/8cedcb708e2b4188b2913be4a3e755de" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="155" spans="1:20" ht="19" customHeight="1">
       <c r="A155" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B155" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="C155" s="3">
         <v>1140</v>
       </c>
       <c r="D155" s="3"/>
-      <c r="E155" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F155" s="38" t="s">
-        <v>307</v>
-      </c>
-      <c r="G155" s="57"/>
-    </row>
-    <row r="156" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E155" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G155" s="3"/>
+      <c r="L155" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M155" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Sweet Coroline.pdf</v>
+      </c>
+      <c r="O155" s="36" t="s">
+        <v>403</v>
+      </c>
+      <c r="P155" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q155" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R155" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S155" s="41"/>
+      <c r="T155" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Sweet_Coroline.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/479f8bedba354a3cbcd38f750d2b5ee1" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="156" spans="1:20" ht="19" customHeight="1">
       <c r="A156" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>97</v>
@@ -5188,72 +5836,176 @@
         <v>1056</v>
       </c>
       <c r="D156" s="3"/>
-      <c r="E156" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F156" s="38" t="s">
-        <v>308</v>
-      </c>
-      <c r="G156" s="57"/>
-    </row>
-    <row r="157" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E156" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G156" s="3"/>
+      <c r="L156" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M156" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Rising Sun.pdf</v>
+      </c>
+      <c r="O156" s="36" t="s">
+        <v>404</v>
+      </c>
+      <c r="P156" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q156" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R156" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S156" s="41"/>
+      <c r="T156" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Rising_Sun.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/947aaf514af34f30a3b1b74ad6d53f86" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="157" spans="1:20" ht="19" customHeight="1">
       <c r="A157" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B157" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="C157" s="3">
         <v>1152</v>
       </c>
       <c r="D157" s="3"/>
-      <c r="E157" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F157" s="38" t="s">
-        <v>318</v>
-      </c>
-      <c r="G157" s="57"/>
-    </row>
-    <row r="158" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E157" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="G157" s="3"/>
+      <c r="L157" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M157" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Here Comes the Sun.pdf</v>
+      </c>
+      <c r="O157" s="36" t="s">
+        <v>405</v>
+      </c>
+      <c r="P157" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q157" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R157" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S157" s="41"/>
+      <c r="T157" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Here_Comes_The_Sun.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/401387cf236a4cb29231fb05c16da963" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="158" spans="1:20" ht="19" customHeight="1">
       <c r="A158" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="C158" s="3">
         <v>1248</v>
       </c>
       <c r="D158" s="3"/>
-      <c r="E158" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F158" s="38" t="s">
-        <v>309</v>
-      </c>
-      <c r="G158" s="57"/>
-    </row>
-    <row r="159" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E158" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G158" s="3"/>
+      <c r="L158" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M158" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Three Little Birds.pdf</v>
+      </c>
+      <c r="O158" s="36" t="s">
+        <v>406</v>
+      </c>
+      <c r="P158" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q158" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R158" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S158" s="41"/>
+      <c r="T158" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Three_Little_Birds.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/38b5f1e44d5f4ef991878af7089a65da" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="159" spans="1:20" ht="19" customHeight="1">
       <c r="A159" s="2" t="s">
-        <v>143</v>
+        <v>376</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C159" s="3">
         <v>1176</v>
       </c>
       <c r="D159" s="3"/>
-      <c r="E159" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F159" s="38"/>
-      <c r="G159" s="57"/>
-    </row>
-    <row r="160" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E159" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="F159" s="3"/>
+      <c r="G159" s="3"/>
+      <c r="L159" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M159" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Stand By Me (Porch).pdf</v>
+      </c>
+      <c r="O159" s="36" t="s">
+        <v>407</v>
+      </c>
+      <c r="P159" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q159" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R159" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S159" s="41"/>
+      <c r="T159" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Stand_By_Me.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="160" spans="1:20" ht="19" customHeight="1">
       <c r="A160" s="2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>98</v>
@@ -5262,53 +6014,131 @@
         <v>1344</v>
       </c>
       <c r="D160" s="3"/>
-      <c r="E160" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F160" s="38" t="s">
-        <v>316</v>
-      </c>
-      <c r="G160" s="57"/>
-    </row>
-    <row r="161" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E160" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G160" s="3"/>
+      <c r="L160" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M160" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/My Girl.pdf</v>
+      </c>
+      <c r="O160" s="36" t="s">
+        <v>408</v>
+      </c>
+      <c r="P160" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q160" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R160" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S160" s="41"/>
+      <c r="T160" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/My_Girl.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/b7986d5c12bb435d87caee93a693c170" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="161" spans="1:20" ht="19" customHeight="1">
       <c r="A161" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C161" s="3">
         <v>1272</v>
       </c>
       <c r="D161" s="3"/>
-      <c r="E161" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F161" s="59" t="s">
-        <v>299</v>
-      </c>
-      <c r="G161" s="30"/>
-    </row>
-    <row r="162" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E161" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="F161" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="G161" s="12"/>
+      <c r="L161" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M161" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Whole Lotta Love (Porch).pdf</v>
+      </c>
+      <c r="O161" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="P161" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q161" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R161" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S161" s="41"/>
+      <c r="T161" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Whole_Lotta_Love.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/8ff1bfaf8f1b44b196157f476b9d15e6" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="162" spans="1:20" ht="19" customHeight="1">
       <c r="A162" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C162" s="3">
         <v>1067</v>
       </c>
       <c r="D162" s="3"/>
-      <c r="E162" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F162" s="38"/>
-      <c r="G162" s="57"/>
-    </row>
-    <row r="163" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E162" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="F162" s="3"/>
+      <c r="G162" s="3"/>
+      <c r="L162" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M162" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Sweet Dreams.pdf</v>
+      </c>
+      <c r="O162" s="36" t="s">
+        <v>410</v>
+      </c>
+      <c r="P162" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q162" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R162" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S162" s="41"/>
+      <c r="T162" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Sweet_Dreams.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="163" spans="1:20" ht="19" customHeight="1">
       <c r="A163" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>90</v>
@@ -5317,17 +6147,43 @@
         <v>1173</v>
       </c>
       <c r="D163" s="3"/>
-      <c r="E163" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F163" s="39" t="s">
-        <v>301</v>
-      </c>
-      <c r="G163" s="58"/>
-    </row>
-    <row r="164" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E163" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="F163" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="G163" s="34"/>
+      <c r="L163" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M163" s="37" t="str">
+        <f>L163&amp;A163&amp;".pdf"</f>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Beautiful Morning.pdf</v>
+      </c>
+      <c r="O163" s="36" t="s">
+        <v>411</v>
+      </c>
+      <c r="P163" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q163" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R163" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S163" s="41"/>
+      <c r="T163" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Beautiful_Morning.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/9641df1bdecf4eb8b682635658efbe5b" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="164" spans="1:20" ht="19" customHeight="1">
       <c r="A164" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>91</v>
@@ -5336,36 +6192,88 @@
         <v>1280</v>
       </c>
       <c r="D164" s="3"/>
-      <c r="E164" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F164" s="39" t="s">
-        <v>302</v>
-      </c>
-      <c r="G164" s="58"/>
-    </row>
-    <row r="165" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E164" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="F164" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="G164" s="34"/>
+      <c r="L164" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M164" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Under Pressure.pdf</v>
+      </c>
+      <c r="O164" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="P164" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q164" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R164" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S164" s="41"/>
+      <c r="T164" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Under_Pressure.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/4b4d091ffa6e4822a8e1166cf12be1af" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="165" spans="1:20" ht="19" customHeight="1">
       <c r="A165" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C165" s="3">
         <v>1306</v>
       </c>
       <c r="D165" s="3"/>
-      <c r="E165" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F165" s="38" t="s">
-        <v>311</v>
-      </c>
-      <c r="G165" s="57"/>
-    </row>
-    <row r="166" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E165" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G165" s="3"/>
+      <c r="L165" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M165" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Johnny B Goode (Porch).pdf</v>
+      </c>
+      <c r="O165" s="36" t="s">
+        <v>413</v>
+      </c>
+      <c r="P165" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q165" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R165" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S165" s="41"/>
+      <c r="T165" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Johnny_B_Goode.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/4b0b4b7c1aa54dff9cf60b1e21bc192a" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="166" spans="1:20" ht="19" customHeight="1">
       <c r="A166" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>114</v>
@@ -5374,15 +6282,41 @@
         <v>1387</v>
       </c>
       <c r="D166" s="3"/>
-      <c r="E166" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F166" s="38"/>
-      <c r="G166" s="57"/>
-    </row>
-    <row r="167" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E166" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="F166" s="3"/>
+      <c r="G166" s="3"/>
+      <c r="L166" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M166" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Free Bird.pdf</v>
+      </c>
+      <c r="O166" s="36" t="s">
+        <v>414</v>
+      </c>
+      <c r="P166" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q166" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R166" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S166" s="41"/>
+      <c r="T166" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Free_Bird.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="167" spans="1:20" ht="19" customHeight="1">
       <c r="A167" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>92</v>
@@ -5391,74 +6325,178 @@
         <v>1493</v>
       </c>
       <c r="D167" s="3"/>
-      <c r="E167" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F167" s="38" t="s">
-        <v>304</v>
-      </c>
-      <c r="G167" s="57"/>
-    </row>
-    <row r="168" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E167" t="s">
+        <v>362</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G167" s="3"/>
+      <c r="L167" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M167" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Shout.pdf</v>
+      </c>
+      <c r="O167" s="36" t="s">
+        <v>415</v>
+      </c>
+      <c r="P167" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q167" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R167" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S167" s="41"/>
+      <c r="T167" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Shout.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/c2f4608676e24913942d72cd08374f85" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="168" spans="1:20" ht="19" customHeight="1">
       <c r="A168" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C168" s="3">
         <v>1414</v>
       </c>
       <c r="D168" s="3"/>
-      <c r="E168" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F168" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="G168" s="57"/>
-    </row>
-    <row r="169" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E168" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G168" s="3"/>
+      <c r="L168" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M168" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Staying Alive (Porch).pdf</v>
+      </c>
+      <c r="O168" s="36" t="s">
+        <v>416</v>
+      </c>
+      <c r="P168" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q168" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R168" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S168" s="41"/>
+      <c r="T168" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Staying_Alive.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/6f069a2a8e794fe7b2b912468c0e5efd" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="169" spans="1:20" ht="19" customHeight="1">
       <c r="A169" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C169" s="3">
         <v>1600</v>
       </c>
       <c r="D169" s="3"/>
-      <c r="E169" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F169" s="39" t="s">
-        <v>313</v>
-      </c>
-      <c r="G169" s="58"/>
-    </row>
-    <row r="170" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E169" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="F169" s="34" t="s">
+        <v>306</v>
+      </c>
+      <c r="G169" s="34"/>
+      <c r="L169" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M169" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Brown Eyed Girl.pdf</v>
+      </c>
+      <c r="O169" s="36" t="s">
+        <v>417</v>
+      </c>
+      <c r="P169" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q169" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R169" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S169" s="41"/>
+      <c r="T169" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Brown_Eyed_Girl.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/095791f5a6084c54ac115b04d6becdb7" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="170" spans="1:20" ht="19" customHeight="1">
       <c r="A170" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C170" s="3">
         <v>1760</v>
       </c>
       <c r="D170" s="3"/>
-      <c r="E170" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F170" s="39" t="s">
-        <v>303</v>
-      </c>
-      <c r="G170" s="58"/>
-    </row>
-    <row r="171" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E170" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="F170" s="34" t="s">
+        <v>296</v>
+      </c>
+      <c r="G170" s="34"/>
+      <c r="L170" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M170" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Rocket Man.pdf</v>
+      </c>
+      <c r="O170" s="36" t="s">
+        <v>418</v>
+      </c>
+      <c r="P170" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q170" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R170" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S170" s="41"/>
+      <c r="T170" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Rocket_Man.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/7adf3930fcb64740986c55e34aa3d850" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="171" spans="1:20" ht="19" customHeight="1">
       <c r="A171" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>109</v>
@@ -5467,171 +6505,301 @@
         <v>1920</v>
       </c>
       <c r="D171" s="3"/>
-      <c r="E171" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F171" s="38" t="s">
-        <v>310</v>
-      </c>
-      <c r="G171" s="57"/>
-    </row>
-    <row r="172" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E171" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G171" s="3"/>
+      <c r="L171" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M171" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Hey Jude.pdf</v>
+      </c>
+      <c r="O171" s="36" t="s">
+        <v>419</v>
+      </c>
+      <c r="P171" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q171" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R171" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S171" s="41"/>
+      <c r="T171" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Hey_Jude.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/fa694db04a254e98b483023c8b1a7517" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="172" spans="1:20" ht="19" customHeight="1">
       <c r="A172" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C172" s="3">
         <v>2052</v>
       </c>
       <c r="D172" s="3"/>
-      <c r="E172" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F172" s="38"/>
-      <c r="G172" s="57"/>
-    </row>
-    <row r="173" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E172" t="s">
+        <v>363</v>
+      </c>
+      <c r="F172" s="3"/>
+      <c r="G172" s="3"/>
+      <c r="L172" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M172" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Superfly.pdf</v>
+      </c>
+      <c r="O172" s="36" t="s">
+        <v>420</v>
+      </c>
+      <c r="P172" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q172" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R172" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S172" s="41"/>
+      <c r="T172" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Superfly.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="173" spans="1:20" ht="19" customHeight="1">
       <c r="A173" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C173" s="3">
         <v>1680</v>
       </c>
       <c r="D173" s="3"/>
-      <c r="E173" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F173" s="38" t="s">
-        <v>298</v>
-      </c>
-      <c r="G173" s="57"/>
-    </row>
-    <row r="174" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E173" t="s">
+        <v>364</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G173" s="3"/>
+      <c r="L173" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="M173" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Limelight.pdf</v>
+      </c>
+      <c r="O173" s="36" t="s">
+        <v>421</v>
+      </c>
+      <c r="P173" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q173" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="R173" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="S173" s="41"/>
+      <c r="T173" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Limelight.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="https://momento360.com/e/uc/52c10d9e02824495a80923576db9ef72" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="174" spans="1:20" ht="19" customHeight="1" thickBot="1">
       <c r="A174" s="2" t="s">
-        <v>166</v>
+        <v>367</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C174" s="3">
         <v>1493</v>
       </c>
       <c r="D174" s="3"/>
-      <c r="E174" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F174" s="38"/>
-      <c r="G174" s="57"/>
+      <c r="E174" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="F174" s="3"/>
+      <c r="G174" s="3"/>
+      <c r="L174" s="39" t="s">
+        <v>358</v>
+      </c>
+      <c r="M174" s="40" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Lean On Me.pdf</v>
+      </c>
+      <c r="O174" s="44" t="s">
+        <v>422</v>
+      </c>
+      <c r="P174" s="57" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q174" s="58" t="s">
+        <v>356</v>
+      </c>
+      <c r="R174" s="59" t="s">
+        <v>357</v>
+      </c>
+      <c r="S174" s="45"/>
+      <c r="T174" s="48" t="str">
+        <f t="shared" si="2"/>
+        <v>&lt;p&gt;&lt;u&gt;&lt;a href="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Lean_On_Me.pdf" target="_blank"&gt;Click Here to Download PDF&lt;/a&gt;&lt;/u&gt;&lt;/p&gt; 
+&lt;p&gt;&amp;nbsp;&lt;/p&gt; 
+&lt;p&gt;&lt;a href="" target="_blank"&gt;&lt;u&gt;Click Here for Virtual Tour&lt;/u&gt;&lt;/a&gt;&lt;/p&gt;</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A143:F143"/>
+    <mergeCell ref="L143:M143"/>
+    <mergeCell ref="O143:T143"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E5" r:id="rId1" xr:uid="{7B873302-3E72-4D96-98DA-7B2E6C8A4D72}"/>
-    <hyperlink ref="E7" r:id="rId2" xr:uid="{460A174F-CBAE-4A44-B68C-AA5BDAEC54C4}"/>
-    <hyperlink ref="E8" r:id="rId3" xr:uid="{88D8986D-4208-4DB4-AA3C-408B291B290B}"/>
-    <hyperlink ref="E9" r:id="rId4" xr:uid="{9E9211E8-7EE6-4BC2-85F6-9F9F686372C4}"/>
-    <hyperlink ref="E10" r:id="rId5" xr:uid="{7243CEC3-5A0A-4E29-8F03-33B735B095F3}"/>
-    <hyperlink ref="E11" r:id="rId6" xr:uid="{C8B16079-03B8-4030-BA75-4B605BBB3BEE}"/>
-    <hyperlink ref="E12" r:id="rId7" xr:uid="{86D4C588-9329-41E2-958C-9F86500C4A79}"/>
-    <hyperlink ref="E13" r:id="rId8" xr:uid="{23C8F005-44A1-420D-B7C6-86B021444B29}"/>
-    <hyperlink ref="E14" r:id="rId9" xr:uid="{1841704F-BE6D-4C58-B9E2-B54A85752386}"/>
-    <hyperlink ref="E15" r:id="rId10" xr:uid="{71608296-C556-4006-B2F3-7CF82D2BEACA}"/>
-    <hyperlink ref="E16" r:id="rId11" xr:uid="{E7EEBF75-18B9-49D2-AC96-05D7F550B9FC}"/>
-    <hyperlink ref="E17" r:id="rId12" xr:uid="{D9B85AC2-E7B0-4F2C-B945-9EAF72932786}"/>
-    <hyperlink ref="E18" r:id="rId13" xr:uid="{4087435B-3AE6-4D52-A4AF-03F841504CE8}"/>
-    <hyperlink ref="E19" r:id="rId14" xr:uid="{CBB29244-D43D-4912-9F30-6A820F1CE395}"/>
-    <hyperlink ref="E20" r:id="rId15" xr:uid="{6371347D-6DF7-4829-8229-7C58298FC7D7}"/>
-    <hyperlink ref="E21" r:id="rId16" xr:uid="{FB7B490E-9A47-49F6-8BDE-C4333CC95D08}"/>
-    <hyperlink ref="E22" r:id="rId17" xr:uid="{5CE486C6-BA97-44DE-BCA6-041B9E2E4570}"/>
-    <hyperlink ref="E23" r:id="rId18" xr:uid="{F84AD7C5-69E7-445A-978F-F4E74281D42C}"/>
-    <hyperlink ref="E24" r:id="rId19" xr:uid="{FBE6104B-0B43-4B12-9E73-B6AC2916FF59}"/>
-    <hyperlink ref="E25" r:id="rId20" xr:uid="{5BC31F52-D087-47A1-890B-0436F6C8AF27}"/>
-    <hyperlink ref="E26" r:id="rId21" xr:uid="{73427174-3CED-48A5-8BAC-176635B3D233}"/>
-    <hyperlink ref="E27" r:id="rId22" xr:uid="{29AB34CD-9C32-4850-83F7-1A27A00FE2C8}"/>
-    <hyperlink ref="E28" r:id="rId23" xr:uid="{CF9097BD-0702-4A2C-8DE7-B70C4B349FB2}"/>
-    <hyperlink ref="E29" r:id="rId24" xr:uid="{CE543A6D-54FB-46F3-966C-F5221D8C2203}"/>
-    <hyperlink ref="E30" r:id="rId25" xr:uid="{BA602D91-48ED-404C-B2D3-50A8C384D59A}"/>
-    <hyperlink ref="E31" r:id="rId26" xr:uid="{0776C1CD-A75E-4C60-807F-F260F902A273}"/>
-    <hyperlink ref="E32" r:id="rId27" xr:uid="{AABDE33C-27EF-4E2D-B583-E3099BD432A4}"/>
-    <hyperlink ref="E33" r:id="rId28" xr:uid="{682DFD0B-E187-4D3A-8F81-5A231E6CFB70}"/>
-    <hyperlink ref="E34" r:id="rId29" xr:uid="{92A05B9B-F230-4E14-8CD9-5BAA2E071782}"/>
-    <hyperlink ref="E35" r:id="rId30" xr:uid="{5C6C7112-FA8E-424E-8C6D-6CC3E20BBD7C}"/>
-    <hyperlink ref="E36" r:id="rId31" xr:uid="{EAF6C162-43AB-4D1A-B7F2-A67071E53C5C}"/>
-    <hyperlink ref="E37" r:id="rId32" xr:uid="{67BD4B36-5169-4C14-935D-89E596B0B0D6}"/>
-    <hyperlink ref="E38" r:id="rId33" xr:uid="{5F9AF9A7-15DE-4927-9431-E59E7226C95C}"/>
-    <hyperlink ref="E39" r:id="rId34" xr:uid="{24951338-93CE-49FB-8287-7FCBEE8CAFA1}"/>
-    <hyperlink ref="E41" r:id="rId35" xr:uid="{952B6FDE-C7AD-4493-B8DA-35B7F8DEB981}"/>
-    <hyperlink ref="F10" r:id="rId36" xr:uid="{50B60948-F77B-4953-B029-D3AC81770E9D}"/>
-    <hyperlink ref="F24" r:id="rId37" xr:uid="{B92A8409-4E93-43A8-9FB9-48BB25DFB3F9}"/>
-    <hyperlink ref="F27" r:id="rId38" xr:uid="{DD4C656C-BB6C-489D-A875-4E0F32DA286E}"/>
-    <hyperlink ref="F30" r:id="rId39" xr:uid="{CF4B1736-FA73-4E0F-A4B0-8F03043104F6}"/>
-    <hyperlink ref="F36" r:id="rId40" xr:uid="{428AD378-0DCC-4D86-880C-2B400D312B34}"/>
-    <hyperlink ref="F43" r:id="rId41" xr:uid="{8CB8E30B-6D23-4FF2-9C71-E5E4CF9ECEEA}"/>
-    <hyperlink ref="F50" r:id="rId42" xr:uid="{5F2403DE-63F2-4418-9AE9-6F0E3478366F}"/>
-    <hyperlink ref="E72" r:id="rId43" xr:uid="{C91572DC-2EDB-4786-B760-FD7E25D2971E}"/>
-    <hyperlink ref="E66" r:id="rId44" xr:uid="{0F7C9799-DF00-43B1-9FD5-5ABEE8361557}"/>
-    <hyperlink ref="E108" r:id="rId45" xr:uid="{230024D0-CB1E-4A2E-8579-A51DD6156739}"/>
-    <hyperlink ref="E126" r:id="rId46" xr:uid="{18732992-8388-4869-9638-236923812CB6}"/>
-    <hyperlink ref="E129" r:id="rId47" xr:uid="{61D67154-64CD-4E7D-A1D6-F595036679CC}"/>
-    <hyperlink ref="F163" r:id="rId48" xr:uid="{2F224CE7-4FD5-489A-9227-F0C003B85261}"/>
-    <hyperlink ref="F164" r:id="rId49" xr:uid="{28F66E20-CF60-4BCF-BB90-8D19B362F1CA}"/>
-    <hyperlink ref="F170" r:id="rId50" xr:uid="{0778CE07-A13C-48EE-B9A3-B4EC6DA47FF3}"/>
-    <hyperlink ref="F169" r:id="rId51" xr:uid="{04B5C6AB-CF34-4F2D-B02F-CFFDD831421E}"/>
-    <hyperlink ref="F154" r:id="rId52" xr:uid="{0EC453EC-9A44-446B-98B6-F76BEF646FA6}"/>
-    <hyperlink ref="F126" r:id="rId53" xr:uid="{D6E45949-0D52-4771-ACF3-D13E9F2E6B25}"/>
-    <hyperlink ref="E123" r:id="rId54" xr:uid="{6F52B6CC-D50B-458C-AD3E-D9AC25A941AA}"/>
-    <hyperlink ref="E124" r:id="rId55" xr:uid="{B81B82D2-BB04-43D5-BD74-59ACAA4F0778}"/>
-    <hyperlink ref="E125" r:id="rId56" xr:uid="{95A629AD-67BD-4AC4-8196-1863CCC24475}"/>
-    <hyperlink ref="E109" r:id="rId57" xr:uid="{1B47E129-3E4A-4CC6-9F27-1466353588BC}"/>
-    <hyperlink ref="E110" r:id="rId58" xr:uid="{4FD4CD76-B867-4AF2-927A-0E8C2D2032E8}"/>
-    <hyperlink ref="E111" r:id="rId59" xr:uid="{9F36D981-3652-46FE-A715-428DEFF257EA}"/>
-    <hyperlink ref="E112" r:id="rId60" xr:uid="{18A3E522-1FDF-42F4-B4E6-942FF7CD60FB}"/>
-    <hyperlink ref="E113" r:id="rId61" xr:uid="{7A06205F-74AF-45B9-B532-08F4E9F5B03F}"/>
-    <hyperlink ref="E114" r:id="rId62" xr:uid="{D9C4CB61-1E3C-4CF9-9BBE-B24DC995D996}"/>
-    <hyperlink ref="E115" r:id="rId63" xr:uid="{BFFE9820-15C4-458A-8A2F-C4A333336B97}"/>
-    <hyperlink ref="E116" r:id="rId64" xr:uid="{8D713FF4-76B1-4863-B785-37990D6B4A6C}"/>
-    <hyperlink ref="E117" r:id="rId65" xr:uid="{3747C92A-960C-4794-97F0-9B5B911C9BDF}"/>
-    <hyperlink ref="E118" r:id="rId66" xr:uid="{68012D0E-2C31-486A-A802-3E497CAEC7F5}"/>
-    <hyperlink ref="E119" r:id="rId67" xr:uid="{F084E286-0835-4876-8C34-0EC92DA4B0E6}"/>
-    <hyperlink ref="E120" r:id="rId68" xr:uid="{B81015F1-B16B-4CA1-87B3-950A9163F096}"/>
-    <hyperlink ref="E121" r:id="rId69" xr:uid="{A57E3390-66FA-4E24-93B0-5D3D3858231E}"/>
-    <hyperlink ref="E122" r:id="rId70" xr:uid="{B24BF8ED-1FB1-4E67-8DA9-FDEC158DFE06}"/>
-    <hyperlink ref="E128" r:id="rId71" xr:uid="{8CE013AA-8243-4E22-98A7-A63E2969F1D6}"/>
-    <hyperlink ref="E130" r:id="rId72" xr:uid="{25068463-871B-497D-94F1-8D101E31C03B}"/>
-    <hyperlink ref="E131" r:id="rId73" xr:uid="{8E939E20-8365-4082-A0C6-E21EDC90EE19}"/>
-    <hyperlink ref="E132" r:id="rId74" xr:uid="{496192E8-B7C8-4049-BBF1-F5A87F3ADE27}"/>
-    <hyperlink ref="E133" r:id="rId75" xr:uid="{36D3CDA5-E45C-4936-AA39-2D3BD750B7A6}"/>
-    <hyperlink ref="E134" r:id="rId76" xr:uid="{2FF293E4-AD4B-40AE-B71B-18FEEA326F9C}"/>
-    <hyperlink ref="E135" r:id="rId77" xr:uid="{05292FD0-3F61-4937-AF0C-E47EF43985D5}"/>
-    <hyperlink ref="E136" r:id="rId78" xr:uid="{4DB7870E-3BE3-4347-8DFB-884BD5774BE7}"/>
-    <hyperlink ref="E137" r:id="rId79" xr:uid="{788E3604-E9A3-4B0B-99C6-9E267438251D}"/>
-    <hyperlink ref="E138" r:id="rId80" xr:uid="{6FDC3EBB-1370-4D67-8457-5374A766616A}"/>
-    <hyperlink ref="F5" r:id="rId81" xr:uid="{AD6F7F6C-6CC4-4F5A-97D9-293FAF7AD4C6}"/>
-    <hyperlink ref="F6" r:id="rId82" xr:uid="{6A4738D8-2CCC-40F0-A75D-AED17777BD7F}"/>
-    <hyperlink ref="F7" r:id="rId83" xr:uid="{A1EAB810-3396-4438-9B7E-658BC583633E}"/>
-    <hyperlink ref="G43" r:id="rId84" xr:uid="{8B55708E-95ED-4853-9BBE-6271E4E5B327}"/>
-    <hyperlink ref="G52" r:id="rId85" xr:uid="{83D93986-820A-426C-8C24-B961323BADFE}"/>
-    <hyperlink ref="E145" r:id="rId86" xr:uid="{95272B36-1B3E-4E9F-A78F-B49AAE3263D2}"/>
-    <hyperlink ref="E146:E174" r:id="rId87" display="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/Imagine.pdf" xr:uid="{D958AEE0-FAA3-4065-B126-6557F87E05A9}"/>
-    <hyperlink ref="E146" r:id="rId88" xr:uid="{43838F99-75E5-4924-A97E-2531FB82672F}"/>
-    <hyperlink ref="G75" r:id="rId89" xr:uid="{2F0FFC39-FD18-42E2-A35A-72A93D0CB54F}"/>
-    <hyperlink ref="G79" r:id="rId90" xr:uid="{AB99604A-9B64-4E9F-A814-DD4D254AE437}"/>
-    <hyperlink ref="G78" r:id="rId91" xr:uid="{B129DBCD-C2C6-4DA8-8342-404C0108A695}"/>
-    <hyperlink ref="G130" r:id="rId92" xr:uid="{C6D7B5EE-9444-4217-8255-0989F4C2A972}"/>
-    <hyperlink ref="G133" r:id="rId93" xr:uid="{4C4DD5E8-6291-4B28-B0C2-0AAD57143E00}"/>
-    <hyperlink ref="G131" r:id="rId94" xr:uid="{B88FC6B3-5EEF-4DFD-B2AD-4CC0466B9506}"/>
-    <hyperlink ref="G132" r:id="rId95" xr:uid="{DB565809-20B2-4A11-860A-11B4868E1FBB}"/>
-    <hyperlink ref="G41" r:id="rId96" xr:uid="{3B4FD59A-0AB6-4ED4-B8F2-C2742B70518C}"/>
-    <hyperlink ref="F161" r:id="rId97" xr:uid="{31F5BEED-4304-4333-9E5A-1BCFBD485562}"/>
+    <hyperlink ref="E8" r:id="rId2" xr:uid="{88D8986D-4208-4DB4-AA3C-408B291B290B}"/>
+    <hyperlink ref="E9" r:id="rId3" xr:uid="{9E9211E8-7EE6-4BC2-85F6-9F9F686372C4}"/>
+    <hyperlink ref="E10" r:id="rId4" xr:uid="{7243CEC3-5A0A-4E29-8F03-33B735B095F3}"/>
+    <hyperlink ref="E11" r:id="rId5" xr:uid="{C8B16079-03B8-4030-BA75-4B605BBB3BEE}"/>
+    <hyperlink ref="E12" r:id="rId6" xr:uid="{86D4C588-9329-41E2-958C-9F86500C4A79}"/>
+    <hyperlink ref="E13" r:id="rId7" xr:uid="{23C8F005-44A1-420D-B7C6-86B021444B29}"/>
+    <hyperlink ref="E14" r:id="rId8" xr:uid="{1841704F-BE6D-4C58-B9E2-B54A85752386}"/>
+    <hyperlink ref="E15" r:id="rId9" xr:uid="{71608296-C556-4006-B2F3-7CF82D2BEACA}"/>
+    <hyperlink ref="E16" r:id="rId10" xr:uid="{E7EEBF75-18B9-49D2-AC96-05D7F550B9FC}"/>
+    <hyperlink ref="E17" r:id="rId11" xr:uid="{D9B85AC2-E7B0-4F2C-B945-9EAF72932786}"/>
+    <hyperlink ref="E18" r:id="rId12" xr:uid="{4087435B-3AE6-4D52-A4AF-03F841504CE8}"/>
+    <hyperlink ref="E19" r:id="rId13" xr:uid="{CBB29244-D43D-4912-9F30-6A820F1CE395}"/>
+    <hyperlink ref="E20" r:id="rId14" xr:uid="{6371347D-6DF7-4829-8229-7C58298FC7D7}"/>
+    <hyperlink ref="E21" r:id="rId15" xr:uid="{FB7B490E-9A47-49F6-8BDE-C4333CC95D08}"/>
+    <hyperlink ref="E22" r:id="rId16" xr:uid="{5CE486C6-BA97-44DE-BCA6-041B9E2E4570}"/>
+    <hyperlink ref="E23" r:id="rId17" xr:uid="{F84AD7C5-69E7-445A-978F-F4E74281D42C}"/>
+    <hyperlink ref="E24" r:id="rId18" xr:uid="{FBE6104B-0B43-4B12-9E73-B6AC2916FF59}"/>
+    <hyperlink ref="E25" r:id="rId19" xr:uid="{5BC31F52-D087-47A1-890B-0436F6C8AF27}"/>
+    <hyperlink ref="E26" r:id="rId20" xr:uid="{73427174-3CED-48A5-8BAC-176635B3D233}"/>
+    <hyperlink ref="E27" r:id="rId21" xr:uid="{29AB34CD-9C32-4850-83F7-1A27A00FE2C8}"/>
+    <hyperlink ref="E28" r:id="rId22" xr:uid="{CF9097BD-0702-4A2C-8DE7-B70C4B349FB2}"/>
+    <hyperlink ref="E29" r:id="rId23" xr:uid="{CE543A6D-54FB-46F3-966C-F5221D8C2203}"/>
+    <hyperlink ref="E30" r:id="rId24" xr:uid="{BA602D91-48ED-404C-B2D3-50A8C384D59A}"/>
+    <hyperlink ref="E31" r:id="rId25" xr:uid="{0776C1CD-A75E-4C60-807F-F260F902A273}"/>
+    <hyperlink ref="E32" r:id="rId26" xr:uid="{AABDE33C-27EF-4E2D-B583-E3099BD432A4}"/>
+    <hyperlink ref="E33" r:id="rId27" xr:uid="{682DFD0B-E187-4D3A-8F81-5A231E6CFB70}"/>
+    <hyperlink ref="E34" r:id="rId28" xr:uid="{92A05B9B-F230-4E14-8CD9-5BAA2E071782}"/>
+    <hyperlink ref="E35" r:id="rId29" xr:uid="{5C6C7112-FA8E-424E-8C6D-6CC3E20BBD7C}"/>
+    <hyperlink ref="E36" r:id="rId30" xr:uid="{EAF6C162-43AB-4D1A-B7F2-A67071E53C5C}"/>
+    <hyperlink ref="E37" r:id="rId31" xr:uid="{67BD4B36-5169-4C14-935D-89E596B0B0D6}"/>
+    <hyperlink ref="E38" r:id="rId32" xr:uid="{5F9AF9A7-15DE-4927-9431-E59E7226C95C}"/>
+    <hyperlink ref="E39" r:id="rId33" xr:uid="{24951338-93CE-49FB-8287-7FCBEE8CAFA1}"/>
+    <hyperlink ref="E41" r:id="rId34" xr:uid="{952B6FDE-C7AD-4493-B8DA-35B7F8DEB981}"/>
+    <hyperlink ref="F10" r:id="rId35" xr:uid="{50B60948-F77B-4953-B029-D3AC81770E9D}"/>
+    <hyperlink ref="F24" r:id="rId36" xr:uid="{B92A8409-4E93-43A8-9FB9-48BB25DFB3F9}"/>
+    <hyperlink ref="F27" r:id="rId37" xr:uid="{DD4C656C-BB6C-489D-A875-4E0F32DA286E}"/>
+    <hyperlink ref="F30" r:id="rId38" xr:uid="{CF4B1736-FA73-4E0F-A4B0-8F03043104F6}"/>
+    <hyperlink ref="F36" r:id="rId39" xr:uid="{428AD378-0DCC-4D86-880C-2B400D312B34}"/>
+    <hyperlink ref="F43" r:id="rId40" xr:uid="{8CB8E30B-6D23-4FF2-9C71-E5E4CF9ECEEA}"/>
+    <hyperlink ref="F50" r:id="rId41" xr:uid="{5F2403DE-63F2-4418-9AE9-6F0E3478366F}"/>
+    <hyperlink ref="E72" r:id="rId42" xr:uid="{C91572DC-2EDB-4786-B760-FD7E25D2971E}"/>
+    <hyperlink ref="E66" r:id="rId43" xr:uid="{0F7C9799-DF00-43B1-9FD5-5ABEE8361557}"/>
+    <hyperlink ref="E108" r:id="rId44" xr:uid="{230024D0-CB1E-4A2E-8579-A51DD6156739}"/>
+    <hyperlink ref="E126" r:id="rId45" xr:uid="{18732992-8388-4869-9638-236923812CB6}"/>
+    <hyperlink ref="E129" r:id="rId46" xr:uid="{61D67154-64CD-4E7D-A1D6-F595036679CC}"/>
+    <hyperlink ref="F163" r:id="rId47" xr:uid="{2F224CE7-4FD5-489A-9227-F0C003B85261}"/>
+    <hyperlink ref="F164" r:id="rId48" xr:uid="{28F66E20-CF60-4BCF-BB90-8D19B362F1CA}"/>
+    <hyperlink ref="F170" r:id="rId49" xr:uid="{0778CE07-A13C-48EE-B9A3-B4EC6DA47FF3}"/>
+    <hyperlink ref="F169" r:id="rId50" xr:uid="{04B5C6AB-CF34-4F2D-B02F-CFFDD831421E}"/>
+    <hyperlink ref="F154" r:id="rId51" xr:uid="{0EC453EC-9A44-446B-98B6-F76BEF646FA6}"/>
+    <hyperlink ref="F126" r:id="rId52" xr:uid="{D6E45949-0D52-4771-ACF3-D13E9F2E6B25}"/>
+    <hyperlink ref="E123" r:id="rId53" xr:uid="{6F52B6CC-D50B-458C-AD3E-D9AC25A941AA}"/>
+    <hyperlink ref="E124" r:id="rId54" xr:uid="{B81B82D2-BB04-43D5-BD74-59ACAA4F0778}"/>
+    <hyperlink ref="E125" r:id="rId55" xr:uid="{95A629AD-67BD-4AC4-8196-1863CCC24475}"/>
+    <hyperlink ref="E109" r:id="rId56" xr:uid="{1B47E129-3E4A-4CC6-9F27-1466353588BC}"/>
+    <hyperlink ref="E110" r:id="rId57" xr:uid="{4FD4CD76-B867-4AF2-927A-0E8C2D2032E8}"/>
+    <hyperlink ref="E111" r:id="rId58" xr:uid="{9F36D981-3652-46FE-A715-428DEFF257EA}"/>
+    <hyperlink ref="E112" r:id="rId59" xr:uid="{18A3E522-1FDF-42F4-B4E6-942FF7CD60FB}"/>
+    <hyperlink ref="E113" r:id="rId60" xr:uid="{7A06205F-74AF-45B9-B532-08F4E9F5B03F}"/>
+    <hyperlink ref="E114" r:id="rId61" xr:uid="{D9C4CB61-1E3C-4CF9-9BBE-B24DC995D996}"/>
+    <hyperlink ref="E115" r:id="rId62" xr:uid="{BFFE9820-15C4-458A-8A2F-C4A333336B97}"/>
+    <hyperlink ref="E116" r:id="rId63" xr:uid="{8D713FF4-76B1-4863-B785-37990D6B4A6C}"/>
+    <hyperlink ref="E117" r:id="rId64" xr:uid="{3747C92A-960C-4794-97F0-9B5B911C9BDF}"/>
+    <hyperlink ref="E118" r:id="rId65" xr:uid="{68012D0E-2C31-486A-A802-3E497CAEC7F5}"/>
+    <hyperlink ref="E119" r:id="rId66" xr:uid="{F084E286-0835-4876-8C34-0EC92DA4B0E6}"/>
+    <hyperlink ref="E120" r:id="rId67" xr:uid="{B81015F1-B16B-4CA1-87B3-950A9163F096}"/>
+    <hyperlink ref="E121" r:id="rId68" xr:uid="{A57E3390-66FA-4E24-93B0-5D3D3858231E}"/>
+    <hyperlink ref="E122" r:id="rId69" xr:uid="{B24BF8ED-1FB1-4E67-8DA9-FDEC158DFE06}"/>
+    <hyperlink ref="E128" r:id="rId70" xr:uid="{8CE013AA-8243-4E22-98A7-A63E2969F1D6}"/>
+    <hyperlink ref="E130" r:id="rId71" xr:uid="{25068463-871B-497D-94F1-8D101E31C03B}"/>
+    <hyperlink ref="E131" r:id="rId72" xr:uid="{8E939E20-8365-4082-A0C6-E21EDC90EE19}"/>
+    <hyperlink ref="E132" r:id="rId73" xr:uid="{496192E8-B7C8-4049-BBF1-F5A87F3ADE27}"/>
+    <hyperlink ref="E133" r:id="rId74" xr:uid="{36D3CDA5-E45C-4936-AA39-2D3BD750B7A6}"/>
+    <hyperlink ref="E134" r:id="rId75" xr:uid="{2FF293E4-AD4B-40AE-B71B-18FEEA326F9C}"/>
+    <hyperlink ref="E135" r:id="rId76" xr:uid="{05292FD0-3F61-4937-AF0C-E47EF43985D5}"/>
+    <hyperlink ref="E136" r:id="rId77" xr:uid="{4DB7870E-3BE3-4347-8DFB-884BD5774BE7}"/>
+    <hyperlink ref="E137" r:id="rId78" xr:uid="{788E3604-E9A3-4B0B-99C6-9E267438251D}"/>
+    <hyperlink ref="E138" r:id="rId79" xr:uid="{6FDC3EBB-1370-4D67-8457-5374A766616A}"/>
+    <hyperlink ref="F5" r:id="rId80" xr:uid="{AD6F7F6C-6CC4-4F5A-97D9-293FAF7AD4C6}"/>
+    <hyperlink ref="F6" r:id="rId81" xr:uid="{6A4738D8-2CCC-40F0-A75D-AED17777BD7F}"/>
+    <hyperlink ref="F7" r:id="rId82" xr:uid="{A1EAB810-3396-4438-9B7E-658BC583633E}"/>
+    <hyperlink ref="G43" r:id="rId83" xr:uid="{8B55708E-95ED-4853-9BBE-6271E4E5B327}"/>
+    <hyperlink ref="G52" r:id="rId84" xr:uid="{83D93986-820A-426C-8C24-B961323BADFE}"/>
+    <hyperlink ref="G75" r:id="rId85" xr:uid="{2F0FFC39-FD18-42E2-A35A-72A93D0CB54F}"/>
+    <hyperlink ref="G79" r:id="rId86" xr:uid="{AB99604A-9B64-4E9F-A814-DD4D254AE437}"/>
+    <hyperlink ref="G78" r:id="rId87" xr:uid="{B129DBCD-C2C6-4DA8-8342-404C0108A695}"/>
+    <hyperlink ref="G130" r:id="rId88" xr:uid="{C6D7B5EE-9444-4217-8255-0989F4C2A972}"/>
+    <hyperlink ref="G133" r:id="rId89" xr:uid="{4C4DD5E8-6291-4B28-B0C2-0AAD57143E00}"/>
+    <hyperlink ref="G131" r:id="rId90" xr:uid="{B88FC6B3-5EEF-4DFD-B2AD-4CC0466B9506}"/>
+    <hyperlink ref="G132" r:id="rId91" xr:uid="{DB565809-20B2-4A11-860A-11B4868E1FBB}"/>
+    <hyperlink ref="G41" r:id="rId92" xr:uid="{3B4FD59A-0AB6-4ED4-B8F2-C2742B70518C}"/>
+    <hyperlink ref="F161" r:id="rId93" xr:uid="{31F5BEED-4304-4333-9E5A-1BCFBD485562}"/>
+    <hyperlink ref="L145" r:id="rId94" xr:uid="{D130D285-7476-419D-97AE-FC0EEF3770EC}"/>
+    <hyperlink ref="E145" r:id="rId95" xr:uid="{95272B36-1B3E-4E9F-A78F-B49AAE3263D2}"/>
+    <hyperlink ref="E146" r:id="rId96" xr:uid="{43838F99-75E5-4924-A97E-2531FB82672F}"/>
+    <hyperlink ref="E152" r:id="rId97" xr:uid="{9E43E84E-28DC-45F6-B890-1DDC89D2611E}"/>
+    <hyperlink ref="E148" r:id="rId98" xr:uid="{0BF35229-48BA-4BC6-ADC3-9EC929EF1C7D}"/>
+    <hyperlink ref="E151" r:id="rId99" xr:uid="{9A7D13AA-7CD9-45C8-B039-4D58DEED3EA6}"/>
+    <hyperlink ref="E153" r:id="rId100" xr:uid="{794D813D-CABF-4A6D-8721-9FC4B568BFF2}"/>
+    <hyperlink ref="E154" r:id="rId101" xr:uid="{22166333-6AEC-4BB7-B42E-374623E39238}"/>
+    <hyperlink ref="E155" r:id="rId102" xr:uid="{BE02D1A8-8E25-4672-8CD0-AB67C20A8DDF}"/>
+    <hyperlink ref="E156" r:id="rId103" xr:uid="{1DCE9C16-37C9-4E6F-A491-838DE5B8EE43}"/>
+    <hyperlink ref="E157" r:id="rId104" xr:uid="{FF7631DB-BF07-4301-8AF9-575C5D6710F6}"/>
+    <hyperlink ref="E158" r:id="rId105" xr:uid="{CF717710-52A9-4D43-B731-A4DDCCAD1C67}"/>
+    <hyperlink ref="E159" r:id="rId106" xr:uid="{CE9B0085-5B3E-4B11-9D7E-127D01782A24}"/>
+    <hyperlink ref="E160" r:id="rId107" xr:uid="{A91011F1-1116-4696-AB2E-04CA708E3A3C}"/>
+    <hyperlink ref="E161" r:id="rId108" xr:uid="{8D23F4B5-2D97-422B-A0BF-77016BF8CE41}"/>
+    <hyperlink ref="E162" r:id="rId109" xr:uid="{04EE6F15-3072-477D-87F5-6BF21DD22FCA}"/>
+    <hyperlink ref="E163" r:id="rId110" xr:uid="{1453B87A-4A2F-4835-8E40-D0BF4A75431B}"/>
+    <hyperlink ref="E164" r:id="rId111" xr:uid="{E0338F08-B1ED-4C0A-AD18-38FA37D877C7}"/>
+    <hyperlink ref="E165" r:id="rId112" xr:uid="{612040B4-768C-4BE9-9AAB-552CD7771E32}"/>
+    <hyperlink ref="E174" r:id="rId113" xr:uid="{D5CBE5A7-B56F-4686-8276-ECEBD4A080CA}"/>
+    <hyperlink ref="E166" r:id="rId114" xr:uid="{71DAB66E-2E6E-4E8A-A1A2-E0DD96123B12}"/>
+    <hyperlink ref="E168" r:id="rId115" xr:uid="{96CDCB0E-358B-4077-B2AD-A29C3FBAAF72}"/>
+    <hyperlink ref="E169" r:id="rId116" xr:uid="{E08DCED1-F60E-4BFE-8492-E13E047BC6E7}"/>
+    <hyperlink ref="E170" r:id="rId117" xr:uid="{4222D1A5-7630-45E6-BE85-FE392A2F7B51}"/>
+    <hyperlink ref="E171" r:id="rId118" xr:uid="{13554329-7DA7-47F7-968D-0B0D45F911F6}"/>
+    <hyperlink ref="L174" r:id="rId119" xr:uid="{9774B588-923D-43BA-855A-753BB5A557DB}"/>
+    <hyperlink ref="L173" r:id="rId120" xr:uid="{B41B9A15-7504-4797-835A-5F0F4E207FE1}"/>
+    <hyperlink ref="L146:L172" r:id="rId121" display="https://raw.githubusercontent.com/CadelMVH/Wix-Gallery-Downloads/main/Tempo/" xr:uid="{66564DED-5DE0-4D33-BB35-76E6E313ECAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
